--- a/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
+++ b/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Plantilla y elegibilidad" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Reglas (resumen)" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="ListaValida" sheetId="11" state="hidden" r:id="rId13"/>
+    <sheet name="Histórico de guardias" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -877,7 +878,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="635">
   <si>
     <t xml:space="preserve">Cuadrante de Guardias — Servicio de Anestesiología y Reanimación</t>
   </si>
@@ -2198,6 +2199,45 @@
     <t xml:space="preserve">R4</t>
   </si>
   <si>
+    <t xml:space="preserve">Médicos sin guardias en octubre 2026 — añadidos al radar, elegibilidad SIN CONFIRMAR salvo la de R4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula Durán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inma</t>
+  </si>
+  <si>
     <t xml:space="preserve">Homónimos — usa siempre el ID, nunca el nombre suelto (§3.1)</t>
   </si>
   <si>
@@ -2244,6 +2284,510 @@
   </si>
   <si>
     <t xml:space="preserve">UCQ-Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISTÓRICO DE GUARDIAS · transcrito desde calendarios de meses anteriores — REVISAR antes de usar para repartir noviembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transcripción manual desde imágenes de calendarios (junio–septiembre 2026). Puede contener errores de lectura — revisa una muestra antes de confiar en los totales. Los puestos PEQ marcados solo como 'R1' en el calendario original no se han contabilizado (no se sabe quién los cubrió). Preparado para ampliar: añade filas nuevas debajo de la última fila de datos y las fórmulas de resumen las recogerán solas (el rango llega hasta la fila 500).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Día semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Festivo Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otro 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otro 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otro 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otro 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junio 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PatriciaR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miércoles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jueves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PatriciaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sábado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DavidR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agosto 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asuncion de la Virgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Septiembre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESUMEN POR PERSONA (fórmulas sobre la tabla en bruto de arriba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDS Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDS Sábado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDS Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX fin de semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX diario/entre semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Festivos Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total guardias histórico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fátima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asís</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricia (R2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana (R2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricia (R3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Gaudioso (R4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (fuera oct)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David (HULP)</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2799,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="63">
+  <fonts count="70">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2715,6 +3259,28 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF7C3D08"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFA02020"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2728,8 +3294,35 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="31">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2829,13 +3422,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE9E7"/>
-        <bgColor rgb="FFFDE2E0"/>
+        <bgColor rgb="FFFBE3DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE2E0"/>
-        <bgColor rgb="FFFBE9E7"/>
+        <bgColor rgb="FFFBE3DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2847,7 +3440,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE5E9EF"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFEDE7F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -2871,7 +3464,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -2889,7 +3482,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6B26B"/>
-        <bgColor rgb="FFCBD5E1"/>
+        <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2910,8 +3503,32 @@
         <bgColor rgb="FFE5E9EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50519E"/>
+        <bgColor rgb="FF44546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE7F6"/>
+        <bgColor rgb="FFE5E9EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE3DC"/>
+        <bgColor rgb="FFFDE2E0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -3018,6 +3635,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3044,7 +3676,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="143">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3457,10 +4089,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3545,16 +4173,80 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="61" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="62" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="32" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="69" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="68" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="69" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3571,18 +4263,18 @@
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFC00000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFF3F4F6"/>
+      <rgbColor rgb="FFF7F9FC"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFF4F7F4"/>
+      <rgbColor rgb="FFE5E9EF"/>
       <rgbColor rgb="FF375623"/>
       <rgbColor rgb="FF1E5B2A"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF4B5563"/>
       <rgbColor rgb="FF047857"/>
-      <rgbColor rgb="FFD6DBE1"/>
+      <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF8E7CC3"/>
       <rgbColor rgb="FFA02020"/>
@@ -3593,26 +4285,26 @@
       <rgbColor rgb="FF1D4ED8"/>
       <rgbColor rgb="FFCBD5E1"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFF7F9FC"/>
+      <rgbColor rgb="FFF8F9FA"/>
+      <rgbColor rgb="FFFFF3CD"/>
+      <rgbColor rgb="FFEDF7ED"/>
       <rgbColor rgb="FF44546A"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF7C5CBF"/>
       <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFF8F9FA"/>
+      <rgbColor rgb="FFEEF2F7"/>
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FFD1FAE5"/>
       <rgbColor rgb="FFFEF3C7"/>
+      <rgbColor rgb="FFD6DBE1"/>
+      <rgbColor rgb="FFFDE2E0"/>
+      <rgbColor rgb="FFEDE7F6"/>
+      <rgbColor rgb="FFF6B26B"/>
+      <rgbColor rgb="FF50519E"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFDE2E0"/>
-      <rgbColor rgb="FFE5E9EF"/>
-      <rgbColor rgb="FFF6B26B"/>
-      <rgbColor rgb="FF7C5CBF"/>
-      <rgbColor rgb="FFF3F4F6"/>
-      <rgbColor rgb="FFEDF7ED"/>
+      <rgbColor rgb="FFFBE3DC"/>
       <rgbColor rgb="FFFBE9E7"/>
-      <rgbColor rgb="FFEEF2F7"/>
       <rgbColor rgb="FFB45309"/>
       <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF9AA0A6"/>
@@ -3851,17 +4543,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
@@ -3930,21 +4622,21 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="113" t="s">
-        <v>440</v>
-      </c>
-      <c r="B1" s="113"/>
+      <c r="A1" s="112" t="s">
+        <v>453</v>
+      </c>
+      <c r="B1" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="127" t="s">
-        <v>441</v>
+      <c r="A3" s="130" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="96" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="116" t="s">
         <v>265</v>
       </c>
     </row>
@@ -3952,7 +4644,7 @@
       <c r="A5" s="100" t="s">
         <v>268</v>
       </c>
-      <c r="B5" s="119" t="s">
+      <c r="B5" s="118" t="s">
         <v>269</v>
       </c>
     </row>
@@ -3960,7 +4652,7 @@
       <c r="A6" s="96" t="s">
         <v>272</v>
       </c>
-      <c r="B6" s="117" t="s">
+      <c r="B6" s="116" t="s">
         <v>273</v>
       </c>
     </row>
@@ -3968,7 +4660,7 @@
       <c r="A7" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="118" t="s">
         <v>275</v>
       </c>
     </row>
@@ -3976,7 +4668,7 @@
       <c r="A8" s="96" t="s">
         <v>276</v>
       </c>
-      <c r="B8" s="117" t="s">
+      <c r="B8" s="116" t="s">
         <v>277</v>
       </c>
     </row>
@@ -3984,7 +4676,7 @@
       <c r="A9" s="100" t="s">
         <v>279</v>
       </c>
-      <c r="B9" s="119" t="s">
+      <c r="B9" s="118" t="s">
         <v>280</v>
       </c>
     </row>
@@ -3992,7 +4684,7 @@
       <c r="A10" s="96" t="s">
         <v>281</v>
       </c>
-      <c r="B10" s="117" t="s">
+      <c r="B10" s="116" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4000,7 +4692,7 @@
       <c r="A11" s="100" t="s">
         <v>283</v>
       </c>
-      <c r="B11" s="119" t="s">
+      <c r="B11" s="118" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4008,7 +4700,7 @@
       <c r="A12" s="96" t="s">
         <v>285</v>
       </c>
-      <c r="B12" s="117" t="s">
+      <c r="B12" s="116" t="s">
         <v>286</v>
       </c>
     </row>
@@ -4016,7 +4708,7 @@
       <c r="A13" s="100" t="s">
         <v>287</v>
       </c>
-      <c r="B13" s="119" t="s">
+      <c r="B13" s="118" t="s">
         <v>288</v>
       </c>
     </row>
@@ -4024,7 +4716,7 @@
       <c r="A14" s="96" t="s">
         <v>291</v>
       </c>
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="116" t="s">
         <v>292</v>
       </c>
     </row>
@@ -4032,7 +4724,7 @@
       <c r="A15" s="100" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="118" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4040,7 +4732,7 @@
       <c r="A16" s="96" t="s">
         <v>295</v>
       </c>
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="116" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4048,7 +4740,7 @@
       <c r="A17" s="100" t="s">
         <v>297</v>
       </c>
-      <c r="B17" s="119" t="s">
+      <c r="B17" s="118" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4056,7 +4748,7 @@
       <c r="A18" s="96" t="s">
         <v>299</v>
       </c>
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="116" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4064,7 +4756,7 @@
       <c r="A19" s="100" t="s">
         <v>302</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="118" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4072,7 +4764,7 @@
       <c r="A20" s="96" t="s">
         <v>305</v>
       </c>
-      <c r="B20" s="117" t="s">
+      <c r="B20" s="116" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4080,69 +4772,69 @@
       <c r="A21" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="118" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="127" t="s">
-        <v>442</v>
+      <c r="A23" s="130" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
         <v>317</v>
       </c>
-      <c r="B24" s="114" t="s">
-        <v>443</v>
+      <c r="B24" s="113" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="115" t="s">
-        <v>444</v>
+      <c r="B25" s="114" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
         <v>321</v>
       </c>
-      <c r="B26" s="114" t="s">
-        <v>445</v>
+      <c r="B26" s="113" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="B27" s="115" t="s">
-        <v>446</v>
+      <c r="B27" s="114" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="96" t="s">
         <v>325</v>
       </c>
-      <c r="B28" s="114" t="s">
-        <v>447</v>
+      <c r="B28" s="113" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="100" t="s">
-        <v>448</v>
-      </c>
-      <c r="B29" s="115" t="s">
-        <v>449</v>
+        <v>461</v>
+      </c>
+      <c r="B29" s="114" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="96" t="s">
         <v>327</v>
       </c>
-      <c r="B30" s="114" t="s">
-        <v>450</v>
+      <c r="B30" s="113" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -4167,7 +4859,7 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -4181,7 +4873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -4195,7 +4887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>67</v>
       </c>
@@ -4209,7 +4901,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
@@ -4223,12 +4915,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>72</v>
@@ -4237,7 +4929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>106</v>
       </c>
@@ -4251,7 +4943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -4262,7 +4954,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -4273,15 +4965,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
@@ -4289,45 +4981,5141 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L533"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="131" t="s">
+        <v>467</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+    </row>
+    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="132" t="s">
+        <v>468</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="131" t="s">
+        <v>469</v>
+      </c>
+      <c r="B4" s="131" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4" s="131" t="s">
+        <v>330</v>
+      </c>
+      <c r="D4" s="131" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" s="131" t="s">
+        <v>472</v>
+      </c>
+      <c r="F4" s="131" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="131" t="s">
+        <v>473</v>
+      </c>
+      <c r="H4" s="131" t="s">
+        <v>474</v>
+      </c>
+      <c r="I4" s="131" t="s">
+        <v>475</v>
+      </c>
+      <c r="J4" s="131" t="s">
+        <v>476</v>
+      </c>
+      <c r="K4" s="131" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="134" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E5" s="133"/>
+      <c r="F5" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G5" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H5" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I5" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="J5" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="K5" s="134"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="134" t="s">
+        <v>482</v>
+      </c>
+      <c r="D6" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E6" s="133"/>
+      <c r="F6" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H6" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I6" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J6" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K6" s="134"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B7" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="134" t="s">
+        <v>485</v>
+      </c>
+      <c r="D7" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E7" s="133"/>
+      <c r="F7" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I7" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" s="134"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B8" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="134" t="s">
+        <v>487</v>
+      </c>
+      <c r="D8" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="133"/>
+      <c r="F8" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H8" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J8" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" s="134"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B9" s="134" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="134" t="s">
+        <v>490</v>
+      </c>
+      <c r="D9" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E9" s="133"/>
+      <c r="F9" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G9" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="H9" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I9" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="J9" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="134"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10" s="136" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="136" t="s">
+        <v>493</v>
+      </c>
+      <c r="D10" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E10" s="135"/>
+      <c r="F10" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G10" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="H10" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I10" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="J10" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="K10" s="136"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B11" s="136" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="136" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G11" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="136"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B12" s="134" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="134" t="s">
+        <v>497</v>
+      </c>
+      <c r="D12" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E12" s="133"/>
+      <c r="F12" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G12" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H12" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J12" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K12" s="134"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B13" s="134" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="134" t="s">
+        <v>498</v>
+      </c>
+      <c r="D13" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E13" s="133"/>
+      <c r="F13" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G13" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J13" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K13" s="134"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B14" s="134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="134" t="s">
+        <v>499</v>
+      </c>
+      <c r="D14" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E14" s="133"/>
+      <c r="F14" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H14" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="I14" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J14" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K14" s="134"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B15" s="134" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="134" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E15" s="133"/>
+      <c r="F15" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I15" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J15" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K15" s="134"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B16" s="134" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="134" t="s">
+        <v>502</v>
+      </c>
+      <c r="D16" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E16" s="133"/>
+      <c r="F16" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H16" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I16" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J16" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="K16" s="134"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B17" s="136" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="136" t="s">
+        <v>503</v>
+      </c>
+      <c r="D17" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E17" s="135"/>
+      <c r="F17" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="H17" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="I17" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="K17" s="136"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B18" s="136" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="136" t="s">
+        <v>504</v>
+      </c>
+      <c r="D18" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E18" s="135"/>
+      <c r="F18" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="H18" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="I18" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="J18" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="K18" s="136"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B19" s="134" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="134" t="s">
+        <v>505</v>
+      </c>
+      <c r="D19" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E19" s="133"/>
+      <c r="F19" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="H19" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I19" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="J19" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K19" s="134"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B20" s="134" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="134" t="s">
+        <v>506</v>
+      </c>
+      <c r="D20" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E20" s="133"/>
+      <c r="F20" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G20" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I20" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="J20" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K20" s="134"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B21" s="134" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="134" t="s">
+        <v>507</v>
+      </c>
+      <c r="D21" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E21" s="133"/>
+      <c r="F21" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H21" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I21" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K21" s="134"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" s="134" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="134" t="s">
+        <v>508</v>
+      </c>
+      <c r="D22" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E22" s="133"/>
+      <c r="F22" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G22" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H22" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="I22" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J22" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K22" s="134"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B23" s="134" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="134" t="s">
+        <v>509</v>
+      </c>
+      <c r="D23" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E23" s="133"/>
+      <c r="F23" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I23" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J23" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K23" s="134"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B24" s="136" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="136" t="s">
+        <v>510</v>
+      </c>
+      <c r="D24" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E24" s="135"/>
+      <c r="F24" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G24" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H24" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="J24" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="136"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B25" s="136" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" s="136" t="s">
+        <v>511</v>
+      </c>
+      <c r="D25" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E25" s="135"/>
+      <c r="F25" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G25" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="H25" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I25" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="J25" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="K25" s="136"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B26" s="134" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="134" t="s">
+        <v>512</v>
+      </c>
+      <c r="D26" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E26" s="133"/>
+      <c r="F26" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G26" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H26" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I26" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="J26" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="K26" s="134"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B27" s="134" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="134" t="s">
+        <v>513</v>
+      </c>
+      <c r="D27" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E27" s="133"/>
+      <c r="F27" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G27" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H27" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I27" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J27" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K27" s="134"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B28" s="134" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="134" t="s">
+        <v>514</v>
+      </c>
+      <c r="D28" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E28" s="133"/>
+      <c r="F28" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G28" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H28" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I28" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J28" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K28" s="134"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B29" s="134" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="134" t="s">
+        <v>515</v>
+      </c>
+      <c r="D29" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E29" s="133"/>
+      <c r="F29" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G29" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="H29" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I29" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J29" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K29" s="134"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B30" s="134" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="134" t="s">
+        <v>516</v>
+      </c>
+      <c r="D30" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E30" s="133"/>
+      <c r="F30" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G30" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H30" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I30" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J30" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K30" s="134"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="136" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="136" t="s">
+        <v>517</v>
+      </c>
+      <c r="D31" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E31" s="135"/>
+      <c r="F31" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="G31" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="I31" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="J31" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="K31" s="136"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="B32" s="136" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" s="136" t="s">
+        <v>518</v>
+      </c>
+      <c r="D32" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E32" s="135"/>
+      <c r="F32" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="I32" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="J32" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="K32" s="136"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B33" s="134" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" s="134" t="s">
+        <v>519</v>
+      </c>
+      <c r="D33" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E33" s="133"/>
+      <c r="F33" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G33" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H33" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I33" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="J33" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K33" s="134" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="133" t="s">
+        <v>478</v>
+      </c>
+      <c r="B34" s="134" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="134" t="s">
+        <v>520</v>
+      </c>
+      <c r="D34" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E34" s="133"/>
+      <c r="F34" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G34" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H34" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I34" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="J34" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="K34" s="134"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B35" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="134" t="s">
+        <v>522</v>
+      </c>
+      <c r="D35" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E35" s="133"/>
+      <c r="F35" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G35" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H35" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="I35" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J35" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="134"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B36" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="134" t="s">
+        <v>523</v>
+      </c>
+      <c r="D36" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E36" s="133"/>
+      <c r="F36" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G36" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I36" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="J36" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K36" s="134"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B37" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="134" t="s">
+        <v>524</v>
+      </c>
+      <c r="D37" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E37" s="133"/>
+      <c r="F37" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G37" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H37" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I37" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J37" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K37" s="134"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B38" s="136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="136" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E38" s="135"/>
+      <c r="F38" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G38" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="H38" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="J38" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="K38" s="136"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B39" s="136" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="136" t="s">
+        <v>526</v>
+      </c>
+      <c r="D39" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E39" s="135"/>
+      <c r="F39" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G39" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="H39" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="I39" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="J39" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K39" s="136"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B40" s="134" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="134" t="s">
+        <v>527</v>
+      </c>
+      <c r="D40" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E40" s="133"/>
+      <c r="F40" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G40" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H40" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K40" s="134"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B41" s="134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="134" t="s">
+        <v>528</v>
+      </c>
+      <c r="D41" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E41" s="133"/>
+      <c r="F41" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G41" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H41" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I41" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J41" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="K41" s="134"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B42" s="134" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="134" t="s">
+        <v>529</v>
+      </c>
+      <c r="D42" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E42" s="133"/>
+      <c r="F42" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G42" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H42" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I42" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="J42" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K42" s="134"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B43" s="134" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="134" t="s">
+        <v>530</v>
+      </c>
+      <c r="D43" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E43" s="133"/>
+      <c r="F43" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G43" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H43" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I43" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J43" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K43" s="134"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B44" s="134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="134" t="s">
+        <v>531</v>
+      </c>
+      <c r="D44" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E44" s="133"/>
+      <c r="F44" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G44" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I44" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J44" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K44" s="134"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B45" s="136" t="n">
+        <v>11</v>
+      </c>
+      <c r="C45" s="136" t="s">
+        <v>532</v>
+      </c>
+      <c r="D45" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E45" s="135"/>
+      <c r="F45" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H45" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="I45" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="J45" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K45" s="136"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B46" s="136" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" s="136" t="s">
+        <v>533</v>
+      </c>
+      <c r="D46" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E46" s="135"/>
+      <c r="F46" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G46" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="H46" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="I46" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="J46" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="K46" s="136"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B47" s="134" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="134" t="s">
+        <v>534</v>
+      </c>
+      <c r="D47" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E47" s="133"/>
+      <c r="F47" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G47" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H47" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J47" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K47" s="134"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B48" s="134" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="134" t="s">
+        <v>535</v>
+      </c>
+      <c r="D48" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E48" s="133"/>
+      <c r="F48" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G48" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H48" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I48" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="J48" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K48" s="134"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B49" s="134" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="134" t="s">
+        <v>536</v>
+      </c>
+      <c r="D49" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E49" s="133"/>
+      <c r="F49" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G49" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H49" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I49" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J49" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K49" s="134"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B50" s="134" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="134" t="s">
+        <v>537</v>
+      </c>
+      <c r="D50" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E50" s="133"/>
+      <c r="F50" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G50" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H50" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I50" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J50" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K50" s="134"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B51" s="134" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" s="134" t="s">
+        <v>538</v>
+      </c>
+      <c r="D51" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E51" s="133"/>
+      <c r="F51" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G51" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H51" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I51" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="J51" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K51" s="134"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B52" s="136" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" s="136" t="s">
+        <v>539</v>
+      </c>
+      <c r="D52" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E52" s="135"/>
+      <c r="F52" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="G52" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="H52" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="I52" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="J52" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="K52" s="136"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B53" s="136" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="136" t="s">
+        <v>540</v>
+      </c>
+      <c r="D53" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E53" s="135"/>
+      <c r="F53" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G53" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H53" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="J53" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K53" s="136"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B54" s="134" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="134" t="s">
+        <v>541</v>
+      </c>
+      <c r="D54" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E54" s="133"/>
+      <c r="F54" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G54" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H54" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I54" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="J54" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="K54" s="134"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B55" s="134" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" s="134" t="s">
+        <v>542</v>
+      </c>
+      <c r="D55" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E55" s="133"/>
+      <c r="F55" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G55" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H55" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I55" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="J55" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K55" s="134"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B56" s="134" t="n">
+        <v>22</v>
+      </c>
+      <c r="C56" s="134" t="s">
+        <v>543</v>
+      </c>
+      <c r="D56" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E56" s="133"/>
+      <c r="F56" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G56" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="H56" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I56" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="J56" s="134" t="s">
+        <v>544</v>
+      </c>
+      <c r="K56" s="134"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B57" s="134" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="134" t="s">
+        <v>545</v>
+      </c>
+      <c r="D57" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E57" s="133"/>
+      <c r="F57" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G57" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H57" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I57" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J57" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="K57" s="134"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B58" s="134" t="n">
+        <v>24</v>
+      </c>
+      <c r="C58" s="134" t="s">
+        <v>546</v>
+      </c>
+      <c r="D58" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E58" s="133"/>
+      <c r="F58" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G58" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H58" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I58" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="J58" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K58" s="134"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B59" s="136" t="n">
+        <v>25</v>
+      </c>
+      <c r="C59" s="136" t="s">
+        <v>547</v>
+      </c>
+      <c r="D59" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E59" s="135"/>
+      <c r="F59" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="G59" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="H59" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="J59" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="K59" s="136"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="135" t="s">
+        <v>521</v>
+      </c>
+      <c r="B60" s="136" t="n">
+        <v>26</v>
+      </c>
+      <c r="C60" s="136" t="s">
+        <v>548</v>
+      </c>
+      <c r="D60" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E60" s="135"/>
+      <c r="F60" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="G60" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="H60" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I60" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="J60" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="K60" s="136"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B61" s="134" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="134" t="s">
+        <v>549</v>
+      </c>
+      <c r="D61" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E61" s="133"/>
+      <c r="F61" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G61" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H61" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I61" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J61" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K61" s="134"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B62" s="134" t="n">
+        <v>28</v>
+      </c>
+      <c r="C62" s="134" t="s">
+        <v>550</v>
+      </c>
+      <c r="D62" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E62" s="133"/>
+      <c r="F62" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G62" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="H62" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I62" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="J62" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K62" s="134"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B63" s="134" t="n">
+        <v>29</v>
+      </c>
+      <c r="C63" s="134" t="s">
+        <v>551</v>
+      </c>
+      <c r="D63" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E63" s="133"/>
+      <c r="F63" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G63" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H63" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I63" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="J63" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="K63" s="134"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="133" t="s">
+        <v>521</v>
+      </c>
+      <c r="B64" s="134" t="n">
+        <v>30</v>
+      </c>
+      <c r="C64" s="134" t="s">
+        <v>552</v>
+      </c>
+      <c r="D64" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E64" s="133"/>
+      <c r="F64" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G64" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H64" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I64" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="J64" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="K64" s="134"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B65" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="136" t="s">
+        <v>554</v>
+      </c>
+      <c r="D65" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E65" s="135"/>
+      <c r="F65" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="G65" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="H65" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I65" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="J65" s="136"/>
+      <c r="K65" s="136"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B66" s="136" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="136" t="s">
+        <v>555</v>
+      </c>
+      <c r="D66" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E66" s="135"/>
+      <c r="F66" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="G66" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="H66" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="I66" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="J66" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="K66" s="136"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B67" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="134" t="s">
+        <v>556</v>
+      </c>
+      <c r="D67" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E67" s="133"/>
+      <c r="F67" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G67" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H67" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I67" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J67" s="134"/>
+      <c r="K67" s="134"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B68" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="134" t="s">
+        <v>557</v>
+      </c>
+      <c r="D68" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E68" s="133"/>
+      <c r="F68" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G68" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H68" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="I68" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J68" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K68" s="134"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B69" s="134" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" s="134" t="s">
+        <v>558</v>
+      </c>
+      <c r="D69" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E69" s="133"/>
+      <c r="F69" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G69" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H69" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I69" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="J69" s="134"/>
+      <c r="K69" s="134"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B70" s="134" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" s="134" t="s">
+        <v>559</v>
+      </c>
+      <c r="D70" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E70" s="133"/>
+      <c r="F70" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G70" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H70" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I70" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J70" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K70" s="134"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B71" s="134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" s="134" t="s">
+        <v>560</v>
+      </c>
+      <c r="D71" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E71" s="133"/>
+      <c r="F71" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="G71" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="H71" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="I71" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="J71" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K71" s="134"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B72" s="136" t="n">
+        <v>8</v>
+      </c>
+      <c r="C72" s="136" t="s">
+        <v>561</v>
+      </c>
+      <c r="D72" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E72" s="135"/>
+      <c r="F72" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G72" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="H72" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="I72" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="J72" s="136"/>
+      <c r="K72" s="136"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B73" s="136" t="n">
+        <v>9</v>
+      </c>
+      <c r="C73" s="136" t="s">
+        <v>562</v>
+      </c>
+      <c r="D73" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E73" s="135"/>
+      <c r="F73" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G73" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="H73" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="I73" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="J73" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="K73" s="136"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B74" s="134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" s="134" t="s">
+        <v>563</v>
+      </c>
+      <c r="D74" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E74" s="133"/>
+      <c r="F74" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G74" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H74" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I74" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="J74" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="K74" s="134"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B75" s="134" t="n">
+        <v>11</v>
+      </c>
+      <c r="C75" s="134" t="s">
+        <v>564</v>
+      </c>
+      <c r="D75" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E75" s="133"/>
+      <c r="F75" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G75" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H75" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I75" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="J75" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="K75" s="134"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B76" s="134" t="n">
+        <v>12</v>
+      </c>
+      <c r="C76" s="134" t="s">
+        <v>565</v>
+      </c>
+      <c r="D76" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E76" s="133"/>
+      <c r="F76" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G76" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H76" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="I76" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J76" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="K76" s="134"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B77" s="134" t="n">
+        <v>13</v>
+      </c>
+      <c r="C77" s="134" t="s">
+        <v>566</v>
+      </c>
+      <c r="D77" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E77" s="133"/>
+      <c r="F77" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G77" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H77" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="I77" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J77" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="K77" s="134"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B78" s="134" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" s="134" t="s">
+        <v>567</v>
+      </c>
+      <c r="D78" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E78" s="133"/>
+      <c r="F78" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G78" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H78" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I78" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="J78" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K78" s="134"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="137" t="s">
+        <v>553</v>
+      </c>
+      <c r="B79" s="138" t="n">
+        <v>15</v>
+      </c>
+      <c r="C79" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="D79" s="138" t="s">
+        <v>494</v>
+      </c>
+      <c r="E79" s="137" t="s">
+        <v>569</v>
+      </c>
+      <c r="F79" s="138" t="s">
+        <v>500</v>
+      </c>
+      <c r="G79" s="138" t="s">
+        <v>243</v>
+      </c>
+      <c r="H79" s="138" t="s">
+        <v>241</v>
+      </c>
+      <c r="I79" s="138" t="s">
+        <v>219</v>
+      </c>
+      <c r="J79" s="138"/>
+      <c r="K79" s="138"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B80" s="136" t="n">
+        <v>16</v>
+      </c>
+      <c r="C80" s="136" t="s">
+        <v>570</v>
+      </c>
+      <c r="D80" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E80" s="135"/>
+      <c r="F80" s="136" t="s">
+        <v>241</v>
+      </c>
+      <c r="G80" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="H80" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I80" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="J80" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="K80" s="136"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B81" s="134" t="n">
+        <v>17</v>
+      </c>
+      <c r="C81" s="134" t="s">
+        <v>571</v>
+      </c>
+      <c r="D81" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E81" s="133"/>
+      <c r="F81" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G81" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H81" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I81" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J81" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K81" s="134"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B82" s="134" t="n">
+        <v>18</v>
+      </c>
+      <c r="C82" s="134" t="s">
+        <v>572</v>
+      </c>
+      <c r="D82" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E82" s="133"/>
+      <c r="F82" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G82" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="H82" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I82" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="J82" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="K82" s="134"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B83" s="134" t="n">
+        <v>19</v>
+      </c>
+      <c r="C83" s="134" t="s">
+        <v>573</v>
+      </c>
+      <c r="D83" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E83" s="133"/>
+      <c r="F83" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G83" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="H83" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="I83" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J83" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K83" s="134"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B84" s="134" t="n">
+        <v>20</v>
+      </c>
+      <c r="C84" s="134" t="s">
+        <v>574</v>
+      </c>
+      <c r="D84" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E84" s="133"/>
+      <c r="F84" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G84" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H84" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I84" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="J84" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="K84" s="134"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B85" s="134" t="n">
+        <v>21</v>
+      </c>
+      <c r="C85" s="134" t="s">
+        <v>575</v>
+      </c>
+      <c r="D85" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E85" s="133"/>
+      <c r="F85" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G85" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H85" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I85" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="J85" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="K85" s="134"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B86" s="136" t="n">
+        <v>22</v>
+      </c>
+      <c r="C86" s="136" t="s">
+        <v>576</v>
+      </c>
+      <c r="D86" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E86" s="135"/>
+      <c r="F86" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="G86" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="H86" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I86" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="J86" s="136"/>
+      <c r="K86" s="136"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B87" s="136" t="n">
+        <v>23</v>
+      </c>
+      <c r="C87" s="136" t="s">
+        <v>577</v>
+      </c>
+      <c r="D87" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E87" s="135"/>
+      <c r="F87" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="G87" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="H87" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="I87" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="J87" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="K87" s="136"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B88" s="134" t="n">
+        <v>24</v>
+      </c>
+      <c r="C88" s="134" t="s">
+        <v>578</v>
+      </c>
+      <c r="D88" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E88" s="133"/>
+      <c r="F88" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="G88" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="H88" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I88" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="J88" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="K88" s="134"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B89" s="134" t="n">
+        <v>25</v>
+      </c>
+      <c r="C89" s="134" t="s">
+        <v>579</v>
+      </c>
+      <c r="D89" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E89" s="133"/>
+      <c r="F89" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G89" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H89" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="I89" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="J89" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K89" s="134"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B90" s="134" t="n">
+        <v>26</v>
+      </c>
+      <c r="C90" s="134" t="s">
+        <v>580</v>
+      </c>
+      <c r="D90" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E90" s="133"/>
+      <c r="F90" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G90" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H90" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="I90" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="J90" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K90" s="134"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B91" s="134" t="n">
+        <v>27</v>
+      </c>
+      <c r="C91" s="134" t="s">
+        <v>581</v>
+      </c>
+      <c r="D91" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E91" s="133"/>
+      <c r="F91" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G91" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="H91" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="I91" s="134" t="s">
+        <v>442</v>
+      </c>
+      <c r="J91" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K91" s="134"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B92" s="134" t="n">
+        <v>28</v>
+      </c>
+      <c r="C92" s="134" t="s">
+        <v>582</v>
+      </c>
+      <c r="D92" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E92" s="133"/>
+      <c r="F92" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G92" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H92" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I92" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J92" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="K92" s="134"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B93" s="136" t="n">
+        <v>29</v>
+      </c>
+      <c r="C93" s="136" t="s">
+        <v>583</v>
+      </c>
+      <c r="D93" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E93" s="135"/>
+      <c r="F93" s="136" t="s">
+        <v>235</v>
+      </c>
+      <c r="G93" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H93" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="I93" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="J93" s="136"/>
+      <c r="K93" s="136"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="135" t="s">
+        <v>553</v>
+      </c>
+      <c r="B94" s="136" t="n">
+        <v>30</v>
+      </c>
+      <c r="C94" s="136" t="s">
+        <v>584</v>
+      </c>
+      <c r="D94" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E94" s="135"/>
+      <c r="F94" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G94" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="H94" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I94" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="J94" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="K94" s="136"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="133" t="s">
+        <v>553</v>
+      </c>
+      <c r="B95" s="134" t="n">
+        <v>31</v>
+      </c>
+      <c r="C95" s="134" t="s">
+        <v>585</v>
+      </c>
+      <c r="D95" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E95" s="133"/>
+      <c r="F95" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G95" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="H95" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="I95" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="J95" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K95" s="134"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B96" s="134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="134" t="s">
+        <v>587</v>
+      </c>
+      <c r="D96" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E96" s="133"/>
+      <c r="F96" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G96" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H96" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I96" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="J96" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K96" s="134"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B97" s="134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="134" t="s">
+        <v>588</v>
+      </c>
+      <c r="D97" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E97" s="133"/>
+      <c r="F97" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G97" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="H97" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I97" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="J97" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="K97" s="134"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B98" s="134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="134" t="s">
+        <v>589</v>
+      </c>
+      <c r="D98" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E98" s="133"/>
+      <c r="F98" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G98" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="H98" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I98" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J98" s="134" t="s">
+        <v>191</v>
+      </c>
+      <c r="K98" s="134"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B99" s="134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" s="134" t="s">
+        <v>590</v>
+      </c>
+      <c r="D99" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E99" s="133"/>
+      <c r="F99" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G99" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H99" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="I99" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J99" s="134" t="s">
+        <v>194</v>
+      </c>
+      <c r="K99" s="134"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B100" s="136" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" s="136" t="s">
+        <v>591</v>
+      </c>
+      <c r="D100" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E100" s="135"/>
+      <c r="F100" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="G100" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="H100" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I100" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="J100" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="K100" s="136"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B101" s="136" t="n">
+        <v>6</v>
+      </c>
+      <c r="C101" s="136" t="s">
+        <v>592</v>
+      </c>
+      <c r="D101" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E101" s="135"/>
+      <c r="F101" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="G101" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="H101" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="I101" s="136" t="s">
+        <v>492</v>
+      </c>
+      <c r="J101" s="136" t="s">
+        <v>194</v>
+      </c>
+      <c r="K101" s="136"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B102" s="134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C102" s="134" t="s">
+        <v>593</v>
+      </c>
+      <c r="D102" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E102" s="133"/>
+      <c r="F102" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G102" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="H102" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I102" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="J102" s="134" t="s">
+        <v>196</v>
+      </c>
+      <c r="K102" s="134"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B103" s="134" t="n">
+        <v>8</v>
+      </c>
+      <c r="C103" s="134" t="s">
+        <v>594</v>
+      </c>
+      <c r="D103" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E103" s="133"/>
+      <c r="F103" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G103" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="H103" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I103" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J103" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="K103" s="134"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B104" s="134" t="n">
+        <v>9</v>
+      </c>
+      <c r="C104" s="134" t="s">
+        <v>595</v>
+      </c>
+      <c r="D104" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E104" s="133"/>
+      <c r="F104" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G104" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H104" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I104" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J104" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="K104" s="134"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B105" s="134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C105" s="134" t="s">
+        <v>596</v>
+      </c>
+      <c r="D105" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E105" s="133"/>
+      <c r="F105" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G105" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="H105" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I105" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="J105" s="134" t="s">
+        <v>196</v>
+      </c>
+      <c r="K105" s="134"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B106" s="134" t="n">
+        <v>11</v>
+      </c>
+      <c r="C106" s="134" t="s">
+        <v>597</v>
+      </c>
+      <c r="D106" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E106" s="133"/>
+      <c r="F106" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G106" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="H106" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I106" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="J106" s="134" t="s">
+        <v>207</v>
+      </c>
+      <c r="K106" s="134"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B107" s="136" t="n">
+        <v>12</v>
+      </c>
+      <c r="C107" s="136" t="s">
+        <v>598</v>
+      </c>
+      <c r="D107" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E107" s="135"/>
+      <c r="F107" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="G107" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="H107" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="I107" s="136" t="s">
+        <v>191</v>
+      </c>
+      <c r="J107" s="136" t="s">
+        <v>203</v>
+      </c>
+      <c r="K107" s="136"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B108" s="136" t="n">
+        <v>13</v>
+      </c>
+      <c r="C108" s="136" t="s">
+        <v>599</v>
+      </c>
+      <c r="D108" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E108" s="135"/>
+      <c r="F108" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="G108" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="H108" s="136" t="s">
+        <v>233</v>
+      </c>
+      <c r="I108" s="136" t="s">
+        <v>489</v>
+      </c>
+      <c r="J108" s="136" t="s">
+        <v>207</v>
+      </c>
+      <c r="K108" s="136"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B109" s="134" t="n">
+        <v>14</v>
+      </c>
+      <c r="C109" s="134" t="s">
+        <v>600</v>
+      </c>
+      <c r="D109" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E109" s="133"/>
+      <c r="F109" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G109" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="H109" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="I109" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J109" s="134" t="s">
+        <v>205</v>
+      </c>
+      <c r="K109" s="134"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B110" s="134" t="n">
+        <v>15</v>
+      </c>
+      <c r="C110" s="134" t="s">
+        <v>601</v>
+      </c>
+      <c r="D110" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E110" s="133"/>
+      <c r="F110" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G110" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="H110" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I110" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J110" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="K110" s="134"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B111" s="134" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" s="134" t="s">
+        <v>602</v>
+      </c>
+      <c r="D111" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E111" s="133"/>
+      <c r="F111" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G111" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="H111" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I111" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="J111" s="134" t="s">
+        <v>201</v>
+      </c>
+      <c r="K111" s="134"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B112" s="134" t="n">
+        <v>17</v>
+      </c>
+      <c r="C112" s="134" t="s">
+        <v>603</v>
+      </c>
+      <c r="D112" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E112" s="133"/>
+      <c r="F112" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G112" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="H112" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="I112" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J112" s="134" t="s">
+        <v>194</v>
+      </c>
+      <c r="K112" s="134"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B113" s="134" t="n">
+        <v>18</v>
+      </c>
+      <c r="C113" s="134" t="s">
+        <v>604</v>
+      </c>
+      <c r="D113" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E113" s="133"/>
+      <c r="F113" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="G113" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="H113" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="I113" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="J113" s="134" t="s">
+        <v>544</v>
+      </c>
+      <c r="K113" s="134"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B114" s="136" t="n">
+        <v>19</v>
+      </c>
+      <c r="C114" s="136" t="s">
+        <v>605</v>
+      </c>
+      <c r="D114" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E114" s="135"/>
+      <c r="F114" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G114" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="H114" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="I114" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="J114" s="136" t="s">
+        <v>196</v>
+      </c>
+      <c r="K114" s="136"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B115" s="136" t="n">
+        <v>20</v>
+      </c>
+      <c r="C115" s="136" t="s">
+        <v>606</v>
+      </c>
+      <c r="D115" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E115" s="135"/>
+      <c r="F115" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="G115" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="H115" s="136" t="s">
+        <v>229</v>
+      </c>
+      <c r="I115" s="136" t="s">
+        <v>221</v>
+      </c>
+      <c r="J115" s="136" t="s">
+        <v>544</v>
+      </c>
+      <c r="K115" s="136"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B116" s="134" t="n">
+        <v>21</v>
+      </c>
+      <c r="C116" s="134" t="s">
+        <v>607</v>
+      </c>
+      <c r="D116" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E116" s="133"/>
+      <c r="F116" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="G116" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="H116" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I116" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J116" s="134" t="s">
+        <v>203</v>
+      </c>
+      <c r="K116" s="134"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B117" s="134" t="n">
+        <v>22</v>
+      </c>
+      <c r="C117" s="134" t="s">
+        <v>608</v>
+      </c>
+      <c r="D117" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E117" s="133"/>
+      <c r="F117" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G117" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H117" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="I117" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J117" s="134" t="s">
+        <v>191</v>
+      </c>
+      <c r="K117" s="134"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B118" s="134" t="n">
+        <v>23</v>
+      </c>
+      <c r="C118" s="134" t="s">
+        <v>609</v>
+      </c>
+      <c r="D118" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E118" s="133"/>
+      <c r="F118" s="134" t="s">
+        <v>500</v>
+      </c>
+      <c r="G118" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="H118" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I118" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="J118" s="134" t="s">
+        <v>196</v>
+      </c>
+      <c r="K118" s="134"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B119" s="134" t="n">
+        <v>24</v>
+      </c>
+      <c r="C119" s="134" t="s">
+        <v>610</v>
+      </c>
+      <c r="D119" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="E119" s="133"/>
+      <c r="F119" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G119" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="H119" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I119" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="J119" s="134" t="s">
+        <v>203</v>
+      </c>
+      <c r="K119" s="134"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B120" s="134" t="n">
+        <v>25</v>
+      </c>
+      <c r="C120" s="134" t="s">
+        <v>611</v>
+      </c>
+      <c r="D120" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="E120" s="133"/>
+      <c r="F120" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G120" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="H120" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="I120" s="134" t="s">
+        <v>205</v>
+      </c>
+      <c r="J120" s="134" t="s">
+        <v>201</v>
+      </c>
+      <c r="K120" s="134"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B121" s="136" t="n">
+        <v>26</v>
+      </c>
+      <c r="C121" s="136" t="s">
+        <v>612</v>
+      </c>
+      <c r="D121" s="136" t="s">
+        <v>494</v>
+      </c>
+      <c r="E121" s="135"/>
+      <c r="F121" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="G121" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="H121" s="136" t="s">
+        <v>481</v>
+      </c>
+      <c r="I121" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="J121" s="136" t="s">
+        <v>225</v>
+      </c>
+      <c r="K121" s="136"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="135" t="s">
+        <v>586</v>
+      </c>
+      <c r="B122" s="136" t="n">
+        <v>27</v>
+      </c>
+      <c r="C122" s="136" t="s">
+        <v>613</v>
+      </c>
+      <c r="D122" s="136" t="s">
+        <v>496</v>
+      </c>
+      <c r="E122" s="135"/>
+      <c r="F122" s="136" t="s">
+        <v>243</v>
+      </c>
+      <c r="G122" s="136" t="s">
+        <v>219</v>
+      </c>
+      <c r="H122" s="136" t="s">
+        <v>484</v>
+      </c>
+      <c r="I122" s="136" t="s">
+        <v>205</v>
+      </c>
+      <c r="J122" s="136" t="s">
+        <v>201</v>
+      </c>
+      <c r="K122" s="136"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B123" s="134" t="n">
+        <v>28</v>
+      </c>
+      <c r="C123" s="134" t="s">
+        <v>614</v>
+      </c>
+      <c r="D123" s="134" t="s">
+        <v>480</v>
+      </c>
+      <c r="E123" s="133"/>
+      <c r="F123" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G123" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="H123" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="I123" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="J123" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="K123" s="134"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B124" s="134" t="n">
+        <v>29</v>
+      </c>
+      <c r="C124" s="134" t="s">
+        <v>615</v>
+      </c>
+      <c r="D124" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E124" s="133"/>
+      <c r="F124" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G124" s="134" t="s">
+        <v>209</v>
+      </c>
+      <c r="H124" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="I124" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="J124" s="134" t="s">
+        <v>207</v>
+      </c>
+      <c r="K124" s="134"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="B125" s="134" t="n">
+        <v>30</v>
+      </c>
+      <c r="C125" s="134" t="s">
+        <v>616</v>
+      </c>
+      <c r="D125" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="E125" s="133"/>
+      <c r="F125" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="G125" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="H125" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="I125" s="134" t="s">
+        <v>492</v>
+      </c>
+      <c r="J125" s="134" t="s">
+        <v>544</v>
+      </c>
+      <c r="K125" s="134"/>
+    </row>
+    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="131" t="s">
+        <v>617</v>
+      </c>
+      <c r="B504" s="131"/>
+      <c r="C504" s="131"/>
+      <c r="D504" s="131"/>
+      <c r="E504" s="131"/>
+      <c r="F504" s="131"/>
+      <c r="G504" s="131"/>
+      <c r="H504" s="131"/>
+      <c r="I504" s="131"/>
+      <c r="J504" s="131"/>
+      <c r="K504" s="131"/>
+      <c r="L504" s="131"/>
+    </row>
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="131" t="s">
+        <v>428</v>
+      </c>
+      <c r="B505" s="131" t="s">
+        <v>176</v>
+      </c>
+      <c r="C505" s="131" t="s">
+        <v>429</v>
+      </c>
+      <c r="D505" s="131" t="s">
+        <v>618</v>
+      </c>
+      <c r="E505" s="131" t="s">
+        <v>619</v>
+      </c>
+      <c r="F505" s="131" t="s">
+        <v>620</v>
+      </c>
+      <c r="G505" s="131" t="s">
+        <v>621</v>
+      </c>
+      <c r="H505" s="131" t="s">
+        <v>622</v>
+      </c>
+      <c r="I505" s="131" t="s">
+        <v>623</v>
+      </c>
+      <c r="J505" s="131" t="s">
+        <v>624</v>
+      </c>
+      <c r="K505" s="131" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A506" s="139" t="s">
+        <v>191</v>
+      </c>
+      <c r="B506" s="140" t="s">
+        <v>192</v>
+      </c>
+      <c r="C506" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D506" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
+        <v>0</v>
+      </c>
+      <c r="E506" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
+        <v>1</v>
+      </c>
+      <c r="F506" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
+        <v>0</v>
+      </c>
+      <c r="G506" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Rosario")</f>
+        <v>0</v>
+      </c>
+      <c r="H506" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Rosario")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I506" s="140" t="n">
+        <f aca="false">G506-H506</f>
+        <v>0</v>
+      </c>
+      <c r="J506" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
+        <v>0</v>
+      </c>
+      <c r="K506" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Rosario")+COUNTIF($G$5:$G$500,"Rosario")+COUNTIF($H$5:$H$500,"Rosario")+COUNTIF($I$5:$I$500,"Rosario")+COUNTIF($J$5:$J$500,"Rosario")+COUNTIF($K$5:$K$500,"Rosario")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A507" s="139" t="s">
+        <v>194</v>
+      </c>
+      <c r="B507" s="140" t="s">
+        <v>195</v>
+      </c>
+      <c r="C507" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D507" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
+        <v>1</v>
+      </c>
+      <c r="E507" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
+        <v>0</v>
+      </c>
+      <c r="F507" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
+        <v>1</v>
+      </c>
+      <c r="G507" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Cristina")</f>
+        <v>0</v>
+      </c>
+      <c r="H507" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Cristina")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I507" s="140" t="n">
+        <f aca="false">G507-H507</f>
+        <v>0</v>
+      </c>
+      <c r="J507" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
+        <v>0</v>
+      </c>
+      <c r="K507" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Cristina")+COUNTIF($G$5:$G$500,"Cristina")+COUNTIF($H$5:$H$500,"Cristina")+COUNTIF($I$5:$I$500,"Cristina")+COUNTIF($J$5:$J$500,"Cristina")+COUNTIF($K$5:$K$500,"Cristina")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A508" s="139" t="s">
+        <v>196</v>
+      </c>
+      <c r="B508" s="140" t="s">
+        <v>197</v>
+      </c>
+      <c r="C508" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D508" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
+        <v>0</v>
+      </c>
+      <c r="E508" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
+        <v>1</v>
+      </c>
+      <c r="F508" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
+        <v>0</v>
+      </c>
+      <c r="G508" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Miriam")</f>
+        <v>0</v>
+      </c>
+      <c r="H508" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Miriam")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I508" s="140" t="n">
+        <f aca="false">G508-H508</f>
+        <v>0</v>
+      </c>
+      <c r="J508" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
+        <v>0</v>
+      </c>
+      <c r="K508" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Miriam")+COUNTIF($G$5:$G$500,"Miriam")+COUNTIF($H$5:$H$500,"Miriam")+COUNTIF($I$5:$I$500,"Miriam")+COUNTIF($J$5:$J$500,"Miriam")+COUNTIF($K$5:$K$500,"Miriam")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="139" t="s">
+        <v>199</v>
+      </c>
+      <c r="B509" s="140" t="s">
+        <v>200</v>
+      </c>
+      <c r="C509" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D509" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
+        <v>0</v>
+      </c>
+      <c r="E509" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
+        <v>0</v>
+      </c>
+      <c r="F509" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
+        <v>0</v>
+      </c>
+      <c r="G509" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"David")</f>
+        <v>0</v>
+      </c>
+      <c r="H509" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="David")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I509" s="140" t="n">
+        <f aca="false">G509-H509</f>
+        <v>0</v>
+      </c>
+      <c r="J509" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
+        <v>0</v>
+      </c>
+      <c r="K509" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"David")+COUNTIF($G$5:$G$500,"David")+COUNTIF($H$5:$H$500,"David")+COUNTIF($I$5:$I$500,"David")+COUNTIF($J$5:$J$500,"David")+COUNTIF($K$5:$K$500,"David")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="139" t="s">
+        <v>201</v>
+      </c>
+      <c r="B510" s="140" t="s">
+        <v>202</v>
+      </c>
+      <c r="C510" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D510" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
+        <v>1</v>
+      </c>
+      <c r="E510" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
+        <v>0</v>
+      </c>
+      <c r="F510" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
+        <v>1</v>
+      </c>
+      <c r="G510" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Mercedes")</f>
+        <v>0</v>
+      </c>
+      <c r="H510" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Mercedes")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I510" s="140" t="n">
+        <f aca="false">G510-H510</f>
+        <v>0</v>
+      </c>
+      <c r="J510" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
+        <v>0</v>
+      </c>
+      <c r="K510" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Mercedes")+COUNTIF($G$5:$G$500,"Mercedes")+COUNTIF($H$5:$H$500,"Mercedes")+COUNTIF($I$5:$I$500,"Mercedes")+COUNTIF($J$5:$J$500,"Mercedes")+COUNTIF($K$5:$K$500,"Mercedes")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A511" s="139" t="s">
+        <v>203</v>
+      </c>
+      <c r="B511" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="C511" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D511" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
+        <v>0</v>
+      </c>
+      <c r="E511" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
+        <v>1</v>
+      </c>
+      <c r="F511" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
+        <v>0</v>
+      </c>
+      <c r="G511" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Arturo")</f>
+        <v>0</v>
+      </c>
+      <c r="H511" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Arturo")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I511" s="140" t="n">
+        <f aca="false">G511-H511</f>
+        <v>0</v>
+      </c>
+      <c r="J511" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
+        <v>0</v>
+      </c>
+      <c r="K511" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Arturo")+COUNTIF($G$5:$G$500,"Arturo")+COUNTIF($H$5:$H$500,"Arturo")+COUNTIF($I$5:$I$500,"Arturo")+COUNTIF($J$5:$J$500,"Arturo")+COUNTIF($K$5:$K$500,"Arturo")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A512" s="139" t="s">
+        <v>205</v>
+      </c>
+      <c r="B512" s="140" t="s">
+        <v>206</v>
+      </c>
+      <c r="C512" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D512" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
+        <v>1</v>
+      </c>
+      <c r="E512" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
+        <v>0</v>
+      </c>
+      <c r="F512" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
+        <v>1</v>
+      </c>
+      <c r="G512" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Aitor")</f>
+        <v>0</v>
+      </c>
+      <c r="H512" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Aitor")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I512" s="140" t="n">
+        <f aca="false">G512-H512</f>
+        <v>0</v>
+      </c>
+      <c r="J512" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
+        <v>0</v>
+      </c>
+      <c r="K512" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Aitor")+COUNTIF($G$5:$G$500,"Aitor")+COUNTIF($H$5:$H$500,"Aitor")+COUNTIF($I$5:$I$500,"Aitor")+COUNTIF($J$5:$J$500,"Aitor")+COUNTIF($K$5:$K$500,"Aitor")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A513" s="139" t="s">
+        <v>626</v>
+      </c>
+      <c r="B513" s="140" t="s">
+        <v>208</v>
+      </c>
+      <c r="C513" s="140" t="s">
+        <v>433</v>
+      </c>
+      <c r="D513" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
+        <v>1</v>
+      </c>
+      <c r="E513" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
+        <v>0</v>
+      </c>
+      <c r="F513" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
+        <v>1</v>
+      </c>
+      <c r="G513" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Fatima")</f>
+        <v>0</v>
+      </c>
+      <c r="H513" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Fatima")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I513" s="140" t="n">
+        <f aca="false">G513-H513</f>
+        <v>0</v>
+      </c>
+      <c r="J513" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
+        <v>0</v>
+      </c>
+      <c r="K513" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Fatima")+COUNTIF($G$5:$G$500,"Fatima")+COUNTIF($H$5:$H$500,"Fatima")+COUNTIF($I$5:$I$500,"Fatima")+COUNTIF($J$5:$J$500,"Fatima")+COUNTIF($K$5:$K$500,"Fatima")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="139" t="s">
+        <v>209</v>
+      </c>
+      <c r="B514" s="140" t="s">
+        <v>210</v>
+      </c>
+      <c r="C514" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D514" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
+        <v>3</v>
+      </c>
+      <c r="E514" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
+        <v>3</v>
+      </c>
+      <c r="F514" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
+        <v>3</v>
+      </c>
+      <c r="G514" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Tania")</f>
+        <v>0</v>
+      </c>
+      <c r="H514" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Tania")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I514" s="140" t="n">
+        <f aca="false">G514-H514</f>
+        <v>0</v>
+      </c>
+      <c r="J514" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
+        <v>0</v>
+      </c>
+      <c r="K514" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Tania")+COUNTIF($G$5:$G$500,"Tania")+COUNTIF($H$5:$H$500,"Tania")+COUNTIF($I$5:$I$500,"Tania")+COUNTIF($J$5:$J$500,"Tania")+COUNTIF($K$5:$K$500,"Tania")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="139" t="s">
+        <v>627</v>
+      </c>
+      <c r="B515" s="140" t="s">
+        <v>213</v>
+      </c>
+      <c r="C515" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D515" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
+        <v>5</v>
+      </c>
+      <c r="E515" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
+        <v>4</v>
+      </c>
+      <c r="F515" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
+        <v>5</v>
+      </c>
+      <c r="G515" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Asis")</f>
+        <v>0</v>
+      </c>
+      <c r="H515" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Asis")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I515" s="140" t="n">
+        <f aca="false">G515-H515</f>
+        <v>0</v>
+      </c>
+      <c r="J515" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
+        <v>0</v>
+      </c>
+      <c r="K515" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Asis")+COUNTIF($G$5:$G$500,"Asis")+COUNTIF($H$5:$H$500,"Asis")+COUNTIF($I$5:$I$500,"Asis")+COUNTIF($J$5:$J$500,"Asis")+COUNTIF($K$5:$K$500,"Asis")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="139" t="s">
+        <v>628</v>
+      </c>
+      <c r="B516" s="140" t="s">
+        <v>216</v>
+      </c>
+      <c r="C516" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D516" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
+        <v>4</v>
+      </c>
+      <c r="E516" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
+        <v>3</v>
+      </c>
+      <c r="F516" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
+        <v>3</v>
+      </c>
+      <c r="G516" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"PatriciaR2")</f>
+        <v>0</v>
+      </c>
+      <c r="H516" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="PatriciaR2")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I516" s="140" t="n">
+        <f aca="false">G516-H516</f>
+        <v>0</v>
+      </c>
+      <c r="J516" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
+        <v>0</v>
+      </c>
+      <c r="K516" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"PatriciaR2")+COUNTIF($G$5:$G$500,"PatriciaR2")+COUNTIF($H$5:$H$500,"PatriciaR2")+COUNTIF($I$5:$I$500,"PatriciaR2")+COUNTIF($J$5:$J$500,"PatriciaR2")+COUNTIF($K$5:$K$500,"PatriciaR2")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="139" t="s">
+        <v>217</v>
+      </c>
+      <c r="B517" s="140" t="s">
+        <v>218</v>
+      </c>
+      <c r="C517" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D517" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
+        <v>2</v>
+      </c>
+      <c r="E517" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
+        <v>5</v>
+      </c>
+      <c r="F517" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
+        <v>3</v>
+      </c>
+      <c r="G517" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Eva")</f>
+        <v>0</v>
+      </c>
+      <c r="H517" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Eva")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I517" s="140" t="n">
+        <f aca="false">G517-H517</f>
+        <v>0</v>
+      </c>
+      <c r="J517" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
+        <v>0</v>
+      </c>
+      <c r="K517" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Eva")+COUNTIF($G$5:$G$500,"Eva")+COUNTIF($H$5:$H$500,"Eva")+COUNTIF($I$5:$I$500,"Eva")+COUNTIF($J$5:$J$500,"Eva")+COUNTIF($K$5:$K$500,"Eva")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A518" s="139" t="s">
+        <v>219</v>
+      </c>
+      <c r="B518" s="140" t="s">
+        <v>220</v>
+      </c>
+      <c r="C518" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D518" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
+        <v>4</v>
+      </c>
+      <c r="E518" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
+        <v>3</v>
+      </c>
+      <c r="F518" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
+        <v>4</v>
+      </c>
+      <c r="G518" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Emilio")</f>
+        <v>0</v>
+      </c>
+      <c r="H518" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Emilio")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I518" s="140" t="n">
+        <f aca="false">G518-H518</f>
+        <v>0</v>
+      </c>
+      <c r="J518" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
+        <v>1</v>
+      </c>
+      <c r="K518" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Emilio")+COUNTIF($G$5:$G$500,"Emilio")+COUNTIF($H$5:$H$500,"Emilio")+COUNTIF($I$5:$I$500,"Emilio")+COUNTIF($J$5:$J$500,"Emilio")+COUNTIF($K$5:$K$500,"Emilio")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A519" s="139" t="s">
+        <v>221</v>
+      </c>
+      <c r="B519" s="140" t="s">
+        <v>222</v>
+      </c>
+      <c r="C519" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D519" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
+        <v>4</v>
+      </c>
+      <c r="E519" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
+        <v>4</v>
+      </c>
+      <c r="F519" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
+        <v>4</v>
+      </c>
+      <c r="G519" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Antonio")</f>
+        <v>0</v>
+      </c>
+      <c r="H519" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Antonio")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I519" s="140" t="n">
+        <f aca="false">G519-H519</f>
+        <v>0</v>
+      </c>
+      <c r="J519" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
+        <v>0</v>
+      </c>
+      <c r="K519" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Antonio")+COUNTIF($G$5:$G$500,"Antonio")+COUNTIF($H$5:$H$500,"Antonio")+COUNTIF($I$5:$I$500,"Antonio")+COUNTIF($J$5:$J$500,"Antonio")+COUNTIF($K$5:$K$500,"Antonio")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A520" s="139" t="s">
+        <v>629</v>
+      </c>
+      <c r="B520" s="140" t="s">
+        <v>224</v>
+      </c>
+      <c r="C520" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D520" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
+        <v>4</v>
+      </c>
+      <c r="E520" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
+        <v>3</v>
+      </c>
+      <c r="F520" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
+        <v>5</v>
+      </c>
+      <c r="G520" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"AnaR2")</f>
+        <v>0</v>
+      </c>
+      <c r="H520" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="AnaR2")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I520" s="140" t="n">
+        <f aca="false">G520-H520</f>
+        <v>0</v>
+      </c>
+      <c r="J520" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
+        <v>0</v>
+      </c>
+      <c r="K520" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"AnaR2")+COUNTIF($G$5:$G$500,"AnaR2")+COUNTIF($H$5:$H$500,"AnaR2")+COUNTIF($I$5:$I$500,"AnaR2")+COUNTIF($J$5:$J$500,"AnaR2")+COUNTIF($K$5:$K$500,"AnaR2")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A521" s="139" t="s">
+        <v>225</v>
+      </c>
+      <c r="B521" s="140" t="s">
+        <v>226</v>
+      </c>
+      <c r="C521" s="140" t="s">
+        <v>435</v>
+      </c>
+      <c r="D521" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
+        <v>2</v>
+      </c>
+      <c r="E521" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
+        <v>5</v>
+      </c>
+      <c r="F521" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
+        <v>4</v>
+      </c>
+      <c r="G521" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Marc")</f>
+        <v>0</v>
+      </c>
+      <c r="H521" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Marc")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I521" s="140" t="n">
+        <f aca="false">G521-H521</f>
+        <v>0</v>
+      </c>
+      <c r="J521" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
+        <v>0</v>
+      </c>
+      <c r="K521" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Marc")+COUNTIF($G$5:$G$500,"Marc")+COUNTIF($H$5:$H$500,"Marc")+COUNTIF($I$5:$I$500,"Marc")+COUNTIF($J$5:$J$500,"Marc")+COUNTIF($K$5:$K$500,"Marc")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A522" s="139" t="s">
+        <v>630</v>
+      </c>
+      <c r="B522" s="140" t="s">
+        <v>228</v>
+      </c>
+      <c r="C522" s="140" t="s">
+        <v>436</v>
+      </c>
+      <c r="D522" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
+        <v>5</v>
+      </c>
+      <c r="E522" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
+        <v>3</v>
+      </c>
+      <c r="F522" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
+        <v>3</v>
+      </c>
+      <c r="G522" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"PatriciaR3")</f>
+        <v>1</v>
+      </c>
+      <c r="H522" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="PatriciaR3")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>1</v>
+      </c>
+      <c r="I522" s="140" t="n">
+        <f aca="false">G522-H522</f>
+        <v>0</v>
+      </c>
+      <c r="J522" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
+        <v>0</v>
+      </c>
+      <c r="K522" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"PatriciaR3")+COUNTIF($G$5:$G$500,"PatriciaR3")+COUNTIF($H$5:$H$500,"PatriciaR3")+COUNTIF($I$5:$I$500,"PatriciaR3")+COUNTIF($J$5:$J$500,"PatriciaR3")+COUNTIF($K$5:$K$500,"PatriciaR3")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A523" s="139" t="s">
+        <v>229</v>
+      </c>
+      <c r="B523" s="140" t="s">
+        <v>230</v>
+      </c>
+      <c r="C523" s="140" t="s">
+        <v>436</v>
+      </c>
+      <c r="D523" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
+        <v>5</v>
+      </c>
+      <c r="E523" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
+        <v>2</v>
+      </c>
+      <c r="F523" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
+        <v>5</v>
+      </c>
+      <c r="G523" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Candela")</f>
+        <v>0</v>
+      </c>
+      <c r="H523" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Candela")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I523" s="140" t="n">
+        <f aca="false">G523-H523</f>
+        <v>0</v>
+      </c>
+      <c r="J523" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
+        <v>0</v>
+      </c>
+      <c r="K523" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Candela")+COUNTIF($G$5:$G$500,"Candela")+COUNTIF($H$5:$H$500,"Candela")+COUNTIF($I$5:$I$500,"Candela")+COUNTIF($J$5:$J$500,"Candela")+COUNTIF($K$5:$K$500,"Candela")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A524" s="139" t="s">
+        <v>631</v>
+      </c>
+      <c r="B524" s="140" t="s">
+        <v>232</v>
+      </c>
+      <c r="C524" s="140" t="s">
+        <v>436</v>
+      </c>
+      <c r="D524" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
+        <v>2</v>
+      </c>
+      <c r="E524" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
+        <v>4</v>
+      </c>
+      <c r="F524" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
+        <v>3</v>
+      </c>
+      <c r="G524" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Fabian")</f>
+        <v>0</v>
+      </c>
+      <c r="H524" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Fabian")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I524" s="140" t="n">
+        <f aca="false">G524-H524</f>
+        <v>0</v>
+      </c>
+      <c r="J524" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
+        <v>0</v>
+      </c>
+      <c r="K524" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Fabian")+COUNTIF($G$5:$G$500,"Fabian")+COUNTIF($H$5:$H$500,"Fabian")+COUNTIF($I$5:$I$500,"Fabian")+COUNTIF($J$5:$J$500,"Fabian")+COUNTIF($K$5:$K$500,"Fabian")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A525" s="139" t="s">
+        <v>233</v>
+      </c>
+      <c r="B525" s="140" t="s">
+        <v>234</v>
+      </c>
+      <c r="C525" s="140" t="s">
+        <v>436</v>
+      </c>
+      <c r="D525" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
+        <v>4</v>
+      </c>
+      <c r="E525" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
+        <v>5</v>
+      </c>
+      <c r="F525" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
+        <v>4</v>
+      </c>
+      <c r="G525" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Tony")</f>
+        <v>0</v>
+      </c>
+      <c r="H525" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Tony")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I525" s="140" t="n">
+        <f aca="false">G525-H525</f>
+        <v>0</v>
+      </c>
+      <c r="J525" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
+        <v>0</v>
+      </c>
+      <c r="K525" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Tony")+COUNTIF($G$5:$G$500,"Tony")+COUNTIF($H$5:$H$500,"Tony")+COUNTIF($I$5:$I$500,"Tony")+COUNTIF($J$5:$J$500,"Tony")+COUNTIF($K$5:$K$500,"Tony")</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A526" s="139" t="s">
+        <v>235</v>
+      </c>
+      <c r="B526" s="140" t="s">
+        <v>236</v>
+      </c>
+      <c r="C526" s="140" t="s">
+        <v>437</v>
+      </c>
+      <c r="D526" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
+        <v>5</v>
+      </c>
+      <c r="E526" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
+        <v>4</v>
+      </c>
+      <c r="F526" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
+        <v>4</v>
+      </c>
+      <c r="G526" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Carlota")</f>
+        <v>15</v>
+      </c>
+      <c r="H526" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Carlota")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>6</v>
+      </c>
+      <c r="I526" s="140" t="n">
+        <f aca="false">G526-H526</f>
+        <v>9</v>
+      </c>
+      <c r="J526" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
+        <v>0</v>
+      </c>
+      <c r="K526" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Carlota")+COUNTIF($G$5:$G$500,"Carlota")+COUNTIF($H$5:$H$500,"Carlota")+COUNTIF($I$5:$I$500,"Carlota")+COUNTIF($J$5:$J$500,"Carlota")+COUNTIF($K$5:$K$500,"Carlota")</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A527" s="139" t="s">
+        <v>237</v>
+      </c>
+      <c r="B527" s="140" t="s">
+        <v>238</v>
+      </c>
+      <c r="C527" s="140" t="s">
+        <v>437</v>
+      </c>
+      <c r="D527" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
+        <v>4</v>
+      </c>
+      <c r="E527" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
+        <v>6</v>
+      </c>
+      <c r="F527" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
+        <v>6</v>
+      </c>
+      <c r="G527" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Almudena")</f>
+        <v>21</v>
+      </c>
+      <c r="H527" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Almudena")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>6</v>
+      </c>
+      <c r="I527" s="140" t="n">
+        <f aca="false">G527-H527</f>
+        <v>15</v>
+      </c>
+      <c r="J527" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
+        <v>0</v>
+      </c>
+      <c r="K527" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Almudena")+COUNTIF($G$5:$G$500,"Almudena")+COUNTIF($H$5:$H$500,"Almudena")+COUNTIF($I$5:$I$500,"Almudena")+COUNTIF($J$5:$J$500,"Almudena")+COUNTIF($K$5:$K$500,"Almudena")</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A528" s="139" t="s">
+        <v>632</v>
+      </c>
+      <c r="B528" s="140" t="s">
+        <v>240</v>
+      </c>
+      <c r="C528" s="140" t="s">
+        <v>437</v>
+      </c>
+      <c r="D528" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
+        <v>4</v>
+      </c>
+      <c r="E528" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
+        <v>3</v>
+      </c>
+      <c r="F528" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
+        <v>3</v>
+      </c>
+      <c r="G528" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"AnaR4")</f>
+        <v>16</v>
+      </c>
+      <c r="H528" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="AnaR4")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>5</v>
+      </c>
+      <c r="I528" s="140" t="n">
+        <f aca="false">G528-H528</f>
+        <v>11</v>
+      </c>
+      <c r="J528" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
+        <v>1</v>
+      </c>
+      <c r="K528" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"AnaR4")+COUNTIF($G$5:$G$500,"AnaR4")+COUNTIF($H$5:$H$500,"AnaR4")+COUNTIF($I$5:$I$500,"AnaR4")+COUNTIF($J$5:$J$500,"AnaR4")+COUNTIF($K$5:$K$500,"AnaR4")</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A529" s="139" t="s">
+        <v>241</v>
+      </c>
+      <c r="B529" s="140" t="s">
+        <v>242</v>
+      </c>
+      <c r="C529" s="140" t="s">
+        <v>437</v>
+      </c>
+      <c r="D529" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
+        <v>5</v>
+      </c>
+      <c r="E529" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
+        <v>4</v>
+      </c>
+      <c r="F529" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
+        <v>7</v>
+      </c>
+      <c r="G529" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Sandra")</f>
+        <v>15</v>
+      </c>
+      <c r="H529" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Sandra")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>9</v>
+      </c>
+      <c r="I529" s="140" t="n">
+        <f aca="false">G529-H529</f>
+        <v>6</v>
+      </c>
+      <c r="J529" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
+        <v>1</v>
+      </c>
+      <c r="K529" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Sandra")+COUNTIF($G$5:$G$500,"Sandra")+COUNTIF($H$5:$H$500,"Sandra")+COUNTIF($I$5:$I$500,"Sandra")+COUNTIF($J$5:$J$500,"Sandra")+COUNTIF($K$5:$K$500,"Sandra")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="B530" s="140" t="s">
+        <v>244</v>
+      </c>
+      <c r="C530" s="140" t="s">
+        <v>437</v>
+      </c>
+      <c r="D530" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
+        <v>4</v>
+      </c>
+      <c r="E530" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
+        <v>8</v>
+      </c>
+      <c r="F530" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
+        <v>5</v>
+      </c>
+      <c r="G530" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Isa")</f>
+        <v>21</v>
+      </c>
+      <c r="H530" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Isa")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>8</v>
+      </c>
+      <c r="I530" s="140" t="n">
+        <f aca="false">G530-H530</f>
+        <v>13</v>
+      </c>
+      <c r="J530" s="140" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
+        <v>1</v>
+      </c>
+      <c r="K530" s="140" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Isa")+COUNTIF($G$5:$G$500,"Isa")+COUNTIF($H$5:$H$500,"Isa")+COUNTIF($I$5:$I$500,"Isa")+COUNTIF($J$5:$J$500,"Isa")+COUNTIF($K$5:$K$500,"Isa")</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A531" s="141" t="s">
+        <v>440</v>
+      </c>
+      <c r="B531" s="142" t="s">
+        <v>633</v>
+      </c>
+      <c r="C531" s="142" t="s">
+        <v>437</v>
+      </c>
+      <c r="D531" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
+        <v>6</v>
+      </c>
+      <c r="E531" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
+        <v>4</v>
+      </c>
+      <c r="F531" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
+        <v>7</v>
+      </c>
+      <c r="G531" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Maria")</f>
+        <v>20</v>
+      </c>
+      <c r="H531" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Maria")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>9</v>
+      </c>
+      <c r="I531" s="142" t="n">
+        <f aca="false">G531-H531</f>
+        <v>11</v>
+      </c>
+      <c r="J531" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
+        <v>0</v>
+      </c>
+      <c r="K531" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Maria")+COUNTIF($G$5:$G$500,"Maria")+COUNTIF($H$5:$H$500,"Maria")+COUNTIF($I$5:$I$500,"Maria")+COUNTIF($J$5:$J$500,"Maria")+COUNTIF($K$5:$K$500,"Maria")</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="141" t="s">
+        <v>442</v>
+      </c>
+      <c r="B532" s="142" t="s">
+        <v>633</v>
+      </c>
+      <c r="C532" s="142" t="s">
+        <v>437</v>
+      </c>
+      <c r="D532" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
+        <v>3</v>
+      </c>
+      <c r="E532" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
+        <v>4</v>
+      </c>
+      <c r="F532" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
+        <v>2</v>
+      </c>
+      <c r="G532" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Gerard")</f>
+        <v>12</v>
+      </c>
+      <c r="H532" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="Gerard")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>6</v>
+      </c>
+      <c r="I532" s="142" t="n">
+        <f aca="false">G532-H532</f>
+        <v>6</v>
+      </c>
+      <c r="J532" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
+        <v>0</v>
+      </c>
+      <c r="K532" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"Gerard")+COUNTIF($G$5:$G$500,"Gerard")+COUNTIF($H$5:$H$500,"Gerard")+COUNTIF($I$5:$I$500,"Gerard")+COUNTIF($J$5:$J$500,"Gerard")+COUNTIF($K$5:$K$500,"Gerard")</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="141" t="s">
+        <v>634</v>
+      </c>
+      <c r="B533" s="142" t="s">
+        <v>633</v>
+      </c>
+      <c r="C533" s="142" t="s">
+        <v>436</v>
+      </c>
+      <c r="D533" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
+        <v>1</v>
+      </c>
+      <c r="E533" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Sábado")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
+        <v>0</v>
+      </c>
+      <c r="F533" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($D$5:$D$500="Domingo")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
+        <v>1</v>
+      </c>
+      <c r="G533" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"DavidR3")</f>
+        <v>0</v>
+      </c>
+      <c r="H533" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($F$5:$F$500="DavidR3")*(($D$5:$D$500="Viernes")+($D$5:$D$500="Sábado")+($D$5:$D$500="Domingo")))</f>
+        <v>0</v>
+      </c>
+      <c r="I533" s="142" t="n">
+        <f aca="false">G533-H533</f>
+        <v>0</v>
+      </c>
+      <c r="J533" s="142" t="n">
+        <f aca="false">SUMPRODUCT(($E$5:$E$500&lt;&gt;"")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
+        <v>0</v>
+      </c>
+      <c r="K533" s="142" t="n">
+        <f aca="false">COUNTIF($F$5:$F$500,"DavidR3")+COUNTIF($G$5:$G$500,"DavidR3")+COUNTIF($H$5:$H$500,"DavidR3")+COUNTIF($I$5:$I$500,"DavidR3")+COUNTIF($J$5:$J$500,"DavidR3")+COUNTIF($K$5:$K$500,"DavidR3")</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A504:L504"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8502,7 +14290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="54" t="s">
         <v>171</v>
       </c>
@@ -8575,7 +14363,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="13" style="1" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="55" t="s">
         <v>172</v>
       </c>
@@ -8665,7 +14453,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="57" t="s">
         <v>191</v>
       </c>
@@ -8732,7 +14520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="63" t="s">
         <v>194</v>
       </c>
@@ -8799,7 +14587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="57" t="s">
         <v>196</v>
       </c>
@@ -8866,7 +14654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="63" t="s">
         <v>199</v>
       </c>
@@ -8933,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
         <v>201</v>
       </c>
@@ -9000,7 +14788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="63" t="s">
         <v>203</v>
       </c>
@@ -9067,7 +14855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
         <v>205</v>
       </c>
@@ -9134,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
         <v>207</v>
       </c>
@@ -9201,7 +14989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
         <v>209</v>
       </c>
@@ -9272,7 +15060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="63" t="s">
         <v>212</v>
       </c>
@@ -9341,7 +15129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
         <v>215</v>
       </c>
@@ -9412,7 +15200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="63" t="s">
         <v>217</v>
       </c>
@@ -9481,7 +15269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="57" t="s">
         <v>219</v>
       </c>
@@ -9550,7 +15338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="63" t="s">
         <v>221</v>
       </c>
@@ -9619,7 +15407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="57" t="s">
         <v>223</v>
       </c>
@@ -9688,7 +15476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="63" t="s">
         <v>225</v>
       </c>
@@ -9759,7 +15547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="57" t="s">
         <v>227</v>
       </c>
@@ -9828,7 +15616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="63" t="s">
         <v>229</v>
       </c>
@@ -9895,7 +15683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="57" t="s">
         <v>231</v>
       </c>
@@ -9966,7 +15754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="63" t="s">
         <v>233</v>
       </c>
@@ -10037,7 +15825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="57" t="s">
         <v>235</v>
       </c>
@@ -10108,7 +15896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63" t="s">
         <v>237</v>
       </c>
@@ -10179,7 +15967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="57" t="s">
         <v>239</v>
       </c>
@@ -10250,7 +16038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="63" t="s">
         <v>241</v>
       </c>
@@ -10321,7 +16109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="57" t="s">
         <v>243</v>
       </c>
@@ -10392,7 +16180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="70" t="s">
         <v>245</v>
       </c>
@@ -10449,7 +16237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="54" t="s">
         <v>246</v>
       </c>
@@ -10584,7 +16372,7 @@
       <c r="AH2" s="73"/>
       <c r="AI2" s="73"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="77" t="s">
         <v>186</v>
       </c>
@@ -10685,7 +16473,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="78" t="s">
         <v>252</v>
       </c>
@@ -12218,7 +18006,7 @@
       <c r="C1" s="95"/>
       <c r="D1" s="95"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="78" t="s">
         <v>260</v>
       </c>
@@ -12369,7 +18157,7 @@
       <c r="D13" s="102" t="s">
         <v>289</v>
       </c>
-      <c r="E13" s="103" t="s">
+      <c r="E13" s="1" t="s">
         <v>290</v>
       </c>
     </row>
@@ -12456,7 +18244,7 @@
       <c r="D19" s="102" t="s">
         <v>271</v>
       </c>
-      <c r="G19" s="103" t="s">
+      <c r="G19" s="1" t="s">
         <v>304</v>
       </c>
     </row>
@@ -12473,7 +18261,7 @@
       <c r="D20" s="99" t="s">
         <v>271</v>
       </c>
-      <c r="G20" s="103" t="s">
+      <c r="G20" s="1" t="s">
         <v>307</v>
       </c>
     </row>
@@ -12490,35 +18278,35 @@
       <c r="D21" s="102" t="s">
         <v>271</v>
       </c>
-      <c r="G21" s="103" t="s">
+      <c r="G21" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="104" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="103" t="s">
         <v>311</v>
       </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-    </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="103"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+    </row>
+    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="70" t="s">
         <v>262</v>
       </c>
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="104" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="106" t="s">
+      <c r="A27" s="105" t="s">
         <v>313</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="78" t="s">
         <v>260</v>
       </c>
@@ -12532,97 +18320,97 @@
         <v>316</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="96" t="s">
         <v>317</v>
       </c>
-      <c r="B29" s="107" t="s">
+      <c r="B29" s="106" t="s">
         <v>318</v>
       </c>
-      <c r="C29" s="108" t="n">
+      <c r="C29" s="107" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="109" t="n">
+      <c r="D29" s="108" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="109" t="s">
         <v>320</v>
       </c>
-      <c r="C30" s="111" t="n">
+      <c r="C30" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="109" t="n">
+      <c r="D30" s="108" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="96" t="s">
         <v>321</v>
       </c>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="106" t="s">
         <v>322</v>
       </c>
-      <c r="C31" s="108" t="n">
+      <c r="C31" s="107" t="n">
         <v>6</v>
       </c>
-      <c r="D31" s="109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="109" t="s">
         <v>324</v>
       </c>
-      <c r="C32" s="111" t="n">
+      <c r="C32" s="110" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="109" t="n">
+      <c r="D32" s="108" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="s">
         <v>325</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="106" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="108" t="n">
+      <c r="C33" s="107" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D33" s="108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="100"/>
-      <c r="B34" s="110"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="109"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="109"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="108"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="96" t="s">
         <v>327</v>
       </c>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="C35" s="108" t="n">
+      <c r="C35" s="107" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="70" t="s">
         <v>245</v>
       </c>
@@ -12636,14 +18424,14 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="106" t="s">
+      <c r="A39" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="B39" s="106"/>
-      <c r="C39" s="106"/>
-      <c r="D39" s="106"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="78" t="s">
         <v>330</v>
       </c>
@@ -12657,42 +18445,42 @@
         <v>333</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B41" s="112" t="s">
+      <c r="B41" s="111" t="s">
         <v>335</v>
       </c>
-      <c r="C41" s="112" t="s">
+      <c r="C41" s="111" t="s">
         <v>336</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B42" s="112" t="s">
+      <c r="B42" s="111" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="112" t="s">
+      <c r="C42" s="111" t="s">
         <v>340</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B43" s="112" t="s">
+      <c r="B43" s="111" t="s">
         <v>342</v>
       </c>
-      <c r="C43" s="112" t="s">
+      <c r="C43" s="111" t="s">
         <v>343</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -12736,13 +18524,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="112" t="s">
         <v>344</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="78" t="s">
         <v>252</v>
       </c>
@@ -12760,7 +18548,7 @@
       <c r="B3" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="113" t="s">
         <v>346</v>
       </c>
     </row>
@@ -12771,7 +18559,7 @@
       <c r="B4" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="114" t="s">
         <v>347</v>
       </c>
     </row>
@@ -12782,7 +18570,7 @@
       <c r="B5" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="113" t="s">
         <v>348</v>
       </c>
     </row>
@@ -12793,7 +18581,7 @@
       <c r="B6" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="C6" s="115" t="s">
+      <c r="C6" s="114" t="s">
         <v>349</v>
       </c>
     </row>
@@ -12804,7 +18592,7 @@
       <c r="B7" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="114" t="s">
+      <c r="C7" s="113" t="s">
         <v>347</v>
       </c>
     </row>
@@ -12815,7 +18603,7 @@
       <c r="B8" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="114" t="s">
         <v>349</v>
       </c>
     </row>
@@ -12826,7 +18614,7 @@
       <c r="B9" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="114" t="s">
+      <c r="C9" s="113" t="s">
         <v>347</v>
       </c>
     </row>
@@ -12837,7 +18625,7 @@
       <c r="B10" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="115" t="s">
+      <c r="C10" s="114" t="s">
         <v>348</v>
       </c>
     </row>
@@ -12848,7 +18636,7 @@
       <c r="B11" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="C11" s="114" t="s">
+      <c r="C11" s="113" t="s">
         <v>61</v>
       </c>
     </row>
@@ -12859,7 +18647,7 @@
       <c r="B12" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="114" t="s">
         <v>350</v>
       </c>
     </row>
@@ -12870,7 +18658,7 @@
       <c r="B13" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="113" t="s">
         <v>351</v>
       </c>
     </row>
@@ -12881,7 +18669,7 @@
       <c r="B14" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="114" t="s">
         <v>352</v>
       </c>
     </row>
@@ -12892,7 +18680,7 @@
       <c r="B15" s="58" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="113" t="s">
         <v>353</v>
       </c>
     </row>
@@ -12903,7 +18691,7 @@
       <c r="B16" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="114" t="s">
         <v>354</v>
       </c>
     </row>
@@ -12914,7 +18702,7 @@
       <c r="B17" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="C17" s="114" t="s">
+      <c r="C17" s="113" t="s">
         <v>355</v>
       </c>
     </row>
@@ -12925,7 +18713,7 @@
       <c r="B18" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="114" t="s">
         <v>351</v>
       </c>
     </row>
@@ -12936,7 +18724,7 @@
       <c r="B19" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="114" t="s">
+      <c r="C19" s="113" t="s">
         <v>356</v>
       </c>
     </row>
@@ -12947,7 +18735,7 @@
       <c r="B20" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="114" t="s">
         <v>357</v>
       </c>
     </row>
@@ -12958,7 +18746,7 @@
       <c r="B21" s="58" t="s">
         <v>232</v>
       </c>
-      <c r="C21" s="114" t="s">
+      <c r="C21" s="113" t="s">
         <v>358</v>
       </c>
     </row>
@@ -12969,7 +18757,7 @@
       <c r="B22" s="64" t="s">
         <v>234</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="114" t="s">
         <v>359</v>
       </c>
     </row>
@@ -12980,7 +18768,7 @@
       <c r="B23" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="113" t="s">
         <v>360</v>
       </c>
     </row>
@@ -12991,7 +18779,7 @@
       <c r="B24" s="64" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="115" t="s">
+      <c r="C24" s="114" t="s">
         <v>361</v>
       </c>
     </row>
@@ -13002,7 +18790,7 @@
       <c r="B25" s="58" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="114" t="s">
+      <c r="C25" s="113" t="s">
         <v>362</v>
       </c>
     </row>
@@ -13013,7 +18801,7 @@
       <c r="B26" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="C26" s="115" t="s">
+      <c r="C26" s="114" t="s">
         <v>363</v>
       </c>
     </row>
@@ -13024,18 +18812,18 @@
       <c r="B27" s="58" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="114" t="s">
+      <c r="C27" s="113" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="105" t="s">
         <v>365</v>
       </c>
-      <c r="B29" s="106"/>
-      <c r="C29" s="106"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="78" t="s">
         <v>366</v>
       </c>
@@ -13046,102 +18834,102 @@
         <v>368</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="116" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="115" t="s">
         <v>369</v>
       </c>
-      <c r="B31" s="116" t="s">
+      <c r="B31" s="115" t="s">
         <v>370</v>
       </c>
-      <c r="C31" s="116" t="s">
+      <c r="C31" s="115" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="116" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="115" t="s">
         <v>372</v>
       </c>
-      <c r="B32" s="116" t="s">
+      <c r="B32" s="115" t="s">
         <v>373</v>
       </c>
-      <c r="C32" s="116" t="s">
+      <c r="C32" s="115" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="116" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="115" t="s">
         <v>375</v>
       </c>
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="115" t="s">
         <v>370</v>
       </c>
-      <c r="C33" s="116" t="s">
+      <c r="C33" s="115" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="116" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="115" t="s">
         <v>376</v>
       </c>
-      <c r="B34" s="116" t="s">
+      <c r="B34" s="115" t="s">
         <v>373</v>
       </c>
-      <c r="C34" s="116" t="s">
+      <c r="C34" s="115" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="116" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="115" t="s">
         <v>377</v>
       </c>
-      <c r="B35" s="116" t="s">
+      <c r="B35" s="115" t="s">
         <v>370</v>
       </c>
-      <c r="C35" s="116" t="s">
+      <c r="C35" s="115" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="116" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="115" t="s">
         <v>378</v>
       </c>
-      <c r="B36" s="116" t="s">
+      <c r="B36" s="115" t="s">
         <v>373</v>
       </c>
-      <c r="C36" s="116" t="s">
+      <c r="C36" s="115" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="116" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="115" t="s">
         <v>379</v>
       </c>
-      <c r="B37" s="116" t="s">
+      <c r="B37" s="115" t="s">
         <v>370</v>
       </c>
-      <c r="C37" s="116" t="s">
+      <c r="C37" s="115" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="116" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="115" t="s">
         <v>380</v>
       </c>
-      <c r="B38" s="116" t="s">
+      <c r="B38" s="115" t="s">
         <v>370</v>
       </c>
-      <c r="C38" s="116" t="s">
+      <c r="C38" s="115" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="116" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="115" t="s">
         <v>381</v>
       </c>
-      <c r="B39" s="116" t="s">
+      <c r="B39" s="115" t="s">
         <v>373</v>
       </c>
-      <c r="C39" s="116" t="s">
+      <c r="C39" s="115" t="s">
         <v>374</v>
       </c>
     </row>
@@ -13175,14 +18963,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="112" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="78" t="s">
         <v>176</v>
       </c>
@@ -13200,13 +18988,13 @@
       <c r="A3" s="96" t="s">
         <v>386</v>
       </c>
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="116" t="s">
         <v>387</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="117" t="s">
         <v>388</v>
       </c>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="116" t="s">
         <v>389</v>
       </c>
     </row>
@@ -13214,13 +19002,13 @@
       <c r="A4" s="100" t="s">
         <v>390</v>
       </c>
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="118" t="s">
         <v>391</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>392</v>
       </c>
-      <c r="D4" s="119" t="s">
+      <c r="D4" s="118" t="s">
         <v>393</v>
       </c>
     </row>
@@ -13228,13 +19016,13 @@
       <c r="A5" s="96" t="s">
         <v>394</v>
       </c>
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="116" t="s">
         <v>395</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C5" s="119" t="s">
         <v>396</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="116" t="s">
         <v>397</v>
       </c>
     </row>
@@ -13242,13 +19030,13 @@
       <c r="A6" s="100" t="s">
         <v>398</v>
       </c>
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="118" t="s">
         <v>399</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C6" s="119" t="s">
         <v>400</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="118" t="s">
         <v>389</v>
       </c>
     </row>
@@ -13256,13 +19044,13 @@
       <c r="A7" s="96" t="s">
         <v>401</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="116" t="s">
         <v>402</v>
       </c>
-      <c r="C7" s="120" t="s">
+      <c r="C7" s="119" t="s">
         <v>403</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="116" t="s">
         <v>397</v>
       </c>
     </row>
@@ -13270,13 +19058,13 @@
       <c r="A8" s="100" t="s">
         <v>404</v>
       </c>
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="118" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="C8" s="119" t="s">
         <v>406</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="118" t="s">
         <v>407</v>
       </c>
     </row>
@@ -13284,13 +19072,13 @@
       <c r="A9" s="96" t="s">
         <v>408</v>
       </c>
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="116" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="118" t="s">
+      <c r="C9" s="117" t="s">
         <v>410</v>
       </c>
-      <c r="D9" s="117" t="s">
+      <c r="D9" s="116" t="s">
         <v>389</v>
       </c>
     </row>
@@ -13298,13 +19086,13 @@
       <c r="A10" s="100" t="s">
         <v>411</v>
       </c>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="118" t="s">
         <v>412</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>413</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="118" t="s">
         <v>389</v>
       </c>
     </row>
@@ -13312,13 +19100,13 @@
       <c r="A11" s="96" t="s">
         <v>414</v>
       </c>
-      <c r="B11" s="117" t="s">
+      <c r="B11" s="116" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="117" t="s">
         <v>416</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="116" t="s">
         <v>389</v>
       </c>
     </row>
@@ -13326,13 +19114,13 @@
       <c r="A12" s="100" t="s">
         <v>417</v>
       </c>
-      <c r="B12" s="119" t="s">
+      <c r="B12" s="118" t="s">
         <v>418</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="117" t="s">
         <v>419</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="118" t="s">
         <v>393</v>
       </c>
     </row>
@@ -13340,13 +19128,13 @@
       <c r="A13" s="96" t="s">
         <v>420</v>
       </c>
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="116" t="s">
         <v>421</v>
       </c>
-      <c r="C13" s="121" t="s">
+      <c r="C13" s="120" t="s">
         <v>422</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="116" t="s">
         <v>423</v>
       </c>
     </row>
@@ -13354,13 +19142,13 @@
       <c r="A14" s="100" t="s">
         <v>424</v>
       </c>
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="118" t="s">
         <v>425</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="117" t="s">
         <v>426</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="118" t="s">
         <v>397</v>
       </c>
     </row>
@@ -13383,7 +19171,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -13394,39 +19182,39 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="112" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="122" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="121" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="121" t="s">
         <v>428</v>
       </c>
-      <c r="C2" s="122" t="s">
+      <c r="C2" s="121" t="s">
         <v>429</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="D2" s="121" t="s">
         <v>430</v>
       </c>
-      <c r="E2" s="122" t="s">
+      <c r="E2" s="121" t="s">
         <v>431</v>
       </c>
-      <c r="F2" s="122" t="s">
+      <c r="F2" s="121" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="122" t="s">
+      <c r="G2" s="121" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="57" t="s">
         <v>192</v>
       </c>
@@ -13436,14 +19224,14 @@
       <c r="C3" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123" t="s">
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G3" s="123"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="122"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="63" t="s">
         <v>195</v>
       </c>
@@ -13453,14 +19241,14 @@
       <c r="C4" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124" t="s">
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G4" s="124"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G4" s="123"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="57" t="s">
         <v>197</v>
       </c>
@@ -13470,14 +19258,14 @@
       <c r="C5" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123" t="s">
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G5" s="123"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G5" s="122"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="63" t="s">
         <v>200</v>
       </c>
@@ -13487,14 +19275,14 @@
       <c r="C6" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124" t="s">
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G6" s="124"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G6" s="123"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="57" t="s">
         <v>202</v>
       </c>
@@ -13504,14 +19292,14 @@
       <c r="C7" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123" t="s">
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G7" s="123"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G7" s="122"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="63" t="s">
         <v>204</v>
       </c>
@@ -13521,14 +19309,14 @@
       <c r="C8" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124" t="s">
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G8" s="124"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G8" s="123"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="57" t="s">
         <v>206</v>
       </c>
@@ -13538,14 +19326,14 @@
       <c r="C9" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="123" t="s">
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G9" s="123"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="122"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
         <v>208</v>
       </c>
@@ -13555,14 +19343,14 @@
       <c r="C10" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124" t="s">
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G10" s="124"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="123"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
         <v>210</v>
       </c>
@@ -13572,14 +19360,14 @@
       <c r="C11" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123" t="s">
+      <c r="D11" s="122"/>
+      <c r="E11" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="63" t="s">
         <v>213</v>
       </c>
@@ -13589,16 +19377,16 @@
       <c r="C12" s="63" t="s">
         <v>435</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124" t="s">
+      <c r="D12" s="123"/>
+      <c r="E12" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="F12" s="124" t="s">
+      <c r="F12" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G12" s="124"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G12" s="123"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
         <v>216</v>
       </c>
@@ -13608,14 +19396,14 @@
       <c r="C13" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123" t="s">
+      <c r="D13" s="122"/>
+      <c r="E13" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="63" t="s">
         <v>218</v>
       </c>
@@ -13625,16 +19413,16 @@
       <c r="C14" s="63" t="s">
         <v>435</v>
       </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124" t="s">
+      <c r="D14" s="123"/>
+      <c r="E14" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="F14" s="124" t="s">
+      <c r="F14" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G14" s="124"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="123"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="57" t="s">
         <v>220</v>
       </c>
@@ -13644,16 +19432,16 @@
       <c r="C15" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123" t="s">
+      <c r="D15" s="122"/>
+      <c r="E15" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="F15" s="123" t="s">
+      <c r="F15" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G15" s="123"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G15" s="122"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="63" t="s">
         <v>222</v>
       </c>
@@ -13663,16 +19451,16 @@
       <c r="C16" s="63" t="s">
         <v>435</v>
       </c>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124" t="s">
+      <c r="D16" s="123"/>
+      <c r="E16" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="F16" s="124" t="s">
+      <c r="F16" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G16" s="124"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="123"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="57" t="s">
         <v>224</v>
       </c>
@@ -13682,16 +19470,16 @@
       <c r="C17" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="D17" s="123"/>
-      <c r="E17" s="123" t="s">
+      <c r="D17" s="122"/>
+      <c r="E17" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="F17" s="123" t="s">
+      <c r="F17" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="G17" s="123"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G17" s="122"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="63" t="s">
         <v>226</v>
       </c>
@@ -13701,16 +19489,16 @@
       <c r="C18" s="63" t="s">
         <v>435</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124" t="s">
+      <c r="D18" s="123"/>
+      <c r="E18" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="F18" s="124" t="s">
+      <c r="F18" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="G18" s="124"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G18" s="123"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="57" t="s">
         <v>228</v>
       </c>
@@ -13720,14 +19508,14 @@
       <c r="C19" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="63" t="s">
         <v>230</v>
       </c>
@@ -13737,14 +19525,14 @@
       <c r="C20" s="63" t="s">
         <v>436</v>
       </c>
-      <c r="D20" s="124" t="s">
+      <c r="D20" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="57" t="s">
         <v>232</v>
       </c>
@@ -13754,14 +19542,14 @@
       <c r="C21" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123" t="s">
+      <c r="D21" s="122"/>
+      <c r="E21" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="F21" s="123"/>
-      <c r="G21" s="123"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="63" t="s">
         <v>234</v>
       </c>
@@ -13771,14 +19559,14 @@
       <c r="C22" s="63" t="s">
         <v>436</v>
       </c>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124" t="s">
+      <c r="D22" s="123"/>
+      <c r="E22" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="57" t="s">
         <v>236</v>
       </c>
@@ -13788,16 +19576,16 @@
       <c r="C23" s="57" t="s">
         <v>437</v>
       </c>
-      <c r="D23" s="123" t="s">
+      <c r="D23" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123" t="s">
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63" t="s">
         <v>238</v>
       </c>
@@ -13807,16 +19595,16 @@
       <c r="C24" s="63" t="s">
         <v>437</v>
       </c>
-      <c r="D24" s="124" t="s">
+      <c r="D24" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124" t="s">
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="123" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="57" t="s">
         <v>240</v>
       </c>
@@ -13826,16 +19614,16 @@
       <c r="C25" s="57" t="s">
         <v>437</v>
       </c>
-      <c r="D25" s="123" t="s">
+      <c r="D25" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="E25" s="123"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123" t="s">
+      <c r="E25" s="122"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="122" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="63" t="s">
         <v>242</v>
       </c>
@@ -13845,16 +19633,16 @@
       <c r="C26" s="63" t="s">
         <v>437</v>
       </c>
-      <c r="D26" s="124" t="s">
+      <c r="D26" s="123" t="s">
         <v>434</v>
       </c>
-      <c r="E26" s="124"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124" t="s">
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="57" t="s">
         <v>244</v>
       </c>
@@ -13864,42 +19652,168 @@
       <c r="C27" s="57" t="s">
         <v>437</v>
       </c>
-      <c r="D27" s="123" t="s">
+      <c r="D27" s="122" t="s">
         <v>434</v>
       </c>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="123" t="s">
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="124" t="s">
+        <v>438</v>
+      </c>
+      <c r="B28" s="124"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="124"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="125" t="s">
-        <v>438</v>
-      </c>
-      <c r="B29" s="125"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
+        <v>439</v>
+      </c>
+      <c r="B29" s="126" t="s">
+        <v>440</v>
+      </c>
+      <c r="C29" s="125" t="s">
+        <v>437</v>
+      </c>
+      <c r="D29" s="125" t="s">
+        <v>434</v>
+      </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
-      <c r="G29" s="125"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="126" t="s">
-        <v>439</v>
-      </c>
-      <c r="B30" s="126"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="126"/>
+      <c r="G29" s="125" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="125" t="s">
+        <v>441</v>
+      </c>
+      <c r="B30" s="126" t="s">
+        <v>442</v>
+      </c>
+      <c r="C30" s="125" t="s">
+        <v>437</v>
+      </c>
+      <c r="D30" s="125" t="s">
+        <v>434</v>
+      </c>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="125" t="s">
+        <v>443</v>
+      </c>
+      <c r="B31" s="126" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D31" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="E31" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="F31" s="125"/>
+      <c r="G31" s="125"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="125" t="s">
+        <v>445</v>
+      </c>
+      <c r="B32" s="126" t="s">
+        <v>446</v>
+      </c>
+      <c r="C32" s="125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D32" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="E32" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="F32" s="125"/>
+      <c r="G32" s="125"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="125" t="s">
+        <v>447</v>
+      </c>
+      <c r="B33" s="126" t="s">
+        <v>448</v>
+      </c>
+      <c r="C33" s="125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D33" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="E33" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="F33" s="125"/>
+      <c r="G33" s="125"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="125" t="s">
+        <v>449</v>
+      </c>
+      <c r="B34" s="126" t="s">
+        <v>450</v>
+      </c>
+      <c r="C34" s="125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D34" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="E34" s="127" t="s">
+        <v>444</v>
+      </c>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="128" t="s">
+        <v>451</v>
+      </c>
+      <c r="B37" s="128"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="128"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="128"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="129" t="s">
+        <v>452</v>
+      </c>
+      <c r="B38" s="129"/>
+      <c r="C38" s="129"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="129"/>
+      <c r="G38" s="129"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
+++ b/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
@@ -879,7 +879,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="660">
   <si>
     <t xml:space="preserve">Cuadrante de Guardias — Servicio de Anestesiología y Reanimación</t>
   </si>
@@ -1004,210 +1004,210 @@
     <t xml:space="preserve">TX-Sandra</t>
   </si>
   <si>
+    <t xml:space="preserve">UCQ-PatriciaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Almudena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Candela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-PatriciaR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Mercedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Arturo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Miriam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Fatima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4, Emi, Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, Carlota, Cris, Eva, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, Carlota, Cris, Eva, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, AnaR4, Carlota, Cris, Eva, Isa, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-Almudena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-Carlota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-AnaR2</t>
+  </si>
+  <si>
     <t xml:space="preserve">UCQ-Tony</t>
   </si>
   <si>
     <t xml:space="preserve">UCQ-Tania</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Fabian</t>
+    <t xml:space="preserve">MAY-Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Sandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Cristina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Rosario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Asis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Aitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4, Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Asís, Cande, Eva, PatR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Asís, Cande, Fati, Miri, PatR3, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, AnaR4, Fati, Miri, PatR3, Tania, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Carlota, Fati, Miri, PatR3, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Emilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-AnaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ PatR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Anto, Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, AnaR4, Anto, Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Emilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Eva</t>
   </si>
   <si>
     <t xml:space="preserve">MAY-Carlota</t>
   </si>
   <si>
-    <t xml:space="preserve">MAY-Candela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-PatriciaR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Fatima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Arturo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-AnaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Marc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4, Emi, Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, Carlota, Cris, Eva, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, Carlota, Cris, Eva, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, AnaR4, Carlota, Cris, Eva, Isa, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-AnaR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-Carlota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-PatriciaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-AnaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Almudena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Sandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-PatriciaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Mercedes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Emilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Asis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4, Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Asís, Cande, Eva, PatR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Asís, Cande, Fati, Miri, PatR3, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, AnaR4, Fati, Miri, PatR3, Tania, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Carlota, Fati, Miri, PatR3, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★ 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-Emilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-AnaR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Aitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Cristina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Tania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ PatR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Anto, Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, AnaR4, Anto, Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-Almudena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Rosario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Miriam</t>
-  </si>
-  <si>
     <t xml:space="preserve">⛔ Almu</t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">★ 1 nov</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Eva</t>
+    <t xml:space="preserve">UCQ-Asis</t>
   </si>
   <si>
     <t xml:space="preserve">⛔ Emi</t>
@@ -1819,10 +1819,34 @@
     <t xml:space="preserve">3. cuando alguien se haya bloqueado un día por vacaciones ese dia previo a las vacaciones si que puede estar de guardia de quirofano o de REA, pero no puede estar de localizada de trasplante.</t>
   </si>
   <si>
+    <t xml:space="preserve">H-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacaciones y TX del día previo: se permite presencial pero no TX el día antes de un bloqueo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope de guardias totales por año: R1 4-5, R2 exactamente 6, R3 máximo 6, R4 sin tope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprobado automáticamente: R1 entre 4 y 5 (Rosario 4, resto 5); R2 exactamente 6 en las 8; R3 entre 5 y 6 (Patricia R3 y Candela 5, Fabián y Tony 6); R4 sin tope aplicado. 0 violaciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tope de fines de semana dentro de R2: máximo 2 por persona.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprobado automáticamente: los 8 R2 tienen exactamente 2 fines de semana cada uno (bloques distintos, no días sueltos). 0 violaciones — Eva y Antonio ya no tienen 3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VEREDICTO GLOBAL: </t>
   </si>
   <si>
-    <t xml:space="preserve">VÁLIDO salvo 1 excepción documentada — MAY 9 y 11 oct sin cubrir (ver H-01/H-05). Todas las demás reglas H-01 a H-19: 0 violaciones.</t>
+    <t xml:space="preserve">VÁLIDO salvo 1 excepción documentada — MAY 9 y 11 oct sin cubrir (ver H-01/H-05). Todas las demás reglas H-01 a H-21: 0 violaciones, incluidos los nuevos topes de guardias totales (H-20) y fines de semana de R2 (H-21) confirmados el 2026-08-18.</t>
   </si>
   <si>
     <t xml:space="preserve">Puntuación de reglas blandas S-01 a S-07 (0-41, ver fuente de la verdad §7 para el detalle de cada métrica)</t>
@@ -1918,6 +1942,18 @@
     <t xml:space="preserve">Aclaracion de Pablo aplicada: 0 incidencias.</t>
   </si>
   <si>
+    <t xml:space="preserve">18/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-20/H-21 (topes de R1/R2/R2-findes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version anterior tenia R1 en 2-3 guardias, R2 en 8, y Eva/Antonio con 3 findes. Corregido a R1 4-5, R2=6 exacto, R2 max 2 findes, segun confirmacion de Pablo por WhatsApp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo (WhatsApp 18/08)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bloqueos y vacaciones declarados — octubre 2026 (32 = 1 nov, 33 = 2 nov)</t>
   </si>
   <si>
@@ -2278,13 +2314,13 @@
     <t xml:space="preserve">Rotar el mayor que supervisa  (peso 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Asis</t>
-  </si>
-  <si>
     <t xml:space="preserve">UCQ-Antonio</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Marc</t>
+    <t xml:space="preserve">PEQ-Tania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-PatriciaR2</t>
   </si>
   <si>
     <t xml:space="preserve">COMPARATIVA ACUMULADA (junio–octubre 2026) · quién lleva más o menos que la media de su año</t>
@@ -2669,9 +2705,6 @@
   </si>
   <si>
     <t xml:space="preserve">17/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19/08/2026</t>
@@ -4132,6 +4165,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4162,10 +4199,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="22" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="54" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4694,13 +4727,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B1" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="130" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4849,63 +4882,63 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="130" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B24" s="113" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="100" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B26" s="113" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="100" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B27" s="114" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="96" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B28" s="113" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="100" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="96" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B30" s="113" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4946,41 +4979,41 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>63</v>
@@ -4988,13 +5021,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>464</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>40</v>
@@ -5002,13 +5035,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>39</v>
@@ -5016,32 +5049,32 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5049,12 +5082,12 @@
         <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>92</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>466</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>73</v>
@@ -5062,32 +5095,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5109,22 +5142,22 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -5141,7 +5174,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -5156,48 +5189,48 @@
       <c r="L2" s="132"/>
       <c r="M2" s="132"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B4" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="131" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F4" s="131" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="L4" s="131" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="M4" s="131" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="133" t="s">
         <v>191</v>
       </c>
@@ -5205,26 +5238,26 @@
         <v>192</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D5" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E5" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$506+'Histórico de guardias'!$E$506+'Histórico de guardias'!$F$506)+('Resumen de guardias'!$Q$3+'Resumen de guardias'!$R$3+'Resumen de guardias'!$S$3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G5" s="136" t="n">
         <f aca="false">E5-F5</f>
-        <v>-0.875</v>
+        <v>-0.125</v>
       </c>
       <c r="H5" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$506+'Resumen de guardias'!$T$3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí")</f>
@@ -5232,7 +5265,7 @@
       </c>
       <c r="J5" s="136" t="n">
         <f aca="false">H5-I5</f>
-        <v>0.625</v>
+        <v>-0.375</v>
       </c>
       <c r="K5" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$506+'Resumen de guardias'!$I$3</f>
@@ -5240,14 +5273,14 @@
       </c>
       <c r="L5" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$506+'Resumen de guardias'!$L$3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="136" t="n">
         <f aca="false">L5-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.625</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="133" t="s">
         <v>194</v>
       </c>
@@ -5255,10 +5288,10 @@
         <v>195</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D6" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E6" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$507+'Histórico de guardias'!$E$507+'Histórico de guardias'!$F$507)+('Resumen de guardias'!$Q$4+'Resumen de guardias'!$R$4+'Resumen de guardias'!$S$4)</f>
@@ -5266,15 +5299,15 @@
       </c>
       <c r="F6" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G6" s="136" t="n">
         <f aca="false">E6-F6</f>
-        <v>0.125</v>
+        <v>-0.125</v>
       </c>
       <c r="H6" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$507+'Resumen de guardias'!$T$4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí")</f>
@@ -5282,7 +5315,7 @@
       </c>
       <c r="J6" s="136" t="n">
         <f aca="false">H6-I6</f>
-        <v>-0.375</v>
+        <v>0.625</v>
       </c>
       <c r="K6" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$507+'Resumen de guardias'!$I$4</f>
@@ -5290,14 +5323,14 @@
       </c>
       <c r="L6" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$507+'Resumen de guardias'!$L$4</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="136" t="n">
         <f aca="false">L6-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí"))</f>
         <v>0.375</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="133" t="s">
         <v>196</v>
       </c>
@@ -5305,10 +5338,10 @@
         <v>197</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D7" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E7" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$508+'Histórico de guardias'!$E$508+'Histórico de guardias'!$F$508)+('Resumen de guardias'!$Q$5+'Resumen de guardias'!$R$5+'Resumen de guardias'!$S$5)</f>
@@ -5316,15 +5349,15 @@
       </c>
       <c r="F7" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G7" s="136" t="n">
         <f aca="false">E7-F7</f>
-        <v>0.125</v>
+        <v>-0.125</v>
       </c>
       <c r="H7" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$508+'Resumen de guardias'!$T$5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí")</f>
@@ -5332,7 +5365,7 @@
       </c>
       <c r="J7" s="136" t="n">
         <f aca="false">H7-I7</f>
-        <v>0.625</v>
+        <v>-0.375</v>
       </c>
       <c r="K7" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$508+'Resumen de guardias'!$I$5</f>
@@ -5340,14 +5373,14 @@
       </c>
       <c r="L7" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$508+'Resumen de guardias'!$L$5</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M7" s="136" t="n">
         <f aca="false">L7-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí"))</f>
         <v>1.375</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="133" t="s">
         <v>199</v>
       </c>
@@ -5355,10 +5388,10 @@
         <v>200</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D8" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E8" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$509+'Histórico de guardias'!$E$509+'Histórico de guardias'!$F$509)+('Resumen de guardias'!$Q$6+'Resumen de guardias'!$R$6+'Resumen de guardias'!$S$6)</f>
@@ -5366,11 +5399,11 @@
       </c>
       <c r="F8" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C8,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G8" s="136" t="n">
         <f aca="false">E8-F8</f>
-        <v>-0.875</v>
+        <v>-1.125</v>
       </c>
       <c r="H8" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$509+'Resumen de guardias'!$T$6</f>
@@ -5390,14 +5423,14 @@
       </c>
       <c r="L8" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$509+'Resumen de guardias'!$L$6</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" s="136" t="n">
         <f aca="false">L8-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C8,$D$5:$D$32,"Sí"))</f>
         <v>-2.625</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="133" t="s">
         <v>201</v>
       </c>
@@ -5405,10 +5438,10 @@
         <v>202</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D9" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E9" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$510+'Histórico de guardias'!$E$510+'Histórico de guardias'!$F$510)+('Resumen de guardias'!$Q$7+'Resumen de guardias'!$R$7+'Resumen de guardias'!$S$7)</f>
@@ -5416,11 +5449,11 @@
       </c>
       <c r="F9" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C9,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G9" s="136" t="n">
         <f aca="false">E9-F9</f>
-        <v>0.125</v>
+        <v>-0.125</v>
       </c>
       <c r="H9" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$510+'Resumen de guardias'!$T$7</f>
@@ -5440,14 +5473,14 @@
       </c>
       <c r="L9" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$510+'Resumen de guardias'!$L$7</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" s="136" t="n">
         <f aca="false">L9-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C9,$D$5:$D$32,"Sí"))</f>
         <v>0.375</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="133" t="s">
         <v>203</v>
       </c>
@@ -5455,22 +5488,22 @@
         <v>204</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D10" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E10" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$511+'Histórico de guardias'!$E$511+'Histórico de guardias'!$F$511)+('Resumen de guardias'!$Q$8+'Resumen de guardias'!$R$8+'Resumen de guardias'!$S$8)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C10,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G10" s="136" t="n">
         <f aca="false">E10-F10</f>
-        <v>-0.875</v>
+        <v>-0.125</v>
       </c>
       <c r="H10" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$511+'Resumen de guardias'!$T$8</f>
@@ -5490,14 +5523,14 @@
       </c>
       <c r="L10" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$511+'Resumen de guardias'!$L$8</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" s="136" t="n">
         <f aca="false">L10-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C10,$D$5:$D$32,"Sí"))</f>
         <v>0.375</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="133" t="s">
         <v>205</v>
       </c>
@@ -5505,10 +5538,10 @@
         <v>206</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D11" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E11" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$512+'Histórico de guardias'!$E$512+'Histórico de guardias'!$F$512)+('Resumen de guardias'!$Q$9+'Resumen de guardias'!$R$9+'Resumen de guardias'!$S$9)</f>
@@ -5516,11 +5549,11 @@
       </c>
       <c r="F11" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C11,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G11" s="136" t="n">
         <f aca="false">E11-F11</f>
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="H11" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$512+'Resumen de guardias'!$T$9</f>
@@ -5540,25 +5573,25 @@
       </c>
       <c r="L11" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$512+'Resumen de guardias'!$L$9</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M11" s="136" t="n">
         <f aca="false">L11-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C11,$D$5:$D$32,"Sí"))</f>
-        <v>-0.625</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="133" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D12" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E12" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$513+'Histórico de guardias'!$E$513+'Histórico de guardias'!$F$513)+('Resumen de guardias'!$Q$10+'Resumen de guardias'!$R$10+'Resumen de guardias'!$S$10)</f>
@@ -5566,15 +5599,15 @@
       </c>
       <c r="F12" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí")</f>
-        <v>2.875</v>
+        <v>3.125</v>
       </c>
       <c r="G12" s="136" t="n">
         <f aca="false">E12-F12</f>
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="H12" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$513+'Resumen de guardias'!$T$10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí")</f>
@@ -5582,7 +5615,7 @@
       </c>
       <c r="J12" s="136" t="n">
         <f aca="false">H12-I12</f>
-        <v>-0.375</v>
+        <v>0.625</v>
       </c>
       <c r="K12" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$513+'Resumen de guardias'!$I$10</f>
@@ -5590,14 +5623,14 @@
       </c>
       <c r="L12" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$513+'Resumen de guardias'!$L$10</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" s="136" t="n">
         <f aca="false">L12-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí"))</f>
         <v>0.375</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="133" t="s">
         <v>209</v>
       </c>
@@ -5605,10 +5638,10 @@
         <v>210</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D13" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E13" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$514+'Histórico de guardias'!$E$514+'Histórico de guardias'!$F$514)+('Resumen de guardias'!$Q$11+'Resumen de guardias'!$R$11+'Resumen de guardias'!$S$11)</f>
@@ -5616,15 +5649,15 @@
       </c>
       <c r="F13" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C13,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G13" s="136" t="n">
         <f aca="false">E13-F13</f>
-        <v>-2.5</v>
+        <v>-2.25</v>
       </c>
       <c r="H13" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$514+'Resumen de guardias'!$T$11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C13,$D$5:$D$32,"Sí")</f>
@@ -5632,7 +5665,7 @@
       </c>
       <c r="J13" s="136" t="n">
         <f aca="false">H13-I13</f>
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="K13" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$514+'Resumen de guardias'!$I$11</f>
@@ -5640,37 +5673,37 @@
       </c>
       <c r="L13" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$514+'Resumen de guardias'!$L$11</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M13" s="136" t="n">
         <f aca="false">L13-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C13,$D$5:$D$32,"Sí"))</f>
         <v>-1.375</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="133" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B14" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D14" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E14" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$515+'Histórico de guardias'!$E$515+'Histórico de guardias'!$F$515)+('Resumen de guardias'!$Q$12+'Resumen de guardias'!$R$12+'Resumen de guardias'!$S$12)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C14,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G14" s="136" t="n">
         <f aca="false">E14-F14</f>
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="H14" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$515+'Resumen de guardias'!$T$12</f>
@@ -5690,25 +5723,25 @@
       </c>
       <c r="L14" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$515+'Resumen de guardias'!$L$12</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M14" s="136" t="n">
         <f aca="false">L14-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C14,$D$5:$D$32,"Sí"))</f>
         <v>0.625</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="133" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B15" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D15" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E15" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$516+'Histórico de guardias'!$E$516+'Histórico de guardias'!$F$516)+('Resumen de guardias'!$Q$13+'Resumen de guardias'!$R$13+'Resumen de guardias'!$S$13)</f>
@@ -5716,11 +5749,11 @@
       </c>
       <c r="F15" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C15,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G15" s="136" t="n">
         <f aca="false">E15-F15</f>
-        <v>-1.5</v>
+        <v>-1.25</v>
       </c>
       <c r="H15" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$516+'Resumen de guardias'!$T$13</f>
@@ -5740,14 +5773,14 @@
       </c>
       <c r="L15" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$516+'Resumen de guardias'!$L$13</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M15" s="136" t="n">
         <f aca="false">L15-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C15,$D$5:$D$32,"Sí"))</f>
         <v>-0.375</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="133" t="s">
         <v>217</v>
       </c>
@@ -5755,26 +5788,26 @@
         <v>218</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D16" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E16" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$517+'Histórico de guardias'!$E$517+'Histórico de guardias'!$F$517)+('Resumen de guardias'!$Q$14+'Resumen de guardias'!$R$14+'Resumen de guardias'!$S$14)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C16,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G16" s="136" t="n">
         <f aca="false">E16-F16</f>
-        <v>-0.5</v>
+        <v>-1.25</v>
       </c>
       <c r="H16" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$517+'Resumen de guardias'!$T$14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C16,$D$5:$D$32,"Sí")</f>
@@ -5782,7 +5815,7 @@
       </c>
       <c r="J16" s="136" t="n">
         <f aca="false">H16-I16</f>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K16" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$517+'Resumen de guardias'!$I$14</f>
@@ -5790,14 +5823,14 @@
       </c>
       <c r="L16" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$517+'Resumen de guardias'!$L$14</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M16" s="136" t="n">
         <f aca="false">L16-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C16,$D$5:$D$32,"Sí"))</f>
         <v>0.625</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="133" t="s">
         <v>219</v>
       </c>
@@ -5805,26 +5838,26 @@
         <v>220</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D17" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E17" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$518+'Histórico de guardias'!$E$518+'Histórico de guardias'!$F$518)+('Resumen de guardias'!$Q$15+'Resumen de guardias'!$R$15+'Resumen de guardias'!$S$15)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F17" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C17,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G17" s="136" t="n">
         <f aca="false">E17-F17</f>
-        <v>-0.5</v>
+        <v>-1.25</v>
       </c>
       <c r="H17" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$518+'Resumen de guardias'!$T$15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C17,$D$5:$D$32,"Sí")</f>
@@ -5832,7 +5865,7 @@
       </c>
       <c r="J17" s="136" t="n">
         <f aca="false">H17-I17</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="K17" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$518+'Resumen de guardias'!$I$15</f>
@@ -5840,14 +5873,14 @@
       </c>
       <c r="L17" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$518+'Resumen de guardias'!$L$15</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M17" s="136" t="n">
         <f aca="false">L17-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C17,$D$5:$D$32,"Sí"))</f>
         <v>-1.375</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="133" t="s">
         <v>221</v>
       </c>
@@ -5855,10 +5888,10 @@
         <v>222</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D18" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E18" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$519+'Histórico de guardias'!$E$519+'Histórico de guardias'!$F$519)+('Resumen de guardias'!$Q$16+'Resumen de guardias'!$R$16+'Resumen de guardias'!$S$16)</f>
@@ -5866,15 +5899,15 @@
       </c>
       <c r="F18" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C18,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G18" s="136" t="n">
         <f aca="false">E18-F18</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H18" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$519+'Resumen de guardias'!$T$16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="134" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C18,$D$5:$D$32,"Sí")</f>
@@ -5882,7 +5915,7 @@
       </c>
       <c r="J18" s="136" t="n">
         <f aca="false">H18-I18</f>
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="K18" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$519+'Resumen de guardias'!$I$16</f>
@@ -5890,37 +5923,37 @@
       </c>
       <c r="L18" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$519+'Resumen de guardias'!$L$16</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M18" s="136" t="n">
         <f aca="false">L18-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C18,$D$5:$D$32,"Sí"))</f>
         <v>-0.375</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="133" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B19" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D19" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E19" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$520+'Histórico de guardias'!$E$520+'Histórico de guardias'!$F$520)+('Resumen de guardias'!$Q$17+'Resumen de guardias'!$R$17+'Resumen de guardias'!$S$17)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C19,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G19" s="136" t="n">
         <f aca="false">E19-F19</f>
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="H19" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$520+'Resumen de guardias'!$T$17</f>
@@ -5940,14 +5973,14 @@
       </c>
       <c r="L19" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$520+'Resumen de guardias'!$L$17</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M19" s="136" t="n">
         <f aca="false">L19-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C19,$D$5:$D$32,"Sí"))</f>
         <v>1.625</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="133" t="s">
         <v>225</v>
       </c>
@@ -5955,10 +5988,10 @@
         <v>226</v>
       </c>
       <c r="C20" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D20" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E20" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$521+'Histórico de guardias'!$E$521+'Histórico de guardias'!$F$521)+('Resumen de guardias'!$Q$18+'Resumen de guardias'!$R$18+'Resumen de guardias'!$S$18)</f>
@@ -5966,11 +5999,11 @@
       </c>
       <c r="F20" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C20,$D$5:$D$32,"Sí")</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="G20" s="136" t="n">
         <f aca="false">E20-F20</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H20" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$521+'Resumen de guardias'!$T$18</f>
@@ -5990,25 +6023,25 @@
       </c>
       <c r="L20" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$521+'Resumen de guardias'!$L$18</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M20" s="136" t="n">
         <f aca="false">L20-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C20,$D$5:$D$32,"Sí"))</f>
         <v>0.625</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="133" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B21" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C21" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D21" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E21" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$522+'Histórico de guardias'!$E$522+'Histórico de guardias'!$F$522)+('Resumen de guardias'!$Q$19+'Resumen de guardias'!$R$19+'Resumen de guardias'!$S$19)</f>
@@ -6047,7 +6080,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="133" t="s">
         <v>229</v>
       </c>
@@ -6055,10 +6088,10 @@
         <v>230</v>
       </c>
       <c r="C22" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D22" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E22" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$523+'Histórico de guardias'!$E$523+'Histórico de guardias'!$F$523)+('Resumen de guardias'!$Q$20+'Resumen de guardias'!$R$20+'Resumen de guardias'!$S$20)</f>
@@ -6097,18 +6130,18 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="133" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B23" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D23" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E23" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$524+'Histórico de guardias'!$E$524+'Histórico de guardias'!$F$524)+('Resumen de guardias'!$Q$21+'Resumen de guardias'!$R$21+'Resumen de guardias'!$S$21)</f>
@@ -6147,7 +6180,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="133" t="s">
         <v>233</v>
       </c>
@@ -6155,10 +6188,10 @@
         <v>234</v>
       </c>
       <c r="C24" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D24" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E24" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$525+'Histórico de guardias'!$E$525+'Histórico de guardias'!$F$525)+('Resumen de guardias'!$Q$22+'Resumen de guardias'!$R$22+'Resumen de guardias'!$S$22)</f>
@@ -6197,7 +6230,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="133" t="s">
         <v>235</v>
       </c>
@@ -6205,10 +6238,10 @@
         <v>236</v>
       </c>
       <c r="C25" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D25" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E25" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$526+'Histórico de guardias'!$E$526+'Histórico de guardias'!$F$526)+('Resumen de guardias'!$Q$23+'Resumen de guardias'!$R$23+'Resumen de guardias'!$S$23)</f>
@@ -6247,7 +6280,7 @@
         <v>-1.8</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="133" t="s">
         <v>237</v>
       </c>
@@ -6255,10 +6288,10 @@
         <v>238</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D26" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E26" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$527+'Histórico de guardias'!$E$527+'Histórico de guardias'!$F$527)+('Resumen de guardias'!$Q$24+'Resumen de guardias'!$R$24+'Resumen de guardias'!$S$24)</f>
@@ -6286,29 +6319,29 @@
       </c>
       <c r="K26" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$527+'Resumen de guardias'!$I$24</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$527+'Resumen de guardias'!$L$24</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M26" s="136" t="n">
         <f aca="false">L26-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C26,$D$5:$D$32,"Sí"))</f>
-        <v>8.2</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="133" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B27" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D27" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E27" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$528+'Histórico de guardias'!$E$528+'Histórico de guardias'!$F$528)+('Resumen de guardias'!$Q$25+'Resumen de guardias'!$R$25+'Resumen de guardias'!$S$25)</f>
@@ -6347,7 +6380,7 @@
         <v>-9.8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="133" t="s">
         <v>241</v>
       </c>
@@ -6355,10 +6388,10 @@
         <v>242</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D28" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E28" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$529+'Histórico de guardias'!$E$529+'Histórico de guardias'!$F$529)+('Resumen de guardias'!$Q$26+'Resumen de guardias'!$R$26+'Resumen de guardias'!$S$26)</f>
@@ -6386,18 +6419,18 @@
       </c>
       <c r="K28" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$G$529+'Resumen de guardias'!$I$26</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$K$529+'Resumen de guardias'!$L$26</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M28" s="136" t="n">
         <f aca="false">L28-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C28,$D$5:$D$32,"Sí"))</f>
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="133" t="s">
         <v>243</v>
       </c>
@@ -6405,10 +6438,10 @@
         <v>244</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D29" s="135" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E29" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$530+'Histórico de guardias'!$E$530+'Histórico de guardias'!$F$530)+('Resumen de guardias'!$Q$27+'Resumen de guardias'!$R$27+'Resumen de guardias'!$S$27)</f>
@@ -6447,18 +6480,18 @@
         <v>8.2</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="137" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B30" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C30" s="138" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E30" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$531+'Histórico de guardias'!$E$531+'Histórico de guardias'!$F$531)+0</f>
@@ -6497,18 +6530,18 @@
         <v>-6.8</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="137" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B31" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C31" s="138" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D31" s="139" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E31" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$532+'Histórico de guardias'!$E$532+'Histórico de guardias'!$F$532)+0</f>
@@ -6547,18 +6580,18 @@
         <v>-23.8</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="137" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B32" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C32" s="138" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D32" s="139" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E32" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$533+'Histórico de guardias'!$E$533+'Histórico de guardias'!$F$533)+0</f>
@@ -6657,7 +6690,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -6672,7 +6705,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -6687,58 +6720,58 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B4" s="131" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C4" s="131" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="F4" s="131" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B5" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="141" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D5" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E5" s="140"/>
       <c r="F5" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H5" s="141" t="s">
         <v>243</v>
@@ -6753,16 +6786,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B6" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="141" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="D6" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E6" s="140"/>
       <c r="F6" s="141" t="s">
@@ -6772,7 +6805,7 @@
         <v>225</v>
       </c>
       <c r="H6" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I6" s="141" t="s">
         <v>231</v>
@@ -6784,16 +6817,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B7" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="141" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="D7" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E7" s="140"/>
       <c r="F7" s="141" t="s">
@@ -6815,23 +6848,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B8" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="141" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="D8" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E8" s="140"/>
       <c r="F8" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G8" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H8" s="141" t="s">
         <v>241</v>
@@ -6846,29 +6879,29 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B9" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="141" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D9" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E9" s="140"/>
       <c r="F9" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G9" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H9" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I9" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J9" s="141" t="s">
         <v>212</v>
@@ -6877,23 +6910,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B10" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="143" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="D10" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E10" s="142"/>
       <c r="F10" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G10" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H10" s="143" t="s">
         <v>237</v>
@@ -6908,20 +6941,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B11" s="143" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="143" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="D11" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E11" s="142"/>
       <c r="F11" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G11" s="143" t="s">
         <v>221</v>
@@ -6939,23 +6972,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B12" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C12" s="141" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D12" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E12" s="140"/>
       <c r="F12" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H12" s="141" t="s">
         <v>235</v>
@@ -6970,16 +7003,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B13" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="141" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="D13" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E13" s="140"/>
       <c r="F13" s="141" t="s">
@@ -6992,7 +7025,7 @@
         <v>241</v>
       </c>
       <c r="I13" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J13" s="141" t="s">
         <v>209</v>
@@ -7001,26 +7034,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B14" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="141" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="D14" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E14" s="140"/>
       <c r="F14" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G14" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H14" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I14" s="141" t="s">
         <v>233</v>
@@ -7032,16 +7065,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B15" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="141" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="D15" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="141" t="s">
@@ -7054,7 +7087,7 @@
         <v>237</v>
       </c>
       <c r="I15" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J15" s="141" t="s">
         <v>212</v>
@@ -7063,23 +7096,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B16" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="141" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="D16" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E16" s="140"/>
       <c r="F16" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G16" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H16" s="141" t="s">
         <v>235</v>
@@ -7094,16 +7127,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B17" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="143" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="D17" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E17" s="142"/>
       <c r="F17" s="143" t="s">
@@ -7125,23 +7158,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B18" s="143" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="143" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D18" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E18" s="142"/>
       <c r="F18" s="143" t="s">
         <v>243</v>
       </c>
       <c r="G18" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H18" s="143" t="s">
         <v>235</v>
@@ -7156,29 +7189,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B19" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E19" s="140"/>
       <c r="F19" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H19" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="J19" s="141" t="s">
         <v>217</v>
@@ -7187,16 +7220,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B20" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="141" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="D20" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E20" s="140"/>
       <c r="F20" s="141" t="s">
@@ -7212,22 +7245,22 @@
         <v>235</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K20" s="141"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B21" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="141" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D21" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E21" s="140"/>
       <c r="F21" s="141" t="s">
@@ -7249,23 +7282,23 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B22" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E22" s="140"/>
       <c r="F22" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G22" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H22" s="141" t="s">
         <v>231</v>
@@ -7280,16 +7313,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B23" s="141" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E23" s="140"/>
       <c r="F23" s="141" t="s">
@@ -7305,22 +7338,22 @@
         <v>229</v>
       </c>
       <c r="J23" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K23" s="141"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B24" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="D24" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E24" s="142"/>
       <c r="F24" s="143" t="s">
@@ -7342,16 +7375,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B25" s="143" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="143" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="D25" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E25" s="142"/>
       <c r="F25" s="143" t="s">
@@ -7367,26 +7400,26 @@
         <v>229</v>
       </c>
       <c r="J25" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B26" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="141" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E26" s="140"/>
       <c r="F26" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G26" s="141" t="s">
         <v>209</v>
@@ -7395,7 +7428,7 @@
         <v>235</v>
       </c>
       <c r="I26" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J26" s="141" t="s">
         <v>225</v>
@@ -7404,16 +7437,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B27" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="141" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E27" s="140"/>
       <c r="F27" s="141" t="s">
@@ -7429,22 +7462,22 @@
         <v>231</v>
       </c>
       <c r="J27" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K27" s="141"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B28" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="141" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E28" s="140"/>
       <c r="F28" s="141" t="s">
@@ -7466,16 +7499,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B29" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="141" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E29" s="140"/>
       <c r="F29" s="141" t="s">
@@ -7497,23 +7530,23 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B30" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E30" s="140"/>
       <c r="F30" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G30" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H30" s="141" t="s">
         <v>241</v>
@@ -7522,22 +7555,22 @@
         <v>233</v>
       </c>
       <c r="J30" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K30" s="141"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B31" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="143" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D31" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E31" s="142"/>
       <c r="F31" s="143" t="s">
@@ -7550,25 +7583,25 @@
         <v>235</v>
       </c>
       <c r="I31" s="143" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="J31" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K31" s="143"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="142" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B32" s="143" t="n">
         <v>28</v>
       </c>
       <c r="C32" s="143" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="D32" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E32" s="142"/>
       <c r="F32" s="143" t="s">
@@ -7584,35 +7617,35 @@
         <v>233</v>
       </c>
       <c r="J32" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K32" s="143"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B33" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C33" s="141" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E33" s="140"/>
       <c r="F33" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G33" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H33" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I33" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J33" s="141" t="s">
         <v>209</v>
@@ -7623,29 +7656,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="140" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B34" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="141" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="D34" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E34" s="140"/>
       <c r="F34" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G34" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H34" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I34" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="J34" s="141" t="s">
         <v>229</v>
@@ -7654,26 +7687,26 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B35" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="141" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="D35" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E35" s="140"/>
       <c r="F35" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G35" s="141" t="s">
         <v>221</v>
       </c>
       <c r="H35" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I35" s="141" t="s">
         <v>231</v>
@@ -7685,54 +7718,54 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B36" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="141" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D36" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E36" s="140"/>
       <c r="F36" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G36" s="141" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I36" s="141" t="s">
         <v>243</v>
       </c>
       <c r="J36" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K36" s="141"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B37" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="141" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D37" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E37" s="140"/>
       <c r="F37" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G37" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H37" s="141" t="s">
         <v>241</v>
@@ -7747,20 +7780,20 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B38" s="143" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="143" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="D38" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E38" s="142"/>
       <c r="F38" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G38" s="143" t="s">
         <v>225</v>
@@ -7778,29 +7811,29 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B39" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C39" s="143" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="D39" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E39" s="142"/>
       <c r="F39" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G39" s="143" t="s">
         <v>229</v>
       </c>
       <c r="H39" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I39" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J39" s="143" t="s">
         <v>212</v>
@@ -7809,16 +7842,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B40" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C40" s="141" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D40" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E40" s="140"/>
       <c r="F40" s="141" t="s">
@@ -7840,26 +7873,26 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B41" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C41" s="141" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="D41" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E41" s="140"/>
       <c r="F41" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G41" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H41" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I41" s="141" t="s">
         <v>219</v>
@@ -7871,16 +7904,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B42" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C42" s="141" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="D42" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E42" s="140"/>
       <c r="F42" s="141" t="s">
@@ -7896,22 +7929,22 @@
         <v>209</v>
       </c>
       <c r="J42" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K42" s="141"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B43" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C43" s="141" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="D43" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E43" s="140"/>
       <c r="F43" s="141" t="s">
@@ -7921,7 +7954,7 @@
         <v>221</v>
       </c>
       <c r="H43" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I43" s="141" t="s">
         <v>217</v>
@@ -7933,20 +7966,20 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B44" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C44" s="141" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="D44" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E44" s="140"/>
       <c r="F44" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G44" s="141" t="s">
         <v>229</v>
@@ -7955,7 +7988,7 @@
         <v>233</v>
       </c>
       <c r="I44" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J44" s="141" t="s">
         <v>212</v>
@@ -7964,16 +7997,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B45" s="143" t="n">
         <v>11</v>
       </c>
       <c r="C45" s="143" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D45" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E45" s="142"/>
       <c r="F45" s="143" t="s">
@@ -7983,7 +8016,7 @@
         <v>221</v>
       </c>
       <c r="H45" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I45" s="143" t="s">
         <v>217</v>
@@ -7995,26 +8028,26 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B46" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C46" s="143" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="D46" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E46" s="142"/>
       <c r="F46" s="143" t="s">
         <v>241</v>
       </c>
       <c r="G46" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H46" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I46" s="143" t="s">
         <v>237</v>
@@ -8026,20 +8059,20 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B47" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C47" s="141" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="D47" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E47" s="140"/>
       <c r="F47" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G47" s="141" t="s">
         <v>221</v>
@@ -8051,22 +8084,22 @@
         <v>217</v>
       </c>
       <c r="J47" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K47" s="141"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B48" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="141" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="D48" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E48" s="140"/>
       <c r="F48" s="141" t="s">
@@ -8076,10 +8109,10 @@
         <v>212</v>
       </c>
       <c r="H48" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I48" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="J48" s="141" t="s">
         <v>219</v>
@@ -8088,20 +8121,20 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B49" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="141" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D49" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E49" s="140"/>
       <c r="F49" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G49" s="141" t="s">
         <v>221</v>
@@ -8119,20 +8152,20 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B50" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C50" s="141" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="D50" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E50" s="140"/>
       <c r="F50" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G50" s="141" t="s">
         <v>225</v>
@@ -8141,35 +8174,35 @@
         <v>235</v>
       </c>
       <c r="I50" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J50" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K50" s="141"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B51" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C51" s="141" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D51" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E51" s="140"/>
       <c r="F51" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G51" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H51" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I51" s="141" t="s">
         <v>241</v>
@@ -8181,20 +8214,20 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B52" s="143" t="n">
         <v>18</v>
       </c>
       <c r="C52" s="143" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D52" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E52" s="142"/>
       <c r="F52" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G52" s="143" t="s">
         <v>225</v>
@@ -8203,25 +8236,25 @@
         <v>235</v>
       </c>
       <c r="I52" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J52" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K52" s="143"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B53" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C53" s="143" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="D53" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E53" s="142"/>
       <c r="F53" s="143" t="s">
@@ -8243,26 +8276,26 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B54" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C54" s="141" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="D54" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E54" s="140"/>
       <c r="F54" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G54" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H54" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I54" s="141" t="s">
         <v>237</v>
@@ -8274,20 +8307,20 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B55" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C55" s="141" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="D55" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E55" s="140"/>
       <c r="F55" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G55" s="141" t="s">
         <v>225</v>
@@ -8305,47 +8338,47 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B56" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C56" s="141" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="D56" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E56" s="140"/>
       <c r="F56" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G56" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H56" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I56" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J56" s="141" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="K56" s="141"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B57" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C57" s="141" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="D57" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E57" s="140"/>
       <c r="F57" s="141" t="s">
@@ -8355,7 +8388,7 @@
         <v>229</v>
       </c>
       <c r="H57" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I57" s="141" t="s">
         <v>233</v>
@@ -8367,16 +8400,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B58" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C58" s="141" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="D58" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E58" s="140"/>
       <c r="F58" s="141" t="s">
@@ -8389,7 +8422,7 @@
         <v>235</v>
       </c>
       <c r="I58" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J58" s="141" t="s">
         <v>212</v>
@@ -8398,16 +8431,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B59" s="143" t="n">
         <v>25</v>
       </c>
       <c r="C59" s="143" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="D59" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E59" s="142"/>
       <c r="F59" s="143" t="s">
@@ -8429,16 +8462,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="142" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B60" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C60" s="143" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="D60" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E60" s="142"/>
       <c r="F60" s="143" t="s">
@@ -8454,22 +8487,22 @@
         <v>243</v>
       </c>
       <c r="J60" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K60" s="143"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B61" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="141" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D61" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E61" s="140"/>
       <c r="F61" s="141" t="s">
@@ -8479,28 +8512,28 @@
         <v>229</v>
       </c>
       <c r="H61" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I61" s="141" t="s">
         <v>233</v>
       </c>
       <c r="J61" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K61" s="141"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B62" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C62" s="141" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="D62" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E62" s="140"/>
       <c r="F62" s="141" t="s">
@@ -8516,29 +8549,29 @@
         <v>212</v>
       </c>
       <c r="J62" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K62" s="141"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B63" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C63" s="141" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D63" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E63" s="140"/>
       <c r="F63" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G63" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H63" s="141" t="s">
         <v>243</v>
@@ -8553,16 +8586,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="140" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B64" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C64" s="141" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="D64" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E64" s="140"/>
       <c r="F64" s="141" t="s">
@@ -8584,16 +8617,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B65" s="143" t="n">
         <v>1</v>
       </c>
       <c r="C65" s="143" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="D65" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E65" s="142"/>
       <c r="F65" s="143" t="s">
@@ -8606,23 +8639,23 @@
         <v>237</v>
       </c>
       <c r="I65" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J65" s="143"/>
       <c r="K65" s="143"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B66" s="143" t="n">
         <v>2</v>
       </c>
       <c r="C66" s="143" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D66" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E66" s="142"/>
       <c r="F66" s="143" t="s">
@@ -8644,16 +8677,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B67" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="141" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="D67" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E67" s="140"/>
       <c r="F67" s="141" t="s">
@@ -8673,20 +8706,20 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B68" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C68" s="141" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="D68" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E68" s="140"/>
       <c r="F68" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G68" s="141" t="s">
         <v>229</v>
@@ -8695,25 +8728,25 @@
         <v>231</v>
       </c>
       <c r="I68" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J68" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K68" s="141"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B69" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C69" s="141" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="D69" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E69" s="140"/>
       <c r="F69" s="141" t="s">
@@ -8723,7 +8756,7 @@
         <v>229</v>
       </c>
       <c r="H69" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I69" s="141" t="s">
         <v>235</v>
@@ -8733,23 +8766,23 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B70" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="141" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E70" s="140"/>
       <c r="F70" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G70" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H70" s="141" t="s">
         <v>241</v>
@@ -8764,16 +8797,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B71" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="141" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D71" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E71" s="140"/>
       <c r="F71" s="141" t="s">
@@ -8783,10 +8816,10 @@
         <v>219</v>
       </c>
       <c r="H71" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I71" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J71" s="141" t="s">
         <v>212</v>
@@ -8795,16 +8828,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B72" s="143" t="n">
         <v>8</v>
       </c>
       <c r="C72" s="143" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="D72" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E72" s="142"/>
       <c r="F72" s="143" t="s">
@@ -8814,7 +8847,7 @@
         <v>225</v>
       </c>
       <c r="H72" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="I72" s="143" t="s">
         <v>231</v>
@@ -8824,16 +8857,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B73" s="143" t="n">
         <v>9</v>
       </c>
       <c r="C73" s="143" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D73" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E73" s="142"/>
       <c r="F73" s="143" t="s">
@@ -8843,10 +8876,10 @@
         <v>219</v>
       </c>
       <c r="H73" s="143" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I73" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J73" s="143" t="s">
         <v>212</v>
@@ -8855,20 +8888,20 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B74" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C74" s="141" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="D74" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E74" s="140"/>
       <c r="F74" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G74" s="141" t="s">
         <v>229</v>
@@ -8886,20 +8919,20 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B75" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C75" s="141" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="D75" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E75" s="140"/>
       <c r="F75" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G75" s="141" t="s">
         <v>209</v>
@@ -8917,20 +8950,20 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B76" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C76" s="141" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="D76" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E76" s="140"/>
       <c r="F76" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G76" s="141" t="s">
         <v>229</v>
@@ -8939,7 +8972,7 @@
         <v>241</v>
       </c>
       <c r="I76" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J76" s="141" t="s">
         <v>212</v>
@@ -8948,26 +8981,26 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B77" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C77" s="141" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="D77" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E77" s="140"/>
       <c r="F77" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G77" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H77" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I77" s="141" t="s">
         <v>219</v>
@@ -8979,20 +9012,20 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B78" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C78" s="141" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="D78" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E78" s="140"/>
       <c r="F78" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G78" s="141" t="s">
         <v>229</v>
@@ -9010,22 +9043,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="144" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B79" s="145" t="n">
         <v>15</v>
       </c>
       <c r="C79" s="145" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="D79" s="145" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E79" s="144" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="F79" s="145" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G79" s="145" t="s">
         <v>243</v>
@@ -9041,16 +9074,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B80" s="143" t="n">
         <v>16</v>
       </c>
       <c r="C80" s="143" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="D80" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E80" s="142"/>
       <c r="F80" s="143" t="s">
@@ -9072,57 +9105,57 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B81" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C81" s="141" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="D81" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E81" s="140"/>
       <c r="F81" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G81" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H81" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I81" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J81" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K81" s="141"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B82" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C82" s="141" t="s">
-        <v>595</v>
+        <v>352</v>
       </c>
       <c r="D82" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E82" s="140"/>
       <c r="F82" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G82" s="141" t="s">
         <v>243</v>
       </c>
       <c r="H82" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I82" s="141" t="s">
         <v>209</v>
@@ -9134,16 +9167,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B83" s="141" t="n">
         <v>19</v>
       </c>
       <c r="C83" s="141" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="D83" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E83" s="140"/>
       <c r="F83" s="141" t="s">
@@ -9156,25 +9189,25 @@
         <v>231</v>
       </c>
       <c r="I83" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J83" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K83" s="141"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B84" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C84" s="141" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="D84" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E84" s="140"/>
       <c r="F84" s="141" t="s">
@@ -9184,10 +9217,10 @@
         <v>221</v>
       </c>
       <c r="H84" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I84" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="J84" s="141" t="s">
         <v>233</v>
@@ -9196,20 +9229,20 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B85" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="141" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="D85" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E85" s="140"/>
       <c r="F85" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G85" s="141" t="s">
         <v>225</v>
@@ -9227,20 +9260,20 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B86" s="143" t="n">
         <v>22</v>
       </c>
       <c r="C86" s="143" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="D86" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E86" s="142"/>
       <c r="F86" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G86" s="143" t="s">
         <v>243</v>
@@ -9249,27 +9282,27 @@
         <v>233</v>
       </c>
       <c r="I86" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J86" s="143"/>
       <c r="K86" s="143"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B87" s="143" t="n">
         <v>23</v>
       </c>
       <c r="C87" s="143" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="D87" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E87" s="142"/>
       <c r="F87" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G87" s="143" t="s">
         <v>225</v>
@@ -9287,20 +9320,20 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B88" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C88" s="141" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="D88" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E88" s="140"/>
       <c r="F88" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="G88" s="141" t="s">
         <v>229</v>
@@ -9309,25 +9342,25 @@
         <v>237</v>
       </c>
       <c r="I88" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="J88" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K88" s="141"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B89" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C89" s="141" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="D89" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E89" s="140"/>
       <c r="F89" s="141" t="s">
@@ -9337,7 +9370,7 @@
         <v>212</v>
       </c>
       <c r="H89" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I89" s="141" t="s">
         <v>233</v>
@@ -9349,16 +9382,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B90" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C90" s="141" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="D90" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E90" s="140"/>
       <c r="F90" s="141" t="s">
@@ -9368,41 +9401,41 @@
         <v>225</v>
       </c>
       <c r="H90" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="I90" s="141" t="s">
         <v>221</v>
       </c>
       <c r="J90" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K90" s="141"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B91" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C91" s="141" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="D91" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E91" s="140"/>
       <c r="F91" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G91" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H91" s="141" t="s">
         <v>231</v>
       </c>
       <c r="I91" s="141" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="J91" s="141" t="s">
         <v>217</v>
@@ -9411,16 +9444,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B92" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C92" s="141" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="D92" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E92" s="140"/>
       <c r="F92" s="141" t="s">
@@ -9433,25 +9466,25 @@
         <v>237</v>
       </c>
       <c r="I92" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J92" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K92" s="141"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B93" s="143" t="n">
         <v>29</v>
       </c>
       <c r="C93" s="143" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="D93" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E93" s="142"/>
       <c r="F93" s="143" t="s">
@@ -9461,61 +9494,61 @@
         <v>221</v>
       </c>
       <c r="H93" s="143" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="I93" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="J93" s="143"/>
       <c r="K93" s="143"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="142" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B94" s="143" t="n">
         <v>30</v>
       </c>
       <c r="C94" s="143" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="D94" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E94" s="142"/>
       <c r="F94" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G94" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H94" s="143" t="s">
         <v>237</v>
       </c>
       <c r="I94" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J94" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="K94" s="143"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="140" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B95" s="141" t="n">
         <v>31</v>
       </c>
       <c r="C95" s="141" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="D95" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E95" s="140"/>
       <c r="F95" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G95" s="141" t="s">
         <v>243</v>
@@ -9533,23 +9566,23 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B96" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="141" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="D96" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E96" s="140"/>
       <c r="F96" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G96" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H96" s="141" t="s">
         <v>233</v>
@@ -9564,23 +9597,23 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B97" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C97" s="141" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D97" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E97" s="140"/>
       <c r="F97" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G97" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H97" s="141" t="s">
         <v>237</v>
@@ -9595,16 +9628,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B98" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C98" s="141" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="D98" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E98" s="140"/>
       <c r="F98" s="141" t="s">
@@ -9614,10 +9647,10 @@
         <v>217</v>
       </c>
       <c r="H98" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I98" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J98" s="141" t="s">
         <v>191</v>
@@ -9626,16 +9659,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B99" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C99" s="141" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="D99" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E99" s="140"/>
       <c r="F99" s="141" t="s">
@@ -9648,7 +9681,7 @@
         <v>229</v>
       </c>
       <c r="I99" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J99" s="141" t="s">
         <v>194</v>
@@ -9657,20 +9690,20 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B100" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C100" s="143" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="D100" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E100" s="142"/>
       <c r="F100" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="G100" s="143" t="s">
         <v>221</v>
@@ -9688,16 +9721,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B101" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C101" s="143" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="D101" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E101" s="142"/>
       <c r="F101" s="143" t="s">
@@ -9710,7 +9743,7 @@
         <v>229</v>
       </c>
       <c r="I101" s="143" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J101" s="143" t="s">
         <v>194</v>
@@ -9719,20 +9752,20 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B102" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C102" s="141" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="D102" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E102" s="140"/>
       <c r="F102" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G102" s="141" t="s">
         <v>212</v>
@@ -9750,29 +9783,29 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B103" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C103" s="141" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="D103" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E103" s="140"/>
       <c r="F103" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G103" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H103" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I103" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J103" s="141" t="s">
         <v>217</v>
@@ -9781,20 +9814,20 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B104" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C104" s="141" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="D104" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E104" s="140"/>
       <c r="F104" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G104" s="141" t="s">
         <v>209</v>
@@ -9803,7 +9836,7 @@
         <v>243</v>
       </c>
       <c r="I104" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J104" s="141" t="s">
         <v>219</v>
@@ -9812,26 +9845,26 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B105" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C105" s="141" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="D105" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G105" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H105" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I105" s="141" t="s">
         <v>212</v>
@@ -9843,20 +9876,20 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B106" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C106" s="141" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="D106" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E106" s="140"/>
       <c r="F106" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G106" s="141" t="s">
         <v>231</v>
@@ -9865,7 +9898,7 @@
         <v>233</v>
       </c>
       <c r="I106" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J106" s="141" t="s">
         <v>207</v>
@@ -9874,20 +9907,20 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B107" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C107" s="143" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="D107" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E107" s="142"/>
       <c r="F107" s="143" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G107" s="143" t="s">
         <v>212</v>
@@ -9905,20 +9938,20 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B108" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C108" s="143" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="D108" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E108" s="142"/>
       <c r="F108" s="143" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G108" s="143" t="s">
         <v>231</v>
@@ -9927,7 +9960,7 @@
         <v>233</v>
       </c>
       <c r="I108" s="143" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J108" s="143" t="s">
         <v>207</v>
@@ -9936,23 +9969,23 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B109" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C109" s="141" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="D109" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E109" s="140"/>
       <c r="F109" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G109" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H109" s="141" t="s">
         <v>229</v>
@@ -9967,16 +10000,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B110" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C110" s="141" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="D110" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E110" s="140"/>
       <c r="F110" s="141" t="s">
@@ -9989,7 +10022,7 @@
         <v>237</v>
       </c>
       <c r="I110" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J110" s="141" t="s">
         <v>225</v>
@@ -9998,26 +10031,26 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B111" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C111" s="141" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="D111" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E111" s="140"/>
       <c r="F111" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G111" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H111" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I111" s="141" t="s">
         <v>212</v>
@@ -10029,16 +10062,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B112" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C112" s="141" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="D112" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E112" s="140"/>
       <c r="F112" s="141" t="s">
@@ -10048,7 +10081,7 @@
         <v>231</v>
       </c>
       <c r="H112" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="I112" s="141" t="s">
         <v>217</v>
@@ -10060,23 +10093,23 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B113" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C113" s="141" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="D113" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E113" s="140"/>
       <c r="F113" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G113" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H113" s="141" t="s">
         <v>229</v>
@@ -10085,26 +10118,26 @@
         <v>221</v>
       </c>
       <c r="J113" s="141" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="K113" s="141"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B114" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C114" s="143" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="D114" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E114" s="142"/>
       <c r="F114" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G114" s="143" t="s">
         <v>209</v>
@@ -10122,23 +10155,23 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B115" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C115" s="143" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="D115" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E115" s="142"/>
       <c r="F115" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G115" s="143" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H115" s="143" t="s">
         <v>229</v>
@@ -10147,22 +10180,22 @@
         <v>221</v>
       </c>
       <c r="J115" s="143" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="K115" s="143"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B116" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C116" s="141" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="D116" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E116" s="140"/>
       <c r="F116" s="141" t="s">
@@ -10184,20 +10217,20 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B117" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C117" s="141" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="D117" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E117" s="140"/>
       <c r="F117" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G117" s="141" t="s">
         <v>209</v>
@@ -10215,29 +10248,29 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B118" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C118" s="141" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="D118" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E118" s="140"/>
       <c r="F118" s="141" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G118" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H118" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I118" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J118" s="141" t="s">
         <v>196</v>
@@ -10246,16 +10279,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B119" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C119" s="141" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="D119" s="141" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E119" s="140"/>
       <c r="F119" s="141" t="s">
@@ -10268,7 +10301,7 @@
         <v>233</v>
       </c>
       <c r="I119" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J119" s="141" t="s">
         <v>203</v>
@@ -10277,16 +10310,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B120" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C120" s="141" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="D120" s="141" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E120" s="140"/>
       <c r="F120" s="141" t="s">
@@ -10296,7 +10329,7 @@
         <v>219</v>
       </c>
       <c r="H120" s="141" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I120" s="141" t="s">
         <v>205</v>
@@ -10308,16 +10341,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B121" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C121" s="143" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="D121" s="143" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E121" s="142"/>
       <c r="F121" s="143" t="s">
@@ -10327,7 +10360,7 @@
         <v>231</v>
       </c>
       <c r="H121" s="143" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="I121" s="143" t="s">
         <v>212</v>
@@ -10339,16 +10372,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="142" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B122" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C122" s="143" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="D122" s="143" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E122" s="142"/>
       <c r="F122" s="143" t="s">
@@ -10358,7 +10391,7 @@
         <v>219</v>
       </c>
       <c r="H122" s="143" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I122" s="143" t="s">
         <v>205</v>
@@ -10370,29 +10403,29 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B123" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C123" s="141" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="D123" s="141" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E123" s="140"/>
       <c r="F123" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G123" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H123" s="141" t="s">
         <v>229</v>
       </c>
       <c r="I123" s="141" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="J123" s="141" t="s">
         <v>221</v>
@@ -10401,16 +10434,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B124" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C124" s="141" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="D124" s="141" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E124" s="140"/>
       <c r="F124" s="141" t="s">
@@ -10420,7 +10453,7 @@
         <v>209</v>
       </c>
       <c r="H124" s="141" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="I124" s="141" t="s">
         <v>225</v>
@@ -10432,16 +10465,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="140" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B125" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C125" s="141" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="D125" s="141" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E125" s="140"/>
       <c r="F125" s="141" t="s">
@@ -10454,16 +10487,16 @@
         <v>243</v>
       </c>
       <c r="I125" s="141" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J125" s="141" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="K125" s="141"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="131" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="B504" s="131"/>
       <c r="C504" s="131"/>
@@ -10479,37 +10512,37 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="131" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B505" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C505" s="131" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D505" s="131" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="E505" s="131" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="F505" s="131" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="G505" s="131" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="H505" s="131" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="I505" s="131" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="J505" s="131" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="K505" s="131" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10520,7 +10553,7 @@
         <v>192</v>
       </c>
       <c r="C506" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D506" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
@@ -10563,7 +10596,7 @@
         <v>195</v>
       </c>
       <c r="C507" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D507" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
@@ -10606,7 +10639,7 @@
         <v>197</v>
       </c>
       <c r="C508" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D508" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
@@ -10649,7 +10682,7 @@
         <v>200</v>
       </c>
       <c r="C509" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D509" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
@@ -10692,7 +10725,7 @@
         <v>202</v>
       </c>
       <c r="C510" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D510" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
@@ -10735,7 +10768,7 @@
         <v>204</v>
       </c>
       <c r="C511" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D511" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
@@ -10778,7 +10811,7 @@
         <v>206</v>
       </c>
       <c r="C512" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D512" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
@@ -10815,13 +10848,13 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="133" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B513" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C513" s="134" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D513" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
@@ -10864,7 +10897,7 @@
         <v>210</v>
       </c>
       <c r="C514" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D514" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
@@ -10901,13 +10934,13 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="133" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B515" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C515" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D515" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
@@ -10944,13 +10977,13 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="133" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B516" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C516" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D516" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
@@ -10993,7 +11026,7 @@
         <v>218</v>
       </c>
       <c r="C517" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D517" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
@@ -11036,7 +11069,7 @@
         <v>220</v>
       </c>
       <c r="C518" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D518" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
@@ -11079,7 +11112,7 @@
         <v>222</v>
       </c>
       <c r="C519" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D519" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
@@ -11116,13 +11149,13 @@
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="133" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B520" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C520" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D520" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
@@ -11165,7 +11198,7 @@
         <v>226</v>
       </c>
       <c r="C521" s="134" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D521" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
@@ -11202,13 +11235,13 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="133" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B522" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C522" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D522" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
@@ -11251,7 +11284,7 @@
         <v>230</v>
       </c>
       <c r="C523" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D523" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
@@ -11288,13 +11321,13 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="133" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B524" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C524" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D524" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
@@ -11337,7 +11370,7 @@
         <v>234</v>
       </c>
       <c r="C525" s="134" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D525" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
@@ -11380,7 +11413,7 @@
         <v>236</v>
       </c>
       <c r="C526" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D526" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
@@ -11423,7 +11456,7 @@
         <v>238</v>
       </c>
       <c r="C527" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D527" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
@@ -11460,13 +11493,13 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="133" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B528" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C528" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D528" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
@@ -11509,7 +11542,7 @@
         <v>242</v>
       </c>
       <c r="C529" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D529" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
@@ -11552,7 +11585,7 @@
         <v>244</v>
       </c>
       <c r="C530" s="134" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D530" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
@@ -11589,13 +11622,13 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="137" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B531" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C531" s="138" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D531" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
@@ -11632,13 +11665,13 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="137" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B532" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C532" s="138" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D532" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
@@ -11675,13 +11708,13 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="137" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B533" s="138" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C533" s="138" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D533" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
@@ -11925,7 +11958,7 @@
         <v>21</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>21</v>
@@ -11945,25 +11978,25 @@
         <v>23</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9" s="28" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="28" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M9" s="28" t="s">
         <v>23</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11977,25 +12010,25 @@
         <v>25</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M10" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12009,25 +12042,25 @@
         <v>25</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M11" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12097,7 +12130,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="23" t="s">
         <v>19</v>
@@ -12109,7 +12142,7 @@
         <v>19</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>19</v>
@@ -12135,43 +12168,43 @@
         <v>21</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="27" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12179,25 +12212,25 @@
         <v>23</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I18" s="28" t="s">
         <v>23</v>
@@ -12207,7 +12240,7 @@
         <v>23</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M18" s="28" t="s">
         <v>23</v>
@@ -12219,25 +12252,25 @@
         <v>25</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C19" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E19" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="G19" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="I19" s="30" t="s">
         <v>25</v>
@@ -12249,7 +12282,7 @@
         <v>25</v>
       </c>
       <c r="L19" s="31" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="M19" s="30" t="s">
         <v>25</v>
@@ -12263,103 +12296,103 @@
         <v>25</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="I20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M20" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J21" s="32"/>
       <c r="K21" s="32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L21" s="32"/>
       <c r="M21" s="32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="35" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B23" s="35"/>
       <c r="C23" s="21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N23" s="22"/>
     </row>
@@ -12375,37 +12408,37 @@
         <v>19</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E25" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>19</v>
       </c>
       <c r="J25" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>19</v>
       </c>
       <c r="N25" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12413,25 +12446,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E26" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>21</v>
@@ -12443,7 +12476,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="27" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="M26" s="26" t="s">
         <v>21</v>
@@ -12457,43 +12490,43 @@
         <v>23</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="G27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="J27" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M27" s="28" t="s">
         <v>23</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12501,43 +12534,43 @@
         <v>25</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="G28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J28" s="31" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="K28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="31" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="M28" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N28" s="31" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12545,7 +12578,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>25</v>
@@ -12557,13 +12590,13 @@
         <v>25</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="G29" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="I29" s="30" t="s">
         <v>25</v>
@@ -12575,7 +12608,7 @@
         <v>25</v>
       </c>
       <c r="L29" s="31" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="M29" s="30" t="s">
         <v>25</v>
@@ -12586,62 +12619,62 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B30" s="32"/>
       <c r="C30" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" s="32"/>
       <c r="G30" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" s="32"/>
       <c r="M30" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N30" s="32"/>
     </row>
     <row r="31" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L32" s="22"/>
       <c r="M32" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N32" s="22"/>
     </row>
@@ -12657,7 +12690,7 @@
         <v>19</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>19</v>
@@ -12675,19 +12708,19 @@
         <v>19</v>
       </c>
       <c r="J34" s="24" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="K34" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L34" s="25" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>19</v>
       </c>
       <c r="N34" s="25" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12695,43 +12728,43 @@
         <v>21</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="L35" s="27" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="M35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="N35" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12739,43 +12772,43 @@
         <v>23</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="G36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="I36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="K36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M36" s="28" t="s">
         <v>23</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12783,43 +12816,43 @@
         <v>25</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="G37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L37" s="31" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="M37" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12827,7 +12860,7 @@
         <v>25</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>25</v>
@@ -12839,31 +12872,31 @@
         <v>25</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G38" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I38" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K38" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L38" s="31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="M38" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N38" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12933,25 +12966,25 @@
         <v>19</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C43" s="23" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E43" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>19</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="I43" s="23" t="s">
         <v>19</v>
@@ -12977,25 +13010,25 @@
         <v>21</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I44" s="26" t="s">
         <v>21</v>
@@ -13007,7 +13040,7 @@
         <v>21</v>
       </c>
       <c r="L44" s="27" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="M44" s="26" t="s">
         <v>21</v>
@@ -13021,43 +13054,43 @@
         <v>23</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="I45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="J45" s="29" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="K45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="29" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="M45" s="28" t="s">
         <v>23</v>
       </c>
       <c r="N45" s="29" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13065,43 +13098,43 @@
         <v>25</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="E46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="K46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="31" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="M46" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N46" s="31" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13109,43 +13142,43 @@
         <v>25</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="31" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="M47" s="30" t="s">
         <v>25</v>
       </c>
       <c r="N47" s="31" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13158,7 +13191,7 @@
       </c>
       <c r="D48" s="36"/>
       <c r="E48" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32" t="s">
@@ -13236,7 +13269,7 @@
         <v>21</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
@@ -13256,7 +13289,7 @@
         <v>23</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="20"/>
@@ -13276,7 +13309,7 @@
         <v>25</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
@@ -13296,7 +13329,7 @@
         <v>25</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
@@ -16087,11 +16120,11 @@
       </c>
       <c r="K3" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Rosario")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="62" t="n">
         <f aca="false">SUM(H3:K3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Rosario")</f>
@@ -16099,7 +16132,7 @@
       </c>
       <c r="N3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Rosario")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Rosario")</f>
@@ -16107,23 +16140,23 @@
       </c>
       <c r="P3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Rosario")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Rosario")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Rosario")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Rosario")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Rosario")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Rosario")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Rosario")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16154,11 +16187,11 @@
       </c>
       <c r="K4" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Cristina")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="62" t="n">
         <f aca="false">SUM(H4:K4)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Cristina")</f>
@@ -16170,7 +16203,7 @@
       </c>
       <c r="O4" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Cristina")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Cristina")</f>
@@ -16190,7 +16223,7 @@
       </c>
       <c r="T4" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Cristina")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Cristina")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Cristina")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16221,43 +16254,43 @@
       </c>
       <c r="K5" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Miriam")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" s="62" t="n">
         <f aca="false">SUM(H5:K5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Miriam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Miriam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Miriam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Miriam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Miriam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Miriam")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Miriam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Miriam")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Miriam")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Miriam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16288,39 +16321,39 @@
       </c>
       <c r="K6" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-David")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="62" t="n">
         <f aca="false">SUM(H6:K6)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-David")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-David")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-David")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-David")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-David")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-David")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-David")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-David")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-David")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-David")</f>
@@ -16355,11 +16388,11 @@
       </c>
       <c r="K7" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Mercedes")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" s="62" t="n">
         <f aca="false">SUM(H7:K7)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Mercedes")</f>
@@ -16371,11 +16404,11 @@
       </c>
       <c r="O7" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Mercedes")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Mercedes")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Mercedes")</f>
@@ -16422,11 +16455,11 @@
       </c>
       <c r="K8" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Arturo")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" s="62" t="n">
         <f aca="false">SUM(H8:K8)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Arturo")</f>
@@ -16434,27 +16467,27 @@
       </c>
       <c r="N8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Arturo")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Arturo")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Arturo")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Arturo")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Arturo")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Arturo")</f>
@@ -16489,11 +16522,11 @@
       </c>
       <c r="K9" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Aitor")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L9" s="62" t="n">
         <f aca="false">SUM(H9:K9)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Aitor")</f>
@@ -16501,15 +16534,15 @@
       </c>
       <c r="N9" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Aitor")</f>
@@ -16556,15 +16589,15 @@
       </c>
       <c r="K10" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Fatima")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" s="62" t="n">
         <f aca="false">SUM(H10:K10)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Fatima")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Fatima")</f>
@@ -16572,11 +16605,11 @@
       </c>
       <c r="O10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Fatima")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Fatima")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Fatima")</f>
@@ -16592,7 +16625,7 @@
       </c>
       <c r="T10" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Fatima")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Fatima")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Fatima")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16623,19 +16656,19 @@
       </c>
       <c r="J11" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Tania")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K11" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Tania")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="62" t="n">
         <f aca="false">SUM(H11:K11)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Tania")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Tania")</f>
@@ -16643,11 +16676,11 @@
       </c>
       <c r="O11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Tania")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Tania")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Tania")</f>
@@ -16663,7 +16696,7 @@
       </c>
       <c r="T11" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Tania")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Tania")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Tania")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16692,19 +16725,19 @@
       </c>
       <c r="J12" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Asis")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Asis")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L12" s="62" t="n">
         <f aca="false">SUM(H12:K12)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Asis")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Asis")</f>
@@ -16712,7 +16745,7 @@
       </c>
       <c r="O12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Asis")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Asis")</f>
@@ -16720,15 +16753,15 @@
       </c>
       <c r="Q12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Asis")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Asis")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Asis")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Asis")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Asis")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Asis")</f>
@@ -16763,19 +16796,19 @@
       </c>
       <c r="J13" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-PatriciaR2")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-PatriciaR2")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="62" t="n">
         <f aca="false">SUM(H13:K13)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-PatriciaR2")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-PatriciaR2")</f>
@@ -16783,11 +16816,11 @@
       </c>
       <c r="O13" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-PatriciaR2")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-PatriciaR2")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-PatriciaR2")</f>
@@ -16836,27 +16869,27 @@
       </c>
       <c r="K14" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Eva")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L14" s="62" t="n">
         <f aca="false">SUM(H14:K14)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Eva")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Eva")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Eva")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Eva")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Eva")</f>
@@ -16864,7 +16897,7 @@
       </c>
       <c r="R14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Eva")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Eva")</f>
@@ -16872,7 +16905,7 @@
       </c>
       <c r="T14" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Eva")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Eva")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Eva")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16901,7 +16934,7 @@
       </c>
       <c r="J15" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Emilio")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Emilio")</f>
@@ -16909,15 +16942,15 @@
       </c>
       <c r="L15" s="62" t="n">
         <f aca="false">SUM(H15:K15)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Emilio")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Emilio")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Emilio")</f>
@@ -16925,23 +16958,23 @@
       </c>
       <c r="P15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Emilio")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Emilio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Emilio")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Emilio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Emilio")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Emilio")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Emilio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16974,19 +17007,19 @@
       </c>
       <c r="K16" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Antonio")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L16" s="62" t="n">
         <f aca="false">SUM(H16:K16)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Antonio")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Antonio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Antonio")</f>
@@ -16994,23 +17027,23 @@
       </c>
       <c r="P16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Antonio")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Antonio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Antonio")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Antonio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Antonio")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Antonio")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Antonio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17039,43 +17072,43 @@
       </c>
       <c r="J17" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-AnaR2")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-AnaR2")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L17" s="62" t="n">
         <f aca="false">SUM(H17:K17)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-AnaR2")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-AnaR2")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-AnaR2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-AnaR2")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-AnaR2")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-AnaR2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-AnaR2")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-AnaR2")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-AnaR2")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-AnaR2")</f>
@@ -17110,23 +17143,23 @@
       </c>
       <c r="J18" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Marc")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Marc")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L18" s="62" t="n">
         <f aca="false">SUM(H18:K18)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M18" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Marc")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Marc")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Marc")</f>
@@ -17195,11 +17228,11 @@
       </c>
       <c r="N19" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-PatriciaR3")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-PatriciaR3")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-PatriciaR3")</f>
@@ -17408,11 +17441,11 @@
       </c>
       <c r="O22" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Tony")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Tony")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Tony")</f>
@@ -17479,11 +17512,11 @@
       </c>
       <c r="O23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Carlota")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Carlota")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Carlota")</f>
@@ -17526,7 +17559,7 @@
       </c>
       <c r="I24" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"TX-Almudena")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Almudena")</f>
@@ -17538,11 +17571,11 @@
       </c>
       <c r="L24" s="62" t="n">
         <f aca="false">SUM(H24:K24)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M24" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Almudena")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Almudena")</f>
@@ -17668,7 +17701,7 @@
       </c>
       <c r="I26" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"TX-Sandra")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" s="61" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"UCQ-Sandra")</f>
@@ -17680,23 +17713,23 @@
       </c>
       <c r="L26" s="62" t="n">
         <f aca="false">SUM(H26:K26)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Sandra")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Sandra")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Sandra")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Sandra")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Sandra")</f>
@@ -18123,43 +18156,43 @@
         <v>253</v>
       </c>
       <c r="O4" s="80" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P4" s="80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="80" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R4" s="80" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S4" s="81" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="T4" s="81" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="U4" s="80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="V4" s="80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W4" s="80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="X4" s="80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y4" s="80" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Z4" s="81" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA4" s="81" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AB4" s="80" t="s">
         <v>115</v>
@@ -19595,7 +19628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -19888,217 +19921,277 @@
         <v>310</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B22" s="103" t="s">
+        <v>312</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="103" t="s">
+        <v>271</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="103" t="s">
-        <v>311</v>
-      </c>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
+      <c r="A23" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="103" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B24" s="103" t="s">
+        <v>317</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="103" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="104" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="104"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="70" t="s">
         <v>262</v>
       </c>
-      <c r="B24" s="104" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="105" t="s">
-        <v>313</v>
-      </c>
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="78" t="s">
+      <c r="B27" s="105" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="106" t="s">
+        <v>321</v>
+      </c>
+      <c r="B30" s="106"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="106"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="78" t="s">
         <v>260</v>
       </c>
-      <c r="B28" s="78" t="s">
-        <v>314</v>
-      </c>
-      <c r="C28" s="78" t="s">
-        <v>315</v>
-      </c>
-      <c r="D28" s="78" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="96" t="s">
-        <v>317</v>
-      </c>
-      <c r="B29" s="106" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" s="107" t="n">
+      <c r="B31" s="78" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" s="78" t="s">
+        <v>323</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="96" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="107" t="s">
+        <v>326</v>
+      </c>
+      <c r="C32" s="108" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="108" t="n">
+      <c r="D32" s="109" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="100" t="s">
-        <v>319</v>
-      </c>
-      <c r="B30" s="109" t="s">
-        <v>320</v>
-      </c>
-      <c r="C30" s="110" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="100" t="s">
+        <v>327</v>
+      </c>
+      <c r="B33" s="110" t="s">
+        <v>328</v>
+      </c>
+      <c r="C33" s="111" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="108" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="96" t="s">
-        <v>321</v>
-      </c>
-      <c r="B31" s="106" t="s">
-        <v>322</v>
-      </c>
-      <c r="C31" s="107" t="n">
+      <c r="D33" s="109" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="96" t="s">
+        <v>329</v>
+      </c>
+      <c r="B34" s="107" t="s">
+        <v>330</v>
+      </c>
+      <c r="C34" s="108" t="n">
         <v>6</v>
       </c>
-      <c r="D31" s="108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="100" t="s">
-        <v>323</v>
-      </c>
-      <c r="B32" s="109" t="s">
-        <v>324</v>
-      </c>
-      <c r="C32" s="110" t="n">
+      <c r="D34" s="109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="100" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="110" t="s">
+        <v>332</v>
+      </c>
+      <c r="C35" s="111" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="108" t="n">
+      <c r="D35" s="109" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="96" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" s="107" t="s">
+        <v>334</v>
+      </c>
+      <c r="C36" s="108" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="96" t="s">
-        <v>325</v>
-      </c>
-      <c r="B33" s="106" t="s">
-        <v>326</v>
-      </c>
-      <c r="C33" s="107" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" s="108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="100"/>
-      <c r="B34" s="109"/>
-      <c r="C34" s="110"/>
-      <c r="D34" s="108"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="96" t="s">
-        <v>327</v>
-      </c>
-      <c r="B35" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="C35" s="107" t="n">
+      <c r="D36" s="109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="100"/>
+      <c r="B37" s="110"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="109"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="96" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" s="107" t="s">
+        <v>336</v>
+      </c>
+      <c r="C38" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="70" t="s">
+      <c r="D38" s="109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="70" t="s">
         <v>245</v>
       </c>
-      <c r="C36" s="70" t="n">
+      <c r="C39" s="70" t="n">
         <f aca="false">SUM(C29:C35)</f>
-        <v>39</v>
-      </c>
-      <c r="D36" s="70" t="n">
+        <v>32</v>
+      </c>
+      <c r="D39" s="70" t="n">
         <f aca="false">SUM(D29:D35)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="105" t="s">
-        <v>329</v>
-      </c>
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="B40" s="78" t="s">
-        <v>331</v>
-      </c>
-      <c r="C40" s="78" t="s">
-        <v>332</v>
-      </c>
-      <c r="D40" s="78" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B41" s="111" t="s">
-        <v>335</v>
-      </c>
-      <c r="C41" s="111" t="s">
-        <v>336</v>
-      </c>
-      <c r="D41" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="106" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="B42" s="106"/>
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+    </row>
+    <row r="43" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="78" t="s">
         <v>338</v>
       </c>
-      <c r="B42" s="111" t="s">
+      <c r="B43" s="78" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="111" t="s">
+      <c r="C43" s="78" t="s">
         <v>340</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="78" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B43" s="111" t="s">
+    <row r="44" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C43" s="111" t="s">
+      <c r="B44" s="103" t="s">
         <v>343</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>341</v>
+      <c r="C44" s="103" t="s">
+        <v>344</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B45" s="103" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" s="103" t="s">
+        <v>348</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B46" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="C46" s="103" t="s">
+        <v>351</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B47" s="103" t="s">
+        <v>353</v>
+      </c>
+      <c r="C47" s="103" t="s">
+        <v>354</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4:C21 B24" type="list">
@@ -20131,7 +20224,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20144,7 +20237,7 @@
         <v>176</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20155,7 +20248,7 @@
         <v>192</v>
       </c>
       <c r="C3" s="113" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20166,7 +20259,7 @@
         <v>195</v>
       </c>
       <c r="C4" s="114" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20177,7 +20270,7 @@
         <v>197</v>
       </c>
       <c r="C5" s="113" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20188,7 +20281,7 @@
         <v>200</v>
       </c>
       <c r="C6" s="114" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20199,7 +20292,7 @@
         <v>202</v>
       </c>
       <c r="C7" s="113" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20210,7 +20303,7 @@
         <v>204</v>
       </c>
       <c r="C8" s="114" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20221,7 +20314,7 @@
         <v>206</v>
       </c>
       <c r="C9" s="113" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20232,7 +20325,7 @@
         <v>208</v>
       </c>
       <c r="C10" s="114" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20254,7 +20347,7 @@
         <v>213</v>
       </c>
       <c r="C12" s="114" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20265,7 +20358,7 @@
         <v>216</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20276,7 +20369,7 @@
         <v>218</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20287,7 +20380,7 @@
         <v>220</v>
       </c>
       <c r="C15" s="113" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20298,7 +20391,7 @@
         <v>222</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20309,7 +20402,7 @@
         <v>224</v>
       </c>
       <c r="C17" s="113" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20320,7 +20413,7 @@
         <v>226</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20331,7 +20424,7 @@
         <v>228</v>
       </c>
       <c r="C19" s="113" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20342,7 +20435,7 @@
         <v>230</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20353,7 +20446,7 @@
         <v>232</v>
       </c>
       <c r="C21" s="113" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20364,7 +20457,7 @@
         <v>234</v>
       </c>
       <c r="C22" s="114" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20375,7 +20468,7 @@
         <v>236</v>
       </c>
       <c r="C23" s="113" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20386,7 +20479,7 @@
         <v>238</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20397,7 +20490,7 @@
         <v>240</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20408,7 +20501,7 @@
         <v>242</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20419,124 +20512,124 @@
         <v>244</v>
       </c>
       <c r="C27" s="113" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="105" t="s">
-        <v>365</v>
-      </c>
-      <c r="B29" s="105"/>
-      <c r="C29" s="105"/>
+      <c r="A29" s="106" t="s">
+        <v>377</v>
+      </c>
+      <c r="B29" s="106"/>
+      <c r="C29" s="106"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="78" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B30" s="78" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="115" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C31" s="115" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="115" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C32" s="115" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="115" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C33" s="115" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="115" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C34" s="115" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="115" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C35" s="115" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="115" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C36" s="115" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="115" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C37" s="115" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="115" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C38" s="115" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="115" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C39" s="115" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -20570,7 +20663,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20581,181 +20674,181 @@
         <v>176</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="96" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B3" s="116" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="100" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="96" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="100" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B6" s="118" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="96" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B7" s="116" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="D7" s="116" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="100" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="96" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B9" s="116" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D9" s="116" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="100" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B10" s="118" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D10" s="118" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="96" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B11" s="116" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D11" s="116" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="100" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B12" s="118" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="96" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B13" s="116" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D13" s="116" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="100" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B14" s="118" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="D14" s="118" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -20789,7 +20882,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20802,19 +20895,19 @@
         <v>176</v>
       </c>
       <c r="B2" s="121" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D2" s="121" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E2" s="121" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="F2" s="121" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="G2" s="121" t="s">
         <v>19</v>
@@ -20828,12 +20921,12 @@
         <v>191</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122"/>
       <c r="F3" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G3" s="122"/>
     </row>
@@ -20845,12 +20938,12 @@
         <v>194</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D4" s="123"/>
       <c r="E4" s="123"/>
       <c r="F4" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G4" s="123"/>
     </row>
@@ -20862,12 +20955,12 @@
         <v>196</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G5" s="122"/>
     </row>
@@ -20879,12 +20972,12 @@
         <v>199</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D6" s="123"/>
       <c r="E6" s="123"/>
       <c r="F6" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G6" s="123"/>
     </row>
@@ -20896,12 +20989,12 @@
         <v>201</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D7" s="122"/>
       <c r="E7" s="122"/>
       <c r="F7" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G7" s="122"/>
     </row>
@@ -20913,12 +21006,12 @@
         <v>203</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D8" s="123"/>
       <c r="E8" s="123"/>
       <c r="F8" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G8" s="123"/>
     </row>
@@ -20930,12 +21023,12 @@
         <v>205</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D9" s="122"/>
       <c r="E9" s="122"/>
       <c r="F9" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G9" s="122"/>
     </row>
@@ -20947,12 +21040,12 @@
         <v>207</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D10" s="123"/>
       <c r="E10" s="123"/>
       <c r="F10" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G10" s="123"/>
     </row>
@@ -20964,11 +21057,11 @@
         <v>209</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D11" s="122"/>
       <c r="E11" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F11" s="122"/>
       <c r="G11" s="122"/>
@@ -20981,14 +21074,14 @@
         <v>212</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D12" s="123"/>
       <c r="E12" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F12" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G12" s="123"/>
     </row>
@@ -21000,11 +21093,11 @@
         <v>215</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D13" s="122"/>
       <c r="E13" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F13" s="122"/>
       <c r="G13" s="122"/>
@@ -21017,14 +21110,14 @@
         <v>217</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D14" s="123"/>
       <c r="E14" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F14" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G14" s="123"/>
     </row>
@@ -21036,14 +21129,14 @@
         <v>219</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D15" s="122"/>
       <c r="E15" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F15" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G15" s="122"/>
     </row>
@@ -21055,14 +21148,14 @@
         <v>221</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D16" s="123"/>
       <c r="E16" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F16" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G16" s="123"/>
     </row>
@@ -21074,14 +21167,14 @@
         <v>223</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D17" s="122"/>
       <c r="E17" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F17" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G17" s="122"/>
     </row>
@@ -21093,14 +21186,14 @@
         <v>225</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D18" s="123"/>
       <c r="E18" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F18" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="G18" s="123"/>
     </row>
@@ -21112,10 +21205,10 @@
         <v>227</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D19" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E19" s="122"/>
       <c r="F19" s="122"/>
@@ -21129,10 +21222,10 @@
         <v>229</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D20" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E20" s="123"/>
       <c r="F20" s="123"/>
@@ -21146,11 +21239,11 @@
         <v>231</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D21" s="122"/>
       <c r="E21" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F21" s="122"/>
       <c r="G21" s="122"/>
@@ -21163,11 +21256,11 @@
         <v>233</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D22" s="123"/>
       <c r="E22" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F22" s="123"/>
       <c r="G22" s="123"/>
@@ -21180,15 +21273,15 @@
         <v>235</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D23" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E23" s="122"/>
       <c r="F23" s="122"/>
       <c r="G23" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21199,15 +21292,15 @@
         <v>237</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D24" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E24" s="123"/>
       <c r="F24" s="123"/>
       <c r="G24" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21218,15 +21311,15 @@
         <v>239</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D25" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E25" s="122"/>
       <c r="F25" s="122"/>
       <c r="G25" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21237,15 +21330,15 @@
         <v>241</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D26" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E26" s="123"/>
       <c r="F26" s="123"/>
       <c r="G26" s="123" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21256,20 +21349,20 @@
         <v>243</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D27" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E27" s="122"/>
       <c r="F27" s="122"/>
       <c r="G27" s="122" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="124" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B28" s="124"/>
       <c r="C28" s="124"/>
@@ -21280,121 +21373,121 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="125" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B29" s="126" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C29" s="125" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D29" s="125" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
       <c r="G29" s="125" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="125" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B30" s="126" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C30" s="125" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D30" s="125" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
       <c r="G30" s="125" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="125" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B31" s="126" t="s">
         <v>199</v>
       </c>
       <c r="C31" s="125" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D31" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E31" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F31" s="125"/>
       <c r="G31" s="125"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="125" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B32" s="126" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C32" s="125" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D32" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E32" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F32" s="125"/>
       <c r="G32" s="125"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="125" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B33" s="126" t="s">
+        <v>460</v>
+      </c>
+      <c r="C33" s="125" t="s">
         <v>448</v>
       </c>
-      <c r="C33" s="125" t="s">
-        <v>436</v>
-      </c>
       <c r="D33" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E33" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F33" s="125"/>
       <c r="G33" s="125"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B34" s="126" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C34" s="125" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D34" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E34" s="127" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F34" s="125"/>
       <c r="G34" s="125"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="128" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B37" s="128"/>
       <c r="C37" s="128"/>
@@ -21405,7 +21498,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="129" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B38" s="129"/>
       <c r="C38" s="129"/>

--- a/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
+++ b/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
@@ -879,7 +879,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="662">
   <si>
     <t xml:space="preserve">Cuadrante de Guardias — Servicio de Anestesiología y Reanimación</t>
   </si>
@@ -1846,7 +1846,7 @@
     <t xml:space="preserve">VEREDICTO GLOBAL: </t>
   </si>
   <si>
-    <t xml:space="preserve">VÁLIDO salvo 1 excepción documentada — MAY 9 y 11 oct sin cubrir (ver H-01/H-05). Todas las demás reglas H-01 a H-21: 0 violaciones, incluidos los nuevos topes de guardias totales (H-20) y fines de semana de R2 (H-21) confirmados el 2026-08-18.</t>
+    <t xml:space="preserve">VÁLIDO salvo 2 excepciones documentadas: (1) MAY 9 y 11 oct sin cubrir (ver H-01/H-05); (2) S-06 — 9 días con 2 R1 juntos en QX-P, mínimo matemáticamente forzado por H-20 (R2 exactamente 6). Pablo decidió el 2026-08-19 mantener H-20 sin relajar y aceptar los 9 días como excepción. Todas las demás reglas H-01 a H-21: 0 violaciones.</t>
   </si>
   <si>
     <t xml:space="preserve">Puntuación de reglas blandas S-01 a S-07 (0-41, ver fuente de la verdad §7 para el detalle de cada métrica)</t>
@@ -1891,6 +1891,12 @@
     <t xml:space="preserve">Separación mínima 3-4 días entre guardias</t>
   </si>
   <si>
+    <t xml:space="preserve">S-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evitar que los dos puestos de QX-P del mismo dia los cubran dos R1</t>
+  </si>
+  <si>
     <t xml:space="preserve">S-07</t>
   </si>
   <si>
@@ -1924,24 +1930,30 @@
     <t xml:space="preserve">Pendiente de Pablo</t>
   </si>
   <si>
+    <t xml:space="preserve">19/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-06 (evitar 2 R1 en PEQ el mismo dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con H-20 fijando R2 en exactamente 6, el reparto fuerza matematicamente un minimo de 9 dias con 2 R1 juntos en QX-P (ver fuente de la verdad SS13.2). Pablo elige mantener R2 en 6 exacto y aceptar los 9 dias como excepcion, en vez de relajar H-20 a un rango.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo (2026-08-19)</t>
+  </si>
+  <si>
     <t xml:space="preserve">todo el mes</t>
   </si>
   <si>
-    <t xml:space="preserve">S-06 (evitar 2 R1 en PEQ el mismo dia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aclaracion de Pablo aplicada como regla dura en el generador: 0 incidencias.</t>
+    <t xml:space="preserve">H-19 (sin TX la vispera de vacaciones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aclaracion de Pablo aplicada: 0 incidencias.</t>
   </si>
   <si>
     <t xml:space="preserve">Pablo (aclaracion previa)</t>
   </si>
   <si>
-    <t xml:space="preserve">H-19 (sin TX la vispera de vacaciones)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aclaracion de Pablo aplicada: 0 incidencias.</t>
-  </si>
-  <si>
     <t xml:space="preserve">18/08/2026</t>
   </si>
   <si>
@@ -2305,9 +2317,6 @@
     <t xml:space="preserve">Separación mínima 3-4 días entre guardias  (peso 5)</t>
   </si>
   <si>
-    <t xml:space="preserve">S-06</t>
-  </si>
-  <si>
     <t xml:space="preserve">Evitar coincidencias repetidas de los mismos 2 R1 en PEQ  (peso 2)</t>
   </si>
   <si>
@@ -2705,9 +2714,6 @@
   </si>
   <si>
     <t xml:space="preserve">17/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20/08/2026</t>
@@ -4727,13 +4733,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B1" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="130" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4882,7 +4888,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="130" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4890,7 +4896,7 @@
         <v>325</v>
       </c>
       <c r="B24" s="113" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4898,7 +4904,7 @@
         <v>327</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4906,7 +4912,7 @@
         <v>329</v>
       </c>
       <c r="B26" s="113" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4914,7 +4920,7 @@
         <v>331</v>
       </c>
       <c r="B27" s="114" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4922,23 +4928,23 @@
         <v>333</v>
       </c>
       <c r="B28" s="113" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="100" t="s">
-        <v>473</v>
+        <v>335</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="96" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B30" s="113" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -5071,7 +5077,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>49</v>
@@ -5082,7 +5088,7 @@
         <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5095,7 +5101,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5157,7 +5163,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -5174,7 +5180,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -5191,43 +5197,43 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B4" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="131" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F4" s="131" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L4" s="131" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M4" s="131" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5238,10 +5244,10 @@
         <v>192</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D5" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E5" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$506+'Histórico de guardias'!$E$506+'Histórico de guardias'!$F$506)+('Resumen de guardias'!$Q$3+'Resumen de guardias'!$R$3+'Resumen de guardias'!$S$3)</f>
@@ -5288,10 +5294,10 @@
         <v>195</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D6" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E6" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$507+'Histórico de guardias'!$E$507+'Histórico de guardias'!$F$507)+('Resumen de guardias'!$Q$4+'Resumen de guardias'!$R$4+'Resumen de guardias'!$S$4)</f>
@@ -5338,10 +5344,10 @@
         <v>197</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D7" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E7" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$508+'Histórico de guardias'!$E$508+'Histórico de guardias'!$F$508)+('Resumen de guardias'!$Q$5+'Resumen de guardias'!$R$5+'Resumen de guardias'!$S$5)</f>
@@ -5388,10 +5394,10 @@
         <v>200</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D8" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E8" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$509+'Histórico de guardias'!$E$509+'Histórico de guardias'!$F$509)+('Resumen de guardias'!$Q$6+'Resumen de guardias'!$R$6+'Resumen de guardias'!$S$6)</f>
@@ -5438,10 +5444,10 @@
         <v>202</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D9" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E9" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$510+'Histórico de guardias'!$E$510+'Histórico de guardias'!$F$510)+('Resumen de guardias'!$Q$7+'Resumen de guardias'!$R$7+'Resumen de guardias'!$S$7)</f>
@@ -5488,10 +5494,10 @@
         <v>204</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D10" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E10" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$511+'Histórico de guardias'!$E$511+'Histórico de guardias'!$F$511)+('Resumen de guardias'!$Q$8+'Resumen de guardias'!$R$8+'Resumen de guardias'!$S$8)</f>
@@ -5538,10 +5544,10 @@
         <v>206</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D11" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E11" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$512+'Histórico de guardias'!$E$512+'Histórico de guardias'!$F$512)+('Resumen de guardias'!$Q$9+'Resumen de guardias'!$R$9+'Resumen de guardias'!$S$9)</f>
@@ -5582,16 +5588,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="133" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D12" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E12" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$513+'Histórico de guardias'!$E$513+'Histórico de guardias'!$F$513)+('Resumen de guardias'!$Q$10+'Resumen de guardias'!$R$10+'Resumen de guardias'!$S$10)</f>
@@ -5638,10 +5644,10 @@
         <v>210</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D13" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E13" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$514+'Histórico de guardias'!$E$514+'Histórico de guardias'!$F$514)+('Resumen de guardias'!$Q$11+'Resumen de guardias'!$R$11+'Resumen de guardias'!$S$11)</f>
@@ -5682,16 +5688,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="133" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B14" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D14" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E14" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$515+'Histórico de guardias'!$E$515+'Histórico de guardias'!$F$515)+('Resumen de guardias'!$Q$12+'Resumen de guardias'!$R$12+'Resumen de guardias'!$S$12)</f>
@@ -5732,16 +5738,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="133" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B15" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D15" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E15" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$516+'Histórico de guardias'!$E$516+'Histórico de guardias'!$F$516)+('Resumen de guardias'!$Q$13+'Resumen de guardias'!$R$13+'Resumen de guardias'!$S$13)</f>
@@ -5788,10 +5794,10 @@
         <v>218</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D16" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E16" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$517+'Histórico de guardias'!$E$517+'Histórico de guardias'!$F$517)+('Resumen de guardias'!$Q$14+'Resumen de guardias'!$R$14+'Resumen de guardias'!$S$14)</f>
@@ -5838,10 +5844,10 @@
         <v>220</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D17" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E17" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$518+'Histórico de guardias'!$E$518+'Histórico de guardias'!$F$518)+('Resumen de guardias'!$Q$15+'Resumen de guardias'!$R$15+'Resumen de guardias'!$S$15)</f>
@@ -5888,10 +5894,10 @@
         <v>222</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D18" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E18" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$519+'Histórico de guardias'!$E$519+'Histórico de guardias'!$F$519)+('Resumen de guardias'!$Q$16+'Resumen de guardias'!$R$16+'Resumen de guardias'!$S$16)</f>
@@ -5932,16 +5938,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="133" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B19" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D19" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E19" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$520+'Histórico de guardias'!$E$520+'Histórico de guardias'!$F$520)+('Resumen de guardias'!$Q$17+'Resumen de guardias'!$R$17+'Resumen de guardias'!$S$17)</f>
@@ -5988,10 +5994,10 @@
         <v>226</v>
       </c>
       <c r="C20" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D20" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E20" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$521+'Histórico de guardias'!$E$521+'Histórico de guardias'!$F$521)+('Resumen de guardias'!$Q$18+'Resumen de guardias'!$R$18+'Resumen de guardias'!$S$18)</f>
@@ -6032,16 +6038,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="133" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B21" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C21" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D21" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E21" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$522+'Histórico de guardias'!$E$522+'Histórico de guardias'!$F$522)+('Resumen de guardias'!$Q$19+'Resumen de guardias'!$R$19+'Resumen de guardias'!$S$19)</f>
@@ -6088,10 +6094,10 @@
         <v>230</v>
       </c>
       <c r="C22" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D22" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E22" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$523+'Histórico de guardias'!$E$523+'Histórico de guardias'!$F$523)+('Resumen de guardias'!$Q$20+'Resumen de guardias'!$R$20+'Resumen de guardias'!$S$20)</f>
@@ -6132,16 +6138,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="133" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B23" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D23" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E23" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$524+'Histórico de guardias'!$E$524+'Histórico de guardias'!$F$524)+('Resumen de guardias'!$Q$21+'Resumen de guardias'!$R$21+'Resumen de guardias'!$S$21)</f>
@@ -6188,10 +6194,10 @@
         <v>234</v>
       </c>
       <c r="C24" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D24" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E24" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$525+'Histórico de guardias'!$E$525+'Histórico de guardias'!$F$525)+('Resumen de guardias'!$Q$22+'Resumen de guardias'!$R$22+'Resumen de guardias'!$S$22)</f>
@@ -6238,10 +6244,10 @@
         <v>236</v>
       </c>
       <c r="C25" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D25" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E25" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$526+'Histórico de guardias'!$E$526+'Histórico de guardias'!$F$526)+('Resumen de guardias'!$Q$23+'Resumen de guardias'!$R$23+'Resumen de guardias'!$S$23)</f>
@@ -6288,10 +6294,10 @@
         <v>238</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D26" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E26" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$527+'Histórico de guardias'!$E$527+'Histórico de guardias'!$F$527)+('Resumen de guardias'!$Q$24+'Resumen de guardias'!$R$24+'Resumen de guardias'!$S$24)</f>
@@ -6332,16 +6338,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="133" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B27" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D27" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E27" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$528+'Histórico de guardias'!$E$528+'Histórico de guardias'!$F$528)+('Resumen de guardias'!$Q$25+'Resumen de guardias'!$R$25+'Resumen de guardias'!$S$25)</f>
@@ -6388,10 +6394,10 @@
         <v>242</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D28" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E28" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$529+'Histórico de guardias'!$E$529+'Histórico de guardias'!$F$529)+('Resumen de guardias'!$Q$26+'Resumen de guardias'!$R$26+'Resumen de guardias'!$S$26)</f>
@@ -6438,10 +6444,10 @@
         <v>244</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D29" s="135" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E29" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$530+'Histórico de guardias'!$E$530+'Histórico de guardias'!$F$530)+('Resumen de guardias'!$Q$27+'Resumen de guardias'!$R$27+'Resumen de guardias'!$S$27)</f>
@@ -6482,16 +6488,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="137" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B30" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C30" s="138" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E30" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$531+'Histórico de guardias'!$E$531+'Histórico de guardias'!$F$531)+0</f>
@@ -6532,16 +6538,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="137" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B31" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C31" s="138" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D31" s="139" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E31" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$532+'Histórico de guardias'!$E$532+'Histórico de guardias'!$F$532)+0</f>
@@ -6582,16 +6588,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="137" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B32" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C32" s="138" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D32" s="139" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E32" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$533+'Histórico de guardias'!$E$533+'Histórico de guardias'!$F$533)+0</f>
@@ -6690,7 +6696,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -6705,7 +6711,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -6720,58 +6726,58 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B4" s="131" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C4" s="131" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F4" s="131" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B5" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="141" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D5" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E5" s="140"/>
       <c r="F5" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H5" s="141" t="s">
         <v>243</v>
@@ -6786,16 +6792,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B6" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="141" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D6" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E6" s="140"/>
       <c r="F6" s="141" t="s">
@@ -6805,7 +6811,7 @@
         <v>225</v>
       </c>
       <c r="H6" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I6" s="141" t="s">
         <v>231</v>
@@ -6817,16 +6823,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B7" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="141" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D7" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E7" s="140"/>
       <c r="F7" s="141" t="s">
@@ -6848,23 +6854,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B8" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="141" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D8" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E8" s="140"/>
       <c r="F8" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G8" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H8" s="141" t="s">
         <v>241</v>
@@ -6879,29 +6885,29 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B9" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="141" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D9" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E9" s="140"/>
       <c r="F9" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G9" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H9" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I9" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J9" s="141" t="s">
         <v>212</v>
@@ -6910,23 +6916,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B10" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="143" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D10" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E10" s="142"/>
       <c r="F10" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G10" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H10" s="143" t="s">
         <v>237</v>
@@ -6941,20 +6947,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B11" s="143" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="143" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D11" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E11" s="142"/>
       <c r="F11" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G11" s="143" t="s">
         <v>221</v>
@@ -6972,23 +6978,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B12" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C12" s="141" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D12" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E12" s="140"/>
       <c r="F12" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H12" s="141" t="s">
         <v>235</v>
@@ -7003,16 +7009,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B13" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="141" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D13" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E13" s="140"/>
       <c r="F13" s="141" t="s">
@@ -7025,7 +7031,7 @@
         <v>241</v>
       </c>
       <c r="I13" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J13" s="141" t="s">
         <v>209</v>
@@ -7034,26 +7040,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B14" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="141" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D14" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E14" s="140"/>
       <c r="F14" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G14" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H14" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I14" s="141" t="s">
         <v>233</v>
@@ -7065,16 +7071,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B15" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="141" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D15" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="141" t="s">
@@ -7087,7 +7093,7 @@
         <v>237</v>
       </c>
       <c r="I15" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J15" s="141" t="s">
         <v>212</v>
@@ -7096,23 +7102,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B16" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="141" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D16" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E16" s="140"/>
       <c r="F16" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G16" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H16" s="141" t="s">
         <v>235</v>
@@ -7127,16 +7133,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B17" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="143" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D17" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E17" s="142"/>
       <c r="F17" s="143" t="s">
@@ -7158,23 +7164,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B18" s="143" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="143" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D18" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E18" s="142"/>
       <c r="F18" s="143" t="s">
         <v>243</v>
       </c>
       <c r="G18" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H18" s="143" t="s">
         <v>235</v>
@@ -7189,29 +7195,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B19" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E19" s="140"/>
       <c r="F19" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H19" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J19" s="141" t="s">
         <v>217</v>
@@ -7220,16 +7226,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B20" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="141" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D20" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E20" s="140"/>
       <c r="F20" s="141" t="s">
@@ -7245,22 +7251,22 @@
         <v>235</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K20" s="141"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B21" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="141" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D21" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E21" s="140"/>
       <c r="F21" s="141" t="s">
@@ -7282,23 +7288,23 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B22" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E22" s="140"/>
       <c r="F22" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G22" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H22" s="141" t="s">
         <v>231</v>
@@ -7313,16 +7319,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B23" s="141" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E23" s="140"/>
       <c r="F23" s="141" t="s">
@@ -7338,22 +7344,22 @@
         <v>229</v>
       </c>
       <c r="J23" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K23" s="141"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B24" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D24" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E24" s="142"/>
       <c r="F24" s="143" t="s">
@@ -7375,16 +7381,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B25" s="143" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="143" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D25" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E25" s="142"/>
       <c r="F25" s="143" t="s">
@@ -7400,26 +7406,26 @@
         <v>229</v>
       </c>
       <c r="J25" s="143" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B26" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="141" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E26" s="140"/>
       <c r="F26" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G26" s="141" t="s">
         <v>209</v>
@@ -7428,7 +7434,7 @@
         <v>235</v>
       </c>
       <c r="I26" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J26" s="141" t="s">
         <v>225</v>
@@ -7437,16 +7443,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B27" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="141" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E27" s="140"/>
       <c r="F27" s="141" t="s">
@@ -7462,22 +7468,22 @@
         <v>231</v>
       </c>
       <c r="J27" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K27" s="141"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B28" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="141" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E28" s="140"/>
       <c r="F28" s="141" t="s">
@@ -7499,16 +7505,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B29" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="141" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E29" s="140"/>
       <c r="F29" s="141" t="s">
@@ -7530,23 +7536,23 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B30" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E30" s="140"/>
       <c r="F30" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G30" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H30" s="141" t="s">
         <v>241</v>
@@ -7555,22 +7561,22 @@
         <v>233</v>
       </c>
       <c r="J30" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K30" s="141"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B31" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="143" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D31" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E31" s="142"/>
       <c r="F31" s="143" t="s">
@@ -7583,25 +7589,25 @@
         <v>235</v>
       </c>
       <c r="I31" s="143" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J31" s="143" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K31" s="143"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="142" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B32" s="143" t="n">
         <v>28</v>
       </c>
       <c r="C32" s="143" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D32" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E32" s="142"/>
       <c r="F32" s="143" t="s">
@@ -7617,35 +7623,35 @@
         <v>233</v>
       </c>
       <c r="J32" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K32" s="143"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B33" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C33" s="141" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E33" s="140"/>
       <c r="F33" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G33" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H33" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I33" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J33" s="141" t="s">
         <v>209</v>
@@ -7656,29 +7662,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="140" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B34" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="141" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D34" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E34" s="140"/>
       <c r="F34" s="141" t="s">
+        <v>522</v>
+      </c>
+      <c r="G34" s="141" t="s">
         <v>519</v>
-      </c>
-      <c r="G34" s="141" t="s">
-        <v>516</v>
       </c>
       <c r="H34" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I34" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J34" s="141" t="s">
         <v>229</v>
@@ -7687,26 +7693,26 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B35" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="141" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D35" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E35" s="140"/>
       <c r="F35" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G35" s="141" t="s">
         <v>221</v>
       </c>
       <c r="H35" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I35" s="141" t="s">
         <v>231</v>
@@ -7718,54 +7724,54 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B36" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="141" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D36" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E36" s="140"/>
       <c r="F36" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G36" s="141" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I36" s="141" t="s">
         <v>243</v>
       </c>
       <c r="J36" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K36" s="141"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B37" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="141" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D37" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E37" s="140"/>
       <c r="F37" s="141" t="s">
+        <v>522</v>
+      </c>
+      <c r="G37" s="141" t="s">
         <v>519</v>
-      </c>
-      <c r="G37" s="141" t="s">
-        <v>516</v>
       </c>
       <c r="H37" s="141" t="s">
         <v>241</v>
@@ -7780,20 +7786,20 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B38" s="143" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="143" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D38" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E38" s="142"/>
       <c r="F38" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G38" s="143" t="s">
         <v>225</v>
@@ -7811,29 +7817,29 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B39" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C39" s="143" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D39" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E39" s="142"/>
       <c r="F39" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G39" s="143" t="s">
         <v>229</v>
       </c>
       <c r="H39" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I39" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J39" s="143" t="s">
         <v>212</v>
@@ -7842,16 +7848,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B40" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C40" s="141" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D40" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E40" s="140"/>
       <c r="F40" s="141" t="s">
@@ -7873,26 +7879,26 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B41" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C41" s="141" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D41" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E41" s="140"/>
       <c r="F41" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G41" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H41" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I41" s="141" t="s">
         <v>219</v>
@@ -7904,16 +7910,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B42" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C42" s="141" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D42" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E42" s="140"/>
       <c r="F42" s="141" t="s">
@@ -7929,22 +7935,22 @@
         <v>209</v>
       </c>
       <c r="J42" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K42" s="141"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B43" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C43" s="141" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D43" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E43" s="140"/>
       <c r="F43" s="141" t="s">
@@ -7954,7 +7960,7 @@
         <v>221</v>
       </c>
       <c r="H43" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I43" s="141" t="s">
         <v>217</v>
@@ -7966,20 +7972,20 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B44" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C44" s="141" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D44" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E44" s="140"/>
       <c r="F44" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G44" s="141" t="s">
         <v>229</v>
@@ -7988,7 +7994,7 @@
         <v>233</v>
       </c>
       <c r="I44" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J44" s="141" t="s">
         <v>212</v>
@@ -7997,16 +8003,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B45" s="143" t="n">
         <v>11</v>
       </c>
       <c r="C45" s="143" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D45" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E45" s="142"/>
       <c r="F45" s="143" t="s">
@@ -8016,7 +8022,7 @@
         <v>221</v>
       </c>
       <c r="H45" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I45" s="143" t="s">
         <v>217</v>
@@ -8028,26 +8034,26 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B46" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C46" s="143" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D46" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E46" s="142"/>
       <c r="F46" s="143" t="s">
         <v>241</v>
       </c>
       <c r="G46" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H46" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I46" s="143" t="s">
         <v>237</v>
@@ -8059,20 +8065,20 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B47" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C47" s="141" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D47" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E47" s="140"/>
       <c r="F47" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G47" s="141" t="s">
         <v>221</v>
@@ -8084,22 +8090,22 @@
         <v>217</v>
       </c>
       <c r="J47" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K47" s="141"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B48" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="141" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D48" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E48" s="140"/>
       <c r="F48" s="141" t="s">
@@ -8109,10 +8115,10 @@
         <v>212</v>
       </c>
       <c r="H48" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I48" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J48" s="141" t="s">
         <v>219</v>
@@ -8121,20 +8127,20 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B49" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="141" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D49" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E49" s="140"/>
       <c r="F49" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G49" s="141" t="s">
         <v>221</v>
@@ -8152,20 +8158,20 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B50" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C50" s="141" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D50" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E50" s="140"/>
       <c r="F50" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G50" s="141" t="s">
         <v>225</v>
@@ -8174,35 +8180,35 @@
         <v>235</v>
       </c>
       <c r="I50" s="141" t="s">
+        <v>530</v>
+      </c>
+      <c r="J50" s="141" t="s">
         <v>527</v>
-      </c>
-      <c r="J50" s="141" t="s">
-        <v>524</v>
       </c>
       <c r="K50" s="141"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B51" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C51" s="141" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D51" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E51" s="140"/>
       <c r="F51" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G51" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H51" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I51" s="141" t="s">
         <v>241</v>
@@ -8214,20 +8220,20 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B52" s="143" t="n">
         <v>18</v>
       </c>
       <c r="C52" s="143" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D52" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E52" s="142"/>
       <c r="F52" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G52" s="143" t="s">
         <v>225</v>
@@ -8236,25 +8242,25 @@
         <v>235</v>
       </c>
       <c r="I52" s="143" t="s">
+        <v>530</v>
+      </c>
+      <c r="J52" s="143" t="s">
         <v>527</v>
-      </c>
-      <c r="J52" s="143" t="s">
-        <v>524</v>
       </c>
       <c r="K52" s="143"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B53" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C53" s="143" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D53" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E53" s="142"/>
       <c r="F53" s="143" t="s">
@@ -8276,26 +8282,26 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B54" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C54" s="141" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D54" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E54" s="140"/>
       <c r="F54" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G54" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H54" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I54" s="141" t="s">
         <v>237</v>
@@ -8307,20 +8313,20 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B55" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C55" s="141" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D55" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E55" s="140"/>
       <c r="F55" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G55" s="141" t="s">
         <v>225</v>
@@ -8338,47 +8344,47 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B56" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C56" s="141" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D56" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E56" s="140"/>
       <c r="F56" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G56" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H56" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I56" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J56" s="141" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K56" s="141"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B57" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C57" s="141" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D57" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E57" s="140"/>
       <c r="F57" s="141" t="s">
@@ -8388,7 +8394,7 @@
         <v>229</v>
       </c>
       <c r="H57" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I57" s="141" t="s">
         <v>233</v>
@@ -8400,16 +8406,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B58" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C58" s="141" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D58" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E58" s="140"/>
       <c r="F58" s="141" t="s">
@@ -8422,7 +8428,7 @@
         <v>235</v>
       </c>
       <c r="I58" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J58" s="141" t="s">
         <v>212</v>
@@ -8431,16 +8437,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B59" s="143" t="n">
         <v>25</v>
       </c>
       <c r="C59" s="143" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D59" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E59" s="142"/>
       <c r="F59" s="143" t="s">
@@ -8462,16 +8468,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B60" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C60" s="143" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D60" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E60" s="142"/>
       <c r="F60" s="143" t="s">
@@ -8487,22 +8493,22 @@
         <v>243</v>
       </c>
       <c r="J60" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K60" s="143"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B61" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="141" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D61" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E61" s="140"/>
       <c r="F61" s="141" t="s">
@@ -8512,28 +8518,28 @@
         <v>229</v>
       </c>
       <c r="H61" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I61" s="141" t="s">
         <v>233</v>
       </c>
       <c r="J61" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K61" s="141"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B62" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C62" s="141" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D62" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E62" s="140"/>
       <c r="F62" s="141" t="s">
@@ -8549,29 +8555,29 @@
         <v>212</v>
       </c>
       <c r="J62" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K62" s="141"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B63" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C63" s="141" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D63" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E63" s="140"/>
       <c r="F63" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G63" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H63" s="141" t="s">
         <v>243</v>
@@ -8586,16 +8592,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="140" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B64" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C64" s="141" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D64" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E64" s="140"/>
       <c r="F64" s="141" t="s">
@@ -8617,16 +8623,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B65" s="143" t="n">
         <v>1</v>
       </c>
       <c r="C65" s="143" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D65" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E65" s="142"/>
       <c r="F65" s="143" t="s">
@@ -8639,23 +8645,23 @@
         <v>237</v>
       </c>
       <c r="I65" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J65" s="143"/>
       <c r="K65" s="143"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B66" s="143" t="n">
         <v>2</v>
       </c>
       <c r="C66" s="143" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D66" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E66" s="142"/>
       <c r="F66" s="143" t="s">
@@ -8677,16 +8683,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B67" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="141" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D67" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E67" s="140"/>
       <c r="F67" s="141" t="s">
@@ -8706,20 +8712,20 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B68" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C68" s="141" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D68" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E68" s="140"/>
       <c r="F68" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G68" s="141" t="s">
         <v>229</v>
@@ -8728,25 +8734,25 @@
         <v>231</v>
       </c>
       <c r="I68" s="141" t="s">
+        <v>530</v>
+      </c>
+      <c r="J68" s="141" t="s">
         <v>527</v>
-      </c>
-      <c r="J68" s="141" t="s">
-        <v>524</v>
       </c>
       <c r="K68" s="141"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B69" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C69" s="141" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D69" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E69" s="140"/>
       <c r="F69" s="141" t="s">
@@ -8756,7 +8762,7 @@
         <v>229</v>
       </c>
       <c r="H69" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I69" s="141" t="s">
         <v>235</v>
@@ -8766,23 +8772,23 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B70" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="141" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E70" s="140"/>
       <c r="F70" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G70" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H70" s="141" t="s">
         <v>241</v>
@@ -8797,16 +8803,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B71" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="141" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D71" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E71" s="140"/>
       <c r="F71" s="141" t="s">
@@ -8816,10 +8822,10 @@
         <v>219</v>
       </c>
       <c r="H71" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I71" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J71" s="141" t="s">
         <v>212</v>
@@ -8828,16 +8834,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B72" s="143" t="n">
         <v>8</v>
       </c>
       <c r="C72" s="143" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D72" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E72" s="142"/>
       <c r="F72" s="143" t="s">
@@ -8847,7 +8853,7 @@
         <v>225</v>
       </c>
       <c r="H72" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I72" s="143" t="s">
         <v>231</v>
@@ -8857,16 +8863,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B73" s="143" t="n">
         <v>9</v>
       </c>
       <c r="C73" s="143" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D73" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E73" s="142"/>
       <c r="F73" s="143" t="s">
@@ -8876,10 +8882,10 @@
         <v>219</v>
       </c>
       <c r="H73" s="143" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I73" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J73" s="143" t="s">
         <v>212</v>
@@ -8888,20 +8894,20 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B74" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C74" s="141" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D74" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E74" s="140"/>
       <c r="F74" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G74" s="141" t="s">
         <v>229</v>
@@ -8919,20 +8925,20 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B75" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C75" s="141" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D75" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E75" s="140"/>
       <c r="F75" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G75" s="141" t="s">
         <v>209</v>
@@ -8950,20 +8956,20 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B76" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C76" s="141" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D76" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E76" s="140"/>
       <c r="F76" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G76" s="141" t="s">
         <v>229</v>
@@ -8972,7 +8978,7 @@
         <v>241</v>
       </c>
       <c r="I76" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J76" s="141" t="s">
         <v>212</v>
@@ -8981,26 +8987,26 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B77" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C77" s="141" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D77" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E77" s="140"/>
       <c r="F77" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G77" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H77" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I77" s="141" t="s">
         <v>219</v>
@@ -9012,20 +9018,20 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B78" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C78" s="141" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D78" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E78" s="140"/>
       <c r="F78" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G78" s="141" t="s">
         <v>229</v>
@@ -9043,22 +9049,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="144" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B79" s="145" t="n">
         <v>15</v>
       </c>
       <c r="C79" s="145" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D79" s="145" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E79" s="144" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F79" s="145" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G79" s="145" t="s">
         <v>243</v>
@@ -9074,16 +9080,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B80" s="143" t="n">
         <v>16</v>
       </c>
       <c r="C80" s="143" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D80" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E80" s="142"/>
       <c r="F80" s="143" t="s">
@@ -9105,57 +9111,57 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B81" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C81" s="141" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D81" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E81" s="140"/>
       <c r="F81" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G81" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H81" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I81" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J81" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K81" s="141"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B82" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C82" s="141" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D82" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E82" s="140"/>
       <c r="F82" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G82" s="141" t="s">
         <v>243</v>
       </c>
       <c r="H82" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I82" s="141" t="s">
         <v>209</v>
@@ -9167,16 +9173,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B83" s="141" t="n">
         <v>19</v>
       </c>
       <c r="C83" s="141" t="s">
-        <v>607</v>
+        <v>348</v>
       </c>
       <c r="D83" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E83" s="140"/>
       <c r="F83" s="141" t="s">
@@ -9189,25 +9195,25 @@
         <v>231</v>
       </c>
       <c r="I83" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J83" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K83" s="141"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B84" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C84" s="141" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D84" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E84" s="140"/>
       <c r="F84" s="141" t="s">
@@ -9217,10 +9223,10 @@
         <v>221</v>
       </c>
       <c r="H84" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I84" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J84" s="141" t="s">
         <v>233</v>
@@ -9229,20 +9235,20 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B85" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="141" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D85" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E85" s="140"/>
       <c r="F85" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G85" s="141" t="s">
         <v>225</v>
@@ -9260,20 +9266,20 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B86" s="143" t="n">
         <v>22</v>
       </c>
       <c r="C86" s="143" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D86" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E86" s="142"/>
       <c r="F86" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G86" s="143" t="s">
         <v>243</v>
@@ -9282,27 +9288,27 @@
         <v>233</v>
       </c>
       <c r="I86" s="143" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J86" s="143"/>
       <c r="K86" s="143"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B87" s="143" t="n">
         <v>23</v>
       </c>
       <c r="C87" s="143" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D87" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E87" s="142"/>
       <c r="F87" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G87" s="143" t="s">
         <v>225</v>
@@ -9320,20 +9326,20 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B88" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C88" s="141" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D88" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E88" s="140"/>
       <c r="F88" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G88" s="141" t="s">
         <v>229</v>
@@ -9342,25 +9348,25 @@
         <v>237</v>
       </c>
       <c r="I88" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J88" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K88" s="141"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B89" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C89" s="141" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D89" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E89" s="140"/>
       <c r="F89" s="141" t="s">
@@ -9370,7 +9376,7 @@
         <v>212</v>
       </c>
       <c r="H89" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I89" s="141" t="s">
         <v>233</v>
@@ -9382,16 +9388,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B90" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C90" s="141" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D90" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E90" s="140"/>
       <c r="F90" s="141" t="s">
@@ -9401,41 +9407,41 @@
         <v>225</v>
       </c>
       <c r="H90" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I90" s="141" t="s">
         <v>221</v>
       </c>
       <c r="J90" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K90" s="141"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B91" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C91" s="141" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D91" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E91" s="140"/>
       <c r="F91" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G91" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H91" s="141" t="s">
         <v>231</v>
       </c>
       <c r="I91" s="141" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J91" s="141" t="s">
         <v>217</v>
@@ -9444,16 +9450,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B92" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C92" s="141" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D92" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E92" s="140"/>
       <c r="F92" s="141" t="s">
@@ -9466,25 +9472,25 @@
         <v>237</v>
       </c>
       <c r="I92" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J92" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K92" s="141"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B93" s="143" t="n">
         <v>29</v>
       </c>
       <c r="C93" s="143" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D93" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E93" s="142"/>
       <c r="F93" s="143" t="s">
@@ -9494,61 +9500,61 @@
         <v>221</v>
       </c>
       <c r="H93" s="143" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I93" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J93" s="143"/>
       <c r="K93" s="143"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="142" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B94" s="143" t="n">
         <v>30</v>
       </c>
       <c r="C94" s="143" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D94" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E94" s="142"/>
       <c r="F94" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G94" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H94" s="143" t="s">
         <v>237</v>
       </c>
       <c r="I94" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J94" s="143" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K94" s="143"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="140" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B95" s="141" t="n">
         <v>31</v>
       </c>
       <c r="C95" s="141" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D95" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E95" s="140"/>
       <c r="F95" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G95" s="141" t="s">
         <v>243</v>
@@ -9566,23 +9572,23 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B96" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="141" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D96" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E96" s="140"/>
       <c r="F96" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G96" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H96" s="141" t="s">
         <v>233</v>
@@ -9597,23 +9603,23 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B97" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C97" s="141" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D97" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E97" s="140"/>
       <c r="F97" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G97" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H97" s="141" t="s">
         <v>237</v>
@@ -9628,16 +9634,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B98" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C98" s="141" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D98" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E98" s="140"/>
       <c r="F98" s="141" t="s">
@@ -9647,10 +9653,10 @@
         <v>217</v>
       </c>
       <c r="H98" s="141" t="s">
+        <v>522</v>
+      </c>
+      <c r="I98" s="141" t="s">
         <v>519</v>
-      </c>
-      <c r="I98" s="141" t="s">
-        <v>516</v>
       </c>
       <c r="J98" s="141" t="s">
         <v>191</v>
@@ -9659,16 +9665,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B99" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C99" s="141" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D99" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E99" s="140"/>
       <c r="F99" s="141" t="s">
@@ -9681,7 +9687,7 @@
         <v>229</v>
       </c>
       <c r="I99" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J99" s="141" t="s">
         <v>194</v>
@@ -9690,20 +9696,20 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B100" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C100" s="143" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D100" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E100" s="142"/>
       <c r="F100" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G100" s="143" t="s">
         <v>221</v>
@@ -9721,16 +9727,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B101" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C101" s="143" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D101" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E101" s="142"/>
       <c r="F101" s="143" t="s">
@@ -9743,7 +9749,7 @@
         <v>229</v>
       </c>
       <c r="I101" s="143" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J101" s="143" t="s">
         <v>194</v>
@@ -9752,20 +9758,20 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B102" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C102" s="141" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D102" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E102" s="140"/>
       <c r="F102" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G102" s="141" t="s">
         <v>212</v>
@@ -9783,29 +9789,29 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B103" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C103" s="141" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D103" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E103" s="140"/>
       <c r="F103" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G103" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H103" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I103" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J103" s="141" t="s">
         <v>217</v>
@@ -9814,20 +9820,20 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B104" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C104" s="141" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D104" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E104" s="140"/>
       <c r="F104" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G104" s="141" t="s">
         <v>209</v>
@@ -9836,7 +9842,7 @@
         <v>243</v>
       </c>
       <c r="I104" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J104" s="141" t="s">
         <v>219</v>
@@ -9845,26 +9851,26 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B105" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C105" s="141" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D105" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G105" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H105" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I105" s="141" t="s">
         <v>212</v>
@@ -9876,20 +9882,20 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B106" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C106" s="141" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D106" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E106" s="140"/>
       <c r="F106" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G106" s="141" t="s">
         <v>231</v>
@@ -9898,7 +9904,7 @@
         <v>233</v>
       </c>
       <c r="I106" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J106" s="141" t="s">
         <v>207</v>
@@ -9907,20 +9913,20 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B107" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C107" s="143" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D107" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E107" s="142"/>
       <c r="F107" s="143" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G107" s="143" t="s">
         <v>212</v>
@@ -9938,20 +9944,20 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B108" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C108" s="143" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D108" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E108" s="142"/>
       <c r="F108" s="143" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G108" s="143" t="s">
         <v>231</v>
@@ -9960,7 +9966,7 @@
         <v>233</v>
       </c>
       <c r="I108" s="143" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J108" s="143" t="s">
         <v>207</v>
@@ -9969,23 +9975,23 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B109" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C109" s="141" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D109" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E109" s="140"/>
       <c r="F109" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G109" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H109" s="141" t="s">
         <v>229</v>
@@ -10000,16 +10006,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B110" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C110" s="141" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D110" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E110" s="140"/>
       <c r="F110" s="141" t="s">
@@ -10022,7 +10028,7 @@
         <v>237</v>
       </c>
       <c r="I110" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J110" s="141" t="s">
         <v>225</v>
@@ -10031,26 +10037,26 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B111" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C111" s="141" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D111" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E111" s="140"/>
       <c r="F111" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G111" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H111" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I111" s="141" t="s">
         <v>212</v>
@@ -10062,16 +10068,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B112" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C112" s="141" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D112" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E112" s="140"/>
       <c r="F112" s="141" t="s">
@@ -10081,7 +10087,7 @@
         <v>231</v>
       </c>
       <c r="H112" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I112" s="141" t="s">
         <v>217</v>
@@ -10093,23 +10099,23 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B113" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C113" s="141" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D113" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E113" s="140"/>
       <c r="F113" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G113" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H113" s="141" t="s">
         <v>229</v>
@@ -10118,26 +10124,26 @@
         <v>221</v>
       </c>
       <c r="J113" s="141" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K113" s="141"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B114" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C114" s="143" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D114" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E114" s="142"/>
       <c r="F114" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G114" s="143" t="s">
         <v>209</v>
@@ -10155,23 +10161,23 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B115" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C115" s="143" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D115" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E115" s="142"/>
       <c r="F115" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G115" s="143" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H115" s="143" t="s">
         <v>229</v>
@@ -10180,22 +10186,22 @@
         <v>221</v>
       </c>
       <c r="J115" s="143" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K115" s="143"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B116" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C116" s="141" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D116" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E116" s="140"/>
       <c r="F116" s="141" t="s">
@@ -10217,20 +10223,20 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B117" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C117" s="141" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D117" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E117" s="140"/>
       <c r="F117" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G117" s="141" t="s">
         <v>209</v>
@@ -10248,29 +10254,29 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B118" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C118" s="141" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D118" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E118" s="140"/>
       <c r="F118" s="141" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G118" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H118" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I118" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J118" s="141" t="s">
         <v>196</v>
@@ -10279,16 +10285,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B119" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C119" s="141" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D119" s="141" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E119" s="140"/>
       <c r="F119" s="141" t="s">
@@ -10301,7 +10307,7 @@
         <v>233</v>
       </c>
       <c r="I119" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J119" s="141" t="s">
         <v>203</v>
@@ -10310,16 +10316,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B120" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C120" s="141" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D120" s="141" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E120" s="140"/>
       <c r="F120" s="141" t="s">
@@ -10329,7 +10335,7 @@
         <v>219</v>
       </c>
       <c r="H120" s="141" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I120" s="141" t="s">
         <v>205</v>
@@ -10341,16 +10347,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B121" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C121" s="143" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D121" s="143" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E121" s="142"/>
       <c r="F121" s="143" t="s">
@@ -10360,7 +10366,7 @@
         <v>231</v>
       </c>
       <c r="H121" s="143" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I121" s="143" t="s">
         <v>212</v>
@@ -10372,16 +10378,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="142" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B122" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C122" s="143" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D122" s="143" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E122" s="142"/>
       <c r="F122" s="143" t="s">
@@ -10391,7 +10397,7 @@
         <v>219</v>
       </c>
       <c r="H122" s="143" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I122" s="143" t="s">
         <v>205</v>
@@ -10403,29 +10409,29 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B123" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C123" s="141" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D123" s="141" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E123" s="140"/>
       <c r="F123" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G123" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H123" s="141" t="s">
         <v>229</v>
       </c>
       <c r="I123" s="141" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J123" s="141" t="s">
         <v>221</v>
@@ -10434,16 +10440,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B124" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C124" s="141" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D124" s="141" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E124" s="140"/>
       <c r="F124" s="141" t="s">
@@ -10453,7 +10459,7 @@
         <v>209</v>
       </c>
       <c r="H124" s="141" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I124" s="141" t="s">
         <v>225</v>
@@ -10465,16 +10471,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="140" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B125" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C125" s="141" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D125" s="141" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E125" s="140"/>
       <c r="F125" s="141" t="s">
@@ -10487,16 +10493,16 @@
         <v>243</v>
       </c>
       <c r="I125" s="141" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J125" s="141" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K125" s="141"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="131" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B504" s="131"/>
       <c r="C504" s="131"/>
@@ -10512,37 +10518,37 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="131" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B505" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C505" s="131" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D505" s="131" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E505" s="131" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F505" s="131" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G505" s="131" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H505" s="131" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I505" s="131" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="J505" s="131" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K505" s="131" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10553,7 +10559,7 @@
         <v>192</v>
       </c>
       <c r="C506" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D506" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
@@ -10596,7 +10602,7 @@
         <v>195</v>
       </c>
       <c r="C507" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D507" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
@@ -10639,7 +10645,7 @@
         <v>197</v>
       </c>
       <c r="C508" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D508" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
@@ -10682,7 +10688,7 @@
         <v>200</v>
       </c>
       <c r="C509" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D509" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
@@ -10725,7 +10731,7 @@
         <v>202</v>
       </c>
       <c r="C510" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D510" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
@@ -10768,7 +10774,7 @@
         <v>204</v>
       </c>
       <c r="C511" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D511" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
@@ -10811,7 +10817,7 @@
         <v>206</v>
       </c>
       <c r="C512" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D512" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
@@ -10848,13 +10854,13 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="133" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B513" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C513" s="134" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D513" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
@@ -10897,7 +10903,7 @@
         <v>210</v>
       </c>
       <c r="C514" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D514" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
@@ -10934,13 +10940,13 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="133" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B515" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C515" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D515" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
@@ -10977,13 +10983,13 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="133" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B516" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C516" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D516" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
@@ -11026,7 +11032,7 @@
         <v>218</v>
       </c>
       <c r="C517" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D517" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
@@ -11069,7 +11075,7 @@
         <v>220</v>
       </c>
       <c r="C518" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D518" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
@@ -11112,7 +11118,7 @@
         <v>222</v>
       </c>
       <c r="C519" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D519" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
@@ -11149,13 +11155,13 @@
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="133" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B520" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C520" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D520" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
@@ -11198,7 +11204,7 @@
         <v>226</v>
       </c>
       <c r="C521" s="134" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D521" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
@@ -11235,13 +11241,13 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="133" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B522" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C522" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D522" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
@@ -11284,7 +11290,7 @@
         <v>230</v>
       </c>
       <c r="C523" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D523" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
@@ -11321,13 +11327,13 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="133" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B524" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C524" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D524" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
@@ -11370,7 +11376,7 @@
         <v>234</v>
       </c>
       <c r="C525" s="134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D525" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
@@ -11413,7 +11419,7 @@
         <v>236</v>
       </c>
       <c r="C526" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D526" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
@@ -11456,7 +11462,7 @@
         <v>238</v>
       </c>
       <c r="C527" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D527" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
@@ -11493,13 +11499,13 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="133" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B528" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C528" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D528" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
@@ -11542,7 +11548,7 @@
         <v>242</v>
       </c>
       <c r="C529" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D529" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
@@ -11585,7 +11591,7 @@
         <v>244</v>
       </c>
       <c r="C530" s="134" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D530" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
@@ -11622,13 +11628,13 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="137" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B531" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C531" s="138" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D531" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
@@ -11665,13 +11671,13 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="137" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B532" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C532" s="138" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D532" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
@@ -11708,13 +11714,13 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="137" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B533" s="138" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C533" s="138" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D533" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
@@ -19921,7 +19927,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>311</v>
       </c>
@@ -19963,7 +19969,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="104" t="s">
         <v>319</v>
       </c>
@@ -20073,18 +20079,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="100"/>
-      <c r="B37" s="110"/>
-      <c r="C37" s="111"/>
-      <c r="D37" s="109"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="100" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" s="110" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="96" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B38" s="107" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C38" s="108" t="n">
         <v>2</v>
@@ -20098,11 +20112,11 @@
         <v>245</v>
       </c>
       <c r="C39" s="70" t="n">
-        <f aca="false">SUM(C29:C35)</f>
-        <v>32</v>
+        <f aca="false">SUM(C32:C38)</f>
+        <v>41</v>
       </c>
       <c r="D39" s="70" t="n">
-        <f aca="false">SUM(D29:D35)</f>
+        <f aca="false">SUM(D32:D38)</f>
         <v>26</v>
       </c>
     </row>
@@ -20110,7 +20124,7 @@
     <row r="41" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="106" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B42" s="106"/>
       <c r="C42" s="106"/>
@@ -20118,72 +20132,72 @@
     </row>
     <row r="43" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="78" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B43" s="78" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D43" s="78" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B44" s="103" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C44" s="103" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B45" s="103" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C45" s="103" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B46" s="103" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C46" s="103" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="175.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B47" s="103" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C47" s="103" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -20224,7 +20238,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20237,7 +20251,7 @@
         <v>176</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20248,7 +20262,7 @@
         <v>192</v>
       </c>
       <c r="C3" s="113" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20259,7 +20273,7 @@
         <v>195</v>
       </c>
       <c r="C4" s="114" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20270,7 +20284,7 @@
         <v>197</v>
       </c>
       <c r="C5" s="113" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20281,7 +20295,7 @@
         <v>200</v>
       </c>
       <c r="C6" s="114" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20292,7 +20306,7 @@
         <v>202</v>
       </c>
       <c r="C7" s="113" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20303,7 +20317,7 @@
         <v>204</v>
       </c>
       <c r="C8" s="114" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20314,7 +20328,7 @@
         <v>206</v>
       </c>
       <c r="C9" s="113" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20325,7 +20339,7 @@
         <v>208</v>
       </c>
       <c r="C10" s="114" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20347,7 +20361,7 @@
         <v>213</v>
       </c>
       <c r="C12" s="114" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20358,7 +20372,7 @@
         <v>216</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20369,7 +20383,7 @@
         <v>218</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20380,7 +20394,7 @@
         <v>220</v>
       </c>
       <c r="C15" s="113" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20391,7 +20405,7 @@
         <v>222</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20402,7 +20416,7 @@
         <v>224</v>
       </c>
       <c r="C17" s="113" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20413,7 +20427,7 @@
         <v>226</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20424,7 +20438,7 @@
         <v>228</v>
       </c>
       <c r="C19" s="113" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20435,7 +20449,7 @@
         <v>230</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20446,7 +20460,7 @@
         <v>232</v>
       </c>
       <c r="C21" s="113" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20457,7 +20471,7 @@
         <v>234</v>
       </c>
       <c r="C22" s="114" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20468,7 +20482,7 @@
         <v>236</v>
       </c>
       <c r="C23" s="113" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20479,7 +20493,7 @@
         <v>238</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20490,7 +20504,7 @@
         <v>240</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20501,7 +20515,7 @@
         <v>242</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20512,124 +20526,124 @@
         <v>244</v>
       </c>
       <c r="C27" s="113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="106" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B29" s="106"/>
       <c r="C29" s="106"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="78" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B30" s="78" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="115" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C31" s="115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="115" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C32" s="115" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="115" t="s">
+        <v>391</v>
+      </c>
+      <c r="B33" s="115" t="s">
+        <v>386</v>
+      </c>
+      <c r="C33" s="115" t="s">
         <v>387</v>
-      </c>
-      <c r="B33" s="115" t="s">
-        <v>382</v>
-      </c>
-      <c r="C33" s="115" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="115" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C34" s="115" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="115" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C35" s="115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="115" t="s">
+        <v>394</v>
+      </c>
+      <c r="B36" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="C36" s="115" t="s">
         <v>390</v>
-      </c>
-      <c r="B36" s="115" t="s">
-        <v>385</v>
-      </c>
-      <c r="C36" s="115" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="115" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C37" s="115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="115" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C38" s="115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="115" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C39" s="115" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -20663,7 +20677,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20674,181 +20688,181 @@
         <v>176</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="96" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B3" s="116" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="100" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="96" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="100" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B6" s="118" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="96" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="D7" s="116" t="s">
         <v>413</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="119" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" s="116" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="100" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="96" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B9" s="116" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D9" s="116" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="100" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B10" s="118" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D10" s="118" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="96" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B11" s="116" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D11" s="116" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="100" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B12" s="118" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="96" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B13" s="116" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D13" s="116" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="100" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B14" s="118" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D14" s="118" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -20882,7 +20896,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20895,19 +20909,19 @@
         <v>176</v>
       </c>
       <c r="B2" s="121" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D2" s="121" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E2" s="121" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F2" s="121" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G2" s="121" t="s">
         <v>19</v>
@@ -20921,12 +20935,12 @@
         <v>191</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122"/>
       <c r="F3" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G3" s="122"/>
     </row>
@@ -20938,12 +20952,12 @@
         <v>194</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D4" s="123"/>
       <c r="E4" s="123"/>
       <c r="F4" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G4" s="123"/>
     </row>
@@ -20955,12 +20969,12 @@
         <v>196</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G5" s="122"/>
     </row>
@@ -20972,12 +20986,12 @@
         <v>199</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D6" s="123"/>
       <c r="E6" s="123"/>
       <c r="F6" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G6" s="123"/>
     </row>
@@ -20989,12 +21003,12 @@
         <v>201</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D7" s="122"/>
       <c r="E7" s="122"/>
       <c r="F7" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G7" s="122"/>
     </row>
@@ -21006,12 +21020,12 @@
         <v>203</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D8" s="123"/>
       <c r="E8" s="123"/>
       <c r="F8" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G8" s="123"/>
     </row>
@@ -21023,12 +21037,12 @@
         <v>205</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D9" s="122"/>
       <c r="E9" s="122"/>
       <c r="F9" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G9" s="122"/>
     </row>
@@ -21040,12 +21054,12 @@
         <v>207</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D10" s="123"/>
       <c r="E10" s="123"/>
       <c r="F10" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G10" s="123"/>
     </row>
@@ -21057,11 +21071,11 @@
         <v>209</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D11" s="122"/>
       <c r="E11" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F11" s="122"/>
       <c r="G11" s="122"/>
@@ -21074,14 +21088,14 @@
         <v>212</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D12" s="123"/>
       <c r="E12" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F12" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G12" s="123"/>
     </row>
@@ -21093,11 +21107,11 @@
         <v>215</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D13" s="122"/>
       <c r="E13" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F13" s="122"/>
       <c r="G13" s="122"/>
@@ -21110,14 +21124,14 @@
         <v>217</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D14" s="123"/>
       <c r="E14" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F14" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G14" s="123"/>
     </row>
@@ -21129,14 +21143,14 @@
         <v>219</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D15" s="122"/>
       <c r="E15" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F15" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G15" s="122"/>
     </row>
@@ -21148,14 +21162,14 @@
         <v>221</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D16" s="123"/>
       <c r="E16" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F16" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G16" s="123"/>
     </row>
@@ -21167,14 +21181,14 @@
         <v>223</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D17" s="122"/>
       <c r="E17" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F17" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G17" s="122"/>
     </row>
@@ -21186,14 +21200,14 @@
         <v>225</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D18" s="123"/>
       <c r="E18" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F18" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G18" s="123"/>
     </row>
@@ -21205,10 +21219,10 @@
         <v>227</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D19" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E19" s="122"/>
       <c r="F19" s="122"/>
@@ -21222,10 +21236,10 @@
         <v>229</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D20" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E20" s="123"/>
       <c r="F20" s="123"/>
@@ -21239,11 +21253,11 @@
         <v>231</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D21" s="122"/>
       <c r="E21" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F21" s="122"/>
       <c r="G21" s="122"/>
@@ -21256,11 +21270,11 @@
         <v>233</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D22" s="123"/>
       <c r="E22" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F22" s="123"/>
       <c r="G22" s="123"/>
@@ -21273,15 +21287,15 @@
         <v>235</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D23" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E23" s="122"/>
       <c r="F23" s="122"/>
       <c r="G23" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21292,15 +21306,15 @@
         <v>237</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D24" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E24" s="123"/>
       <c r="F24" s="123"/>
       <c r="G24" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21311,15 +21325,15 @@
         <v>239</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D25" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E25" s="122"/>
       <c r="F25" s="122"/>
       <c r="G25" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21330,15 +21344,15 @@
         <v>241</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D26" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E26" s="123"/>
       <c r="F26" s="123"/>
       <c r="G26" s="123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21349,20 +21363,20 @@
         <v>243</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D27" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E27" s="122"/>
       <c r="F27" s="122"/>
       <c r="G27" s="122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="124" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B28" s="124"/>
       <c r="C28" s="124"/>
@@ -21373,121 +21387,121 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="125" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B29" s="126" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C29" s="125" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D29" s="125" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
       <c r="G29" s="125" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="125" t="s">
+        <v>457</v>
+      </c>
+      <c r="B30" s="126" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="125" t="s">
         <v>453</v>
       </c>
-      <c r="B30" s="126" t="s">
-        <v>454</v>
-      </c>
-      <c r="C30" s="125" t="s">
-        <v>449</v>
-      </c>
       <c r="D30" s="125" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
       <c r="G30" s="125" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="125" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B31" s="126" t="s">
         <v>199</v>
       </c>
       <c r="C31" s="125" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D31" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E31" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F31" s="125"/>
       <c r="G31" s="125"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="125" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B32" s="126" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C32" s="125" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D32" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E32" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F32" s="125"/>
       <c r="G32" s="125"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="125" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B33" s="126" t="s">
+        <v>464</v>
+      </c>
+      <c r="C33" s="125" t="s">
+        <v>452</v>
+      </c>
+      <c r="D33" s="127" t="s">
         <v>460</v>
       </c>
-      <c r="C33" s="125" t="s">
-        <v>448</v>
-      </c>
-      <c r="D33" s="127" t="s">
-        <v>456</v>
-      </c>
       <c r="E33" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F33" s="125"/>
       <c r="G33" s="125"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B34" s="126" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C34" s="125" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D34" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E34" s="127" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F34" s="125"/>
       <c r="G34" s="125"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="128" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B37" s="128"/>
       <c r="C37" s="128"/>
@@ -21498,7 +21512,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="129" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B38" s="129"/>
       <c r="C38" s="129"/>

--- a/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
+++ b/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
@@ -122,6 +122,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Compromiso confirmado con Pablo (Q-08): Sandra cubre sábado 10 + lunes 12 de MAY.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cambiado el 2026-08-19: consecuencia obligada de H-04 (sabado normal -&gt; libra domingo Y lunes). Al pasar el sabado 24 a Carlota, ella debe librar el 26; Sandra, que queda libre ese periodo, cubre este MAY.</t>
         </r>
       </text>
     </comment>
@@ -599,6 +611,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="L36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cambiado el 2026-08-19 a peticion de Pablo: Carlota cubre este sabado (en lugar de Sandra) para llegar a 3 fines de semana. Se libero su bloqueo de vacaciones 23-25 oct.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="M5" authorId="0">
       <text>
         <r>
@@ -879,7 +903,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="664">
   <si>
     <t xml:space="preserve">Cuadrante de Guardias — Servicio de Anestesiología y Reanimación</t>
   </si>
@@ -1846,7 +1870,7 @@
     <t xml:space="preserve">VEREDICTO GLOBAL: </t>
   </si>
   <si>
-    <t xml:space="preserve">VÁLIDO salvo 2 excepciones documentadas: (1) MAY 9 y 11 oct sin cubrir (ver H-01/H-05); (2) S-06 — 9 días con 2 R1 juntos en QX-P, mínimo matemáticamente forzado por H-20 (R2 exactamente 6). Pablo decidió el 2026-08-19 mantener H-20 sin relajar y aceptar los 9 días como excepción. Todas las demás reglas H-01 a H-21: 0 violaciones.</t>
+    <t xml:space="preserve">VÁLIDO salvo 2 excepciones documentadas: (1) MAY 9 y 11 oct sin cubrir (ver H-01/H-05); (2) S-06 — 9 días con 2 R1 juntos en QX-P, mínimo matemáticamente forzado por H-20. Ajuste de fines de semana R4 confirmado el 2026-08-19: Carlota 3 findes (FDS-3, FDS-4, FDS-5), Sandra 2 findes incluyendo el puente 10-12 (FDS-1, FDS-2) — 1 caso adicional de S-08 aceptado (ver log de excepciones). Todas las reglas duras H-01 a H-21: 0 violaciones.</t>
   </si>
   <si>
     <t xml:space="preserve">Puntuación de reglas blandas S-01 a S-07 (0-41, ver fuente de la verdad §7 para el detalle de cada métrica)</t>
@@ -1966,6 +1990,12 @@
     <t xml:space="preserve">Pablo (WhatsApp 18/08)</t>
   </si>
   <si>
+    <t xml:space="preserve">S-08 (preferencia) TX el dia de saliente de una guardia — Sandra dia 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A peticion de Pablo se movio el MAY del lunes 26 de Carlota a Sandra (para que Carlota pudiera cubrir el sabado 24 y llegar a 3 findes, liberando su bloqueo de vacaciones 23-25). Consecuencia aceptada: Sandra tiene TX el dia 27, justo el dia despues de su guardia presencial del 26. No viola ninguna regla dura (H-03 solo bloquea presencial-tras-presencial), solo la preferencia blanda S-08.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bloqueos y vacaciones declarados — octubre 2026 (32 = 1 nov, 33 = 2 nov)</t>
   </si>
   <si>
@@ -2014,7 +2044,7 @@
     <t xml:space="preserve">9-11</t>
   </si>
   <si>
-    <t xml:space="preserve">2-4, 11, 23-25 ("si se puede" — alcance sin confirmar, Q-11)</t>
+    <t xml:space="preserve">2-4, 11 (duro). Bloqueo de 23-25 levantado el 2026-08-19 a peticion de Pablo para que Carlota cubra el sabado 24 de MAY.</t>
   </si>
   <si>
     <t xml:space="preserve">2-4, 9-11, 15-21 (duro)</t>
@@ -4733,13 +4763,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B1" s="112"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="130" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4888,7 +4918,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="130" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4896,7 +4926,7 @@
         <v>325</v>
       </c>
       <c r="B24" s="113" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4904,7 +4934,7 @@
         <v>327</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4912,7 +4942,7 @@
         <v>329</v>
       </c>
       <c r="B26" s="113" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4920,7 +4950,7 @@
         <v>331</v>
       </c>
       <c r="B27" s="114" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4928,7 +4958,7 @@
         <v>333</v>
       </c>
       <c r="B28" s="113" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4936,7 +4966,7 @@
         <v>335</v>
       </c>
       <c r="B29" s="114" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4944,7 +4974,7 @@
         <v>337</v>
       </c>
       <c r="B30" s="113" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -5077,7 +5107,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>49</v>
@@ -5088,7 +5118,7 @@
         <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5101,7 +5131,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5163,7 +5193,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -5180,7 +5210,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -5197,43 +5227,43 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B4" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="131" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F4" s="131" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L4" s="131" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M4" s="131" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5244,10 +5274,10 @@
         <v>192</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D5" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E5" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$506+'Histórico de guardias'!$E$506+'Histórico de guardias'!$F$506)+('Resumen de guardias'!$Q$3+'Resumen de guardias'!$R$3+'Resumen de guardias'!$S$3)</f>
@@ -5294,10 +5324,10 @@
         <v>195</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D6" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E6" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$507+'Histórico de guardias'!$E$507+'Histórico de guardias'!$F$507)+('Resumen de guardias'!$Q$4+'Resumen de guardias'!$R$4+'Resumen de guardias'!$S$4)</f>
@@ -5344,10 +5374,10 @@
         <v>197</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D7" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E7" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$508+'Histórico de guardias'!$E$508+'Histórico de guardias'!$F$508)+('Resumen de guardias'!$Q$5+'Resumen de guardias'!$R$5+'Resumen de guardias'!$S$5)</f>
@@ -5394,10 +5424,10 @@
         <v>200</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D8" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E8" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$509+'Histórico de guardias'!$E$509+'Histórico de guardias'!$F$509)+('Resumen de guardias'!$Q$6+'Resumen de guardias'!$R$6+'Resumen de guardias'!$S$6)</f>
@@ -5444,10 +5474,10 @@
         <v>202</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D9" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E9" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$510+'Histórico de guardias'!$E$510+'Histórico de guardias'!$F$510)+('Resumen de guardias'!$Q$7+'Resumen de guardias'!$R$7+'Resumen de guardias'!$S$7)</f>
@@ -5494,10 +5524,10 @@
         <v>204</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D10" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E10" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$511+'Histórico de guardias'!$E$511+'Histórico de guardias'!$F$511)+('Resumen de guardias'!$Q$8+'Resumen de guardias'!$R$8+'Resumen de guardias'!$S$8)</f>
@@ -5544,10 +5574,10 @@
         <v>206</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D11" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E11" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$512+'Histórico de guardias'!$E$512+'Histórico de guardias'!$F$512)+('Resumen de guardias'!$Q$9+'Resumen de guardias'!$R$9+'Resumen de guardias'!$S$9)</f>
@@ -5588,16 +5618,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="133" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D12" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E12" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$513+'Histórico de guardias'!$E$513+'Histórico de guardias'!$F$513)+('Resumen de guardias'!$Q$10+'Resumen de guardias'!$R$10+'Resumen de guardias'!$S$10)</f>
@@ -5644,10 +5674,10 @@
         <v>210</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D13" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E13" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$514+'Histórico de guardias'!$E$514+'Histórico de guardias'!$F$514)+('Resumen de guardias'!$Q$11+'Resumen de guardias'!$R$11+'Resumen de guardias'!$S$11)</f>
@@ -5688,16 +5718,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="133" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B14" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D14" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E14" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$515+'Histórico de guardias'!$E$515+'Histórico de guardias'!$F$515)+('Resumen de guardias'!$Q$12+'Resumen de guardias'!$R$12+'Resumen de guardias'!$S$12)</f>
@@ -5738,16 +5768,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="133" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B15" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D15" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E15" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$516+'Histórico de guardias'!$E$516+'Histórico de guardias'!$F$516)+('Resumen de guardias'!$Q$13+'Resumen de guardias'!$R$13+'Resumen de guardias'!$S$13)</f>
@@ -5794,10 +5824,10 @@
         <v>218</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D16" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E16" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$517+'Histórico de guardias'!$E$517+'Histórico de guardias'!$F$517)+('Resumen de guardias'!$Q$14+'Resumen de guardias'!$R$14+'Resumen de guardias'!$S$14)</f>
@@ -5844,10 +5874,10 @@
         <v>220</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D17" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E17" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$518+'Histórico de guardias'!$E$518+'Histórico de guardias'!$F$518)+('Resumen de guardias'!$Q$15+'Resumen de guardias'!$R$15+'Resumen de guardias'!$S$15)</f>
@@ -5894,10 +5924,10 @@
         <v>222</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D18" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E18" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$519+'Histórico de guardias'!$E$519+'Histórico de guardias'!$F$519)+('Resumen de guardias'!$Q$16+'Resumen de guardias'!$R$16+'Resumen de guardias'!$S$16)</f>
@@ -5938,16 +5968,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="133" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B19" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D19" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E19" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$520+'Histórico de guardias'!$E$520+'Histórico de guardias'!$F$520)+('Resumen de guardias'!$Q$17+'Resumen de guardias'!$R$17+'Resumen de guardias'!$S$17)</f>
@@ -5994,10 +6024,10 @@
         <v>226</v>
       </c>
       <c r="C20" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D20" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E20" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$521+'Histórico de guardias'!$E$521+'Histórico de guardias'!$F$521)+('Resumen de guardias'!$Q$18+'Resumen de guardias'!$R$18+'Resumen de guardias'!$S$18)</f>
@@ -6038,16 +6068,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="133" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B21" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C21" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D21" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E21" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$522+'Histórico de guardias'!$E$522+'Histórico de guardias'!$F$522)+('Resumen de guardias'!$Q$19+'Resumen de guardias'!$R$19+'Resumen de guardias'!$S$19)</f>
@@ -6094,10 +6124,10 @@
         <v>230</v>
       </c>
       <c r="C22" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D22" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E22" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$523+'Histórico de guardias'!$E$523+'Histórico de guardias'!$F$523)+('Resumen de guardias'!$Q$20+'Resumen de guardias'!$R$20+'Resumen de guardias'!$S$20)</f>
@@ -6138,16 +6168,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="133" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B23" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D23" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E23" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$524+'Histórico de guardias'!$E$524+'Histórico de guardias'!$F$524)+('Resumen de guardias'!$Q$21+'Resumen de guardias'!$R$21+'Resumen de guardias'!$S$21)</f>
@@ -6194,10 +6224,10 @@
         <v>234</v>
       </c>
       <c r="C24" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D24" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E24" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$525+'Histórico de guardias'!$E$525+'Histórico de guardias'!$F$525)+('Resumen de guardias'!$Q$22+'Resumen de guardias'!$R$22+'Resumen de guardias'!$S$22)</f>
@@ -6244,14 +6274,14 @@
         <v>236</v>
       </c>
       <c r="C25" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D25" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E25" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$526+'Histórico de guardias'!$E$526+'Histórico de guardias'!$F$526)+('Resumen de guardias'!$Q$23+'Resumen de guardias'!$R$23+'Resumen de guardias'!$S$23)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F25" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C25,$D$5:$D$32,"Sí")</f>
@@ -6259,7 +6289,7 @@
       </c>
       <c r="G25" s="136" t="n">
         <f aca="false">E25-F25</f>
-        <v>-0.800000000000001</v>
+        <v>0.199999999999999</v>
       </c>
       <c r="H25" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$526+'Resumen de guardias'!$T$23</f>
@@ -6294,10 +6324,10 @@
         <v>238</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D26" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E26" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$527+'Histórico de guardias'!$E$527+'Histórico de guardias'!$F$527)+('Resumen de guardias'!$Q$24+'Resumen de guardias'!$R$24+'Resumen de guardias'!$S$24)</f>
@@ -6338,16 +6368,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="133" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B27" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D27" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E27" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$528+'Histórico de guardias'!$E$528+'Histórico de guardias'!$F$528)+('Resumen de guardias'!$Q$25+'Resumen de guardias'!$R$25+'Resumen de guardias'!$S$25)</f>
@@ -6394,14 +6424,14 @@
         <v>242</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D28" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E28" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$529+'Histórico de guardias'!$E$529+'Histórico de guardias'!$F$529)+('Resumen de guardias'!$Q$26+'Resumen de guardias'!$R$26+'Resumen de guardias'!$S$26)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" s="134" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C28,$D$5:$D$32,"Sí")</f>
@@ -6409,7 +6439,7 @@
       </c>
       <c r="G28" s="136" t="n">
         <f aca="false">E28-F28</f>
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H28" s="134" t="n">
         <f aca="false">'Histórico de guardias'!$J$529+'Resumen de guardias'!$T$26</f>
@@ -6444,10 +6474,10 @@
         <v>244</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D29" s="135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E29" s="134" t="n">
         <f aca="false">('Histórico de guardias'!$D$530+'Histórico de guardias'!$E$530+'Histórico de guardias'!$F$530)+('Resumen de guardias'!$Q$27+'Resumen de guardias'!$R$27+'Resumen de guardias'!$S$27)</f>
@@ -6488,16 +6518,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="137" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B30" s="138" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C30" s="138" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E30" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$531+'Histórico de guardias'!$E$531+'Histórico de guardias'!$F$531)+0</f>
@@ -6538,16 +6568,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="137" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B31" s="138" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C31" s="138" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D31" s="139" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E31" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$532+'Histórico de guardias'!$E$532+'Histórico de guardias'!$F$532)+0</f>
@@ -6588,16 +6618,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="137" t="s">
+        <v>506</v>
+      </c>
+      <c r="B32" s="138" t="s">
         <v>504</v>
       </c>
-      <c r="B32" s="138" t="s">
-        <v>502</v>
-      </c>
       <c r="C32" s="138" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D32" s="139" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E32" s="138" t="n">
         <f aca="false">('Histórico de guardias'!$D$533+'Histórico de guardias'!$E$533+'Histórico de guardias'!$F$533)+0</f>
@@ -6696,7 +6726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="131" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -6711,7 +6741,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="132" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B2" s="132"/>
       <c r="C2" s="132"/>
@@ -6726,58 +6756,58 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B4" s="131" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C4" s="131" t="s">
         <v>340</v>
       </c>
       <c r="D4" s="131" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F4" s="131" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H4" s="131" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J4" s="131" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K4" s="131" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B5" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="141" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D5" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E5" s="140"/>
       <c r="F5" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H5" s="141" t="s">
         <v>243</v>
@@ -6792,16 +6822,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B6" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="141" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D6" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E6" s="140"/>
       <c r="F6" s="141" t="s">
@@ -6811,7 +6841,7 @@
         <v>225</v>
       </c>
       <c r="H6" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I6" s="141" t="s">
         <v>231</v>
@@ -6823,16 +6853,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B7" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="141" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D7" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E7" s="140"/>
       <c r="F7" s="141" t="s">
@@ -6854,23 +6884,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B8" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="141" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D8" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E8" s="140"/>
       <c r="F8" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G8" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H8" s="141" t="s">
         <v>241</v>
@@ -6885,29 +6915,29 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B9" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="141" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D9" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E9" s="140"/>
       <c r="F9" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G9" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H9" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I9" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J9" s="141" t="s">
         <v>212</v>
@@ -6916,23 +6946,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B10" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="143" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D10" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E10" s="142"/>
       <c r="F10" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G10" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H10" s="143" t="s">
         <v>237</v>
@@ -6947,20 +6977,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B11" s="143" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="143" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D11" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E11" s="142"/>
       <c r="F11" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G11" s="143" t="s">
         <v>221</v>
@@ -6978,23 +7008,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B12" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C12" s="141" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D12" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E12" s="140"/>
       <c r="F12" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H12" s="141" t="s">
         <v>235</v>
@@ -7009,16 +7039,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B13" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="141" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D13" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E13" s="140"/>
       <c r="F13" s="141" t="s">
@@ -7031,7 +7061,7 @@
         <v>241</v>
       </c>
       <c r="I13" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J13" s="141" t="s">
         <v>209</v>
@@ -7040,26 +7070,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B14" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="141" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D14" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E14" s="140"/>
       <c r="F14" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G14" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H14" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I14" s="141" t="s">
         <v>233</v>
@@ -7071,16 +7101,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B15" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="141" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D15" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="141" t="s">
@@ -7093,7 +7123,7 @@
         <v>237</v>
       </c>
       <c r="I15" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J15" s="141" t="s">
         <v>212</v>
@@ -7102,23 +7132,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B16" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="141" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D16" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E16" s="140"/>
       <c r="F16" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G16" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H16" s="141" t="s">
         <v>235</v>
@@ -7133,16 +7163,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B17" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="143" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D17" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E17" s="142"/>
       <c r="F17" s="143" t="s">
@@ -7164,23 +7194,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B18" s="143" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="143" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D18" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E18" s="142"/>
       <c r="F18" s="143" t="s">
         <v>243</v>
       </c>
       <c r="G18" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H18" s="143" t="s">
         <v>235</v>
@@ -7195,29 +7225,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B19" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E19" s="140"/>
       <c r="F19" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H19" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J19" s="141" t="s">
         <v>217</v>
@@ -7226,16 +7256,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B20" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="141" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D20" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E20" s="140"/>
       <c r="F20" s="141" t="s">
@@ -7251,22 +7281,22 @@
         <v>235</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K20" s="141"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B21" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="141" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D21" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E21" s="140"/>
       <c r="F21" s="141" t="s">
@@ -7288,23 +7318,23 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B22" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E22" s="140"/>
       <c r="F22" s="141" t="s">
         <v>241</v>
       </c>
       <c r="G22" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H22" s="141" t="s">
         <v>231</v>
@@ -7319,16 +7349,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B23" s="141" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E23" s="140"/>
       <c r="F23" s="141" t="s">
@@ -7344,22 +7374,22 @@
         <v>229</v>
       </c>
       <c r="J23" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K23" s="141"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B24" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D24" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E24" s="142"/>
       <c r="F24" s="143" t="s">
@@ -7381,16 +7411,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B25" s="143" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="143" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D25" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E25" s="142"/>
       <c r="F25" s="143" t="s">
@@ -7406,26 +7436,26 @@
         <v>229</v>
       </c>
       <c r="J25" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B26" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="141" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E26" s="140"/>
       <c r="F26" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G26" s="141" t="s">
         <v>209</v>
@@ -7434,7 +7464,7 @@
         <v>235</v>
       </c>
       <c r="I26" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J26" s="141" t="s">
         <v>225</v>
@@ -7443,16 +7473,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B27" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="141" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E27" s="140"/>
       <c r="F27" s="141" t="s">
@@ -7468,22 +7498,22 @@
         <v>231</v>
       </c>
       <c r="J27" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K27" s="141"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B28" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="141" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E28" s="140"/>
       <c r="F28" s="141" t="s">
@@ -7505,16 +7535,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B29" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="141" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E29" s="140"/>
       <c r="F29" s="141" t="s">
@@ -7536,23 +7566,23 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B30" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E30" s="140"/>
       <c r="F30" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G30" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H30" s="141" t="s">
         <v>241</v>
@@ -7561,22 +7591,22 @@
         <v>233</v>
       </c>
       <c r="J30" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K30" s="141"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B31" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="143" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D31" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E31" s="142"/>
       <c r="F31" s="143" t="s">
@@ -7589,25 +7619,25 @@
         <v>235</v>
       </c>
       <c r="I31" s="143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J31" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K31" s="143"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="142" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B32" s="143" t="n">
         <v>28</v>
       </c>
       <c r="C32" s="143" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D32" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E32" s="142"/>
       <c r="F32" s="143" t="s">
@@ -7623,35 +7653,35 @@
         <v>233</v>
       </c>
       <c r="J32" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K32" s="143"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B33" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C33" s="141" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E33" s="140"/>
       <c r="F33" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G33" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H33" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I33" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J33" s="141" t="s">
         <v>209</v>
@@ -7662,29 +7692,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="140" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B34" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="141" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D34" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E34" s="140"/>
       <c r="F34" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G34" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H34" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I34" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J34" s="141" t="s">
         <v>229</v>
@@ -7693,26 +7723,26 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B35" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="141" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D35" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E35" s="140"/>
       <c r="F35" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G35" s="141" t="s">
         <v>221</v>
       </c>
       <c r="H35" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I35" s="141" t="s">
         <v>231</v>
@@ -7724,54 +7754,54 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B36" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="141" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D36" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E36" s="140"/>
       <c r="F36" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G36" s="141" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I36" s="141" t="s">
         <v>243</v>
       </c>
       <c r="J36" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K36" s="141"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B37" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="141" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D37" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E37" s="140"/>
       <c r="F37" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G37" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H37" s="141" t="s">
         <v>241</v>
@@ -7786,20 +7816,20 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B38" s="143" t="n">
         <v>4</v>
       </c>
       <c r="C38" s="143" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D38" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E38" s="142"/>
       <c r="F38" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G38" s="143" t="s">
         <v>225</v>
@@ -7817,29 +7847,29 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B39" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C39" s="143" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D39" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E39" s="142"/>
       <c r="F39" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G39" s="143" t="s">
         <v>229</v>
       </c>
       <c r="H39" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I39" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J39" s="143" t="s">
         <v>212</v>
@@ -7848,16 +7878,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B40" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C40" s="141" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D40" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E40" s="140"/>
       <c r="F40" s="141" t="s">
@@ -7879,26 +7909,26 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B41" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C41" s="141" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D41" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E41" s="140"/>
       <c r="F41" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G41" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H41" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I41" s="141" t="s">
         <v>219</v>
@@ -7910,16 +7940,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B42" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C42" s="141" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D42" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E42" s="140"/>
       <c r="F42" s="141" t="s">
@@ -7935,22 +7965,22 @@
         <v>209</v>
       </c>
       <c r="J42" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K42" s="141"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B43" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C43" s="141" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D43" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E43" s="140"/>
       <c r="F43" s="141" t="s">
@@ -7960,7 +7990,7 @@
         <v>221</v>
       </c>
       <c r="H43" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I43" s="141" t="s">
         <v>217</v>
@@ -7972,20 +8002,20 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B44" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C44" s="141" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D44" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E44" s="140"/>
       <c r="F44" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G44" s="141" t="s">
         <v>229</v>
@@ -7994,7 +8024,7 @@
         <v>233</v>
       </c>
       <c r="I44" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J44" s="141" t="s">
         <v>212</v>
@@ -8003,16 +8033,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B45" s="143" t="n">
         <v>11</v>
       </c>
       <c r="C45" s="143" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D45" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E45" s="142"/>
       <c r="F45" s="143" t="s">
@@ -8022,7 +8052,7 @@
         <v>221</v>
       </c>
       <c r="H45" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I45" s="143" t="s">
         <v>217</v>
@@ -8034,26 +8064,26 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B46" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C46" s="143" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D46" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E46" s="142"/>
       <c r="F46" s="143" t="s">
         <v>241</v>
       </c>
       <c r="G46" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H46" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I46" s="143" t="s">
         <v>237</v>
@@ -8065,20 +8095,20 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B47" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C47" s="141" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D47" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E47" s="140"/>
       <c r="F47" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G47" s="141" t="s">
         <v>221</v>
@@ -8090,22 +8120,22 @@
         <v>217</v>
       </c>
       <c r="J47" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K47" s="141"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B48" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="141" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D48" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E48" s="140"/>
       <c r="F48" s="141" t="s">
@@ -8115,10 +8145,10 @@
         <v>212</v>
       </c>
       <c r="H48" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I48" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J48" s="141" t="s">
         <v>219</v>
@@ -8127,20 +8157,20 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B49" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="141" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D49" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E49" s="140"/>
       <c r="F49" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G49" s="141" t="s">
         <v>221</v>
@@ -8158,20 +8188,20 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B50" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C50" s="141" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D50" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E50" s="140"/>
       <c r="F50" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G50" s="141" t="s">
         <v>225</v>
@@ -8180,35 +8210,35 @@
         <v>235</v>
       </c>
       <c r="I50" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J50" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K50" s="141"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B51" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C51" s="141" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D51" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E51" s="140"/>
       <c r="F51" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G51" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H51" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I51" s="141" t="s">
         <v>241</v>
@@ -8220,20 +8250,20 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B52" s="143" t="n">
         <v>18</v>
       </c>
       <c r="C52" s="143" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D52" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E52" s="142"/>
       <c r="F52" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G52" s="143" t="s">
         <v>225</v>
@@ -8242,25 +8272,25 @@
         <v>235</v>
       </c>
       <c r="I52" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J52" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K52" s="143"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B53" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C53" s="143" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D53" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E53" s="142"/>
       <c r="F53" s="143" t="s">
@@ -8282,26 +8312,26 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B54" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C54" s="141" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D54" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E54" s="140"/>
       <c r="F54" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G54" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H54" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I54" s="141" t="s">
         <v>237</v>
@@ -8313,20 +8343,20 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B55" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C55" s="141" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D55" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E55" s="140"/>
       <c r="F55" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G55" s="141" t="s">
         <v>225</v>
@@ -8344,47 +8374,47 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B56" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C56" s="141" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D56" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E56" s="140"/>
       <c r="F56" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G56" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H56" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I56" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J56" s="141" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K56" s="141"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B57" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C57" s="141" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D57" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E57" s="140"/>
       <c r="F57" s="141" t="s">
@@ -8394,7 +8424,7 @@
         <v>229</v>
       </c>
       <c r="H57" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I57" s="141" t="s">
         <v>233</v>
@@ -8406,16 +8436,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B58" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C58" s="141" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D58" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E58" s="140"/>
       <c r="F58" s="141" t="s">
@@ -8428,7 +8458,7 @@
         <v>235</v>
       </c>
       <c r="I58" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J58" s="141" t="s">
         <v>212</v>
@@ -8437,16 +8467,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B59" s="143" t="n">
         <v>25</v>
       </c>
       <c r="C59" s="143" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D59" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E59" s="142"/>
       <c r="F59" s="143" t="s">
@@ -8468,16 +8498,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="142" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B60" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C60" s="143" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D60" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E60" s="142"/>
       <c r="F60" s="143" t="s">
@@ -8493,22 +8523,22 @@
         <v>243</v>
       </c>
       <c r="J60" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K60" s="143"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B61" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="141" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D61" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E61" s="140"/>
       <c r="F61" s="141" t="s">
@@ -8518,28 +8548,28 @@
         <v>229</v>
       </c>
       <c r="H61" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I61" s="141" t="s">
         <v>233</v>
       </c>
       <c r="J61" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K61" s="141"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B62" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C62" s="141" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D62" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E62" s="140"/>
       <c r="F62" s="141" t="s">
@@ -8555,29 +8585,29 @@
         <v>212</v>
       </c>
       <c r="J62" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K62" s="141"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B63" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C63" s="141" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D63" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E63" s="140"/>
       <c r="F63" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G63" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H63" s="141" t="s">
         <v>243</v>
@@ -8592,16 +8622,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="140" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B64" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C64" s="141" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D64" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E64" s="140"/>
       <c r="F64" s="141" t="s">
@@ -8623,16 +8653,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B65" s="143" t="n">
         <v>1</v>
       </c>
       <c r="C65" s="143" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D65" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E65" s="142"/>
       <c r="F65" s="143" t="s">
@@ -8645,23 +8675,23 @@
         <v>237</v>
       </c>
       <c r="I65" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J65" s="143"/>
       <c r="K65" s="143"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B66" s="143" t="n">
         <v>2</v>
       </c>
       <c r="C66" s="143" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D66" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E66" s="142"/>
       <c r="F66" s="143" t="s">
@@ -8683,16 +8713,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B67" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="141" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D67" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E67" s="140"/>
       <c r="F67" s="141" t="s">
@@ -8712,20 +8742,20 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B68" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C68" s="141" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D68" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E68" s="140"/>
       <c r="F68" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G68" s="141" t="s">
         <v>229</v>
@@ -8734,25 +8764,25 @@
         <v>231</v>
       </c>
       <c r="I68" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J68" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K68" s="141"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B69" s="141" t="n">
         <v>5</v>
       </c>
       <c r="C69" s="141" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D69" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E69" s="140"/>
       <c r="F69" s="141" t="s">
@@ -8762,7 +8792,7 @@
         <v>229</v>
       </c>
       <c r="H69" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I69" s="141" t="s">
         <v>235</v>
@@ -8772,23 +8802,23 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B70" s="141" t="n">
         <v>6</v>
       </c>
       <c r="C70" s="141" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E70" s="140"/>
       <c r="F70" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G70" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H70" s="141" t="s">
         <v>241</v>
@@ -8803,16 +8833,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B71" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="141" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D71" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E71" s="140"/>
       <c r="F71" s="141" t="s">
@@ -8822,10 +8852,10 @@
         <v>219</v>
       </c>
       <c r="H71" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I71" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J71" s="141" t="s">
         <v>212</v>
@@ -8834,16 +8864,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B72" s="143" t="n">
         <v>8</v>
       </c>
       <c r="C72" s="143" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D72" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E72" s="142"/>
       <c r="F72" s="143" t="s">
@@ -8853,7 +8883,7 @@
         <v>225</v>
       </c>
       <c r="H72" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I72" s="143" t="s">
         <v>231</v>
@@ -8863,16 +8893,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B73" s="143" t="n">
         <v>9</v>
       </c>
       <c r="C73" s="143" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D73" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E73" s="142"/>
       <c r="F73" s="143" t="s">
@@ -8882,10 +8912,10 @@
         <v>219</v>
       </c>
       <c r="H73" s="143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I73" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J73" s="143" t="s">
         <v>212</v>
@@ -8894,20 +8924,20 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B74" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C74" s="141" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D74" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E74" s="140"/>
       <c r="F74" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G74" s="141" t="s">
         <v>229</v>
@@ -8925,20 +8955,20 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B75" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C75" s="141" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D75" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E75" s="140"/>
       <c r="F75" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G75" s="141" t="s">
         <v>209</v>
@@ -8956,20 +8986,20 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B76" s="141" t="n">
         <v>12</v>
       </c>
       <c r="C76" s="141" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D76" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E76" s="140"/>
       <c r="F76" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G76" s="141" t="s">
         <v>229</v>
@@ -8978,7 +9008,7 @@
         <v>241</v>
       </c>
       <c r="I76" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J76" s="141" t="s">
         <v>212</v>
@@ -8987,26 +9017,26 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B77" s="141" t="n">
         <v>13</v>
       </c>
       <c r="C77" s="141" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D77" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E77" s="140"/>
       <c r="F77" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G77" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H77" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I77" s="141" t="s">
         <v>219</v>
@@ -9018,20 +9048,20 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B78" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C78" s="141" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D78" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E78" s="140"/>
       <c r="F78" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G78" s="141" t="s">
         <v>229</v>
@@ -9049,22 +9079,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="144" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B79" s="145" t="n">
         <v>15</v>
       </c>
       <c r="C79" s="145" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D79" s="145" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E79" s="144" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F79" s="145" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G79" s="145" t="s">
         <v>243</v>
@@ -9080,16 +9110,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B80" s="143" t="n">
         <v>16</v>
       </c>
       <c r="C80" s="143" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D80" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E80" s="142"/>
       <c r="F80" s="143" t="s">
@@ -9111,38 +9141,38 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B81" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C81" s="141" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D81" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E81" s="140"/>
       <c r="F81" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G81" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H81" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I81" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J81" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K81" s="141"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B82" s="141" t="n">
         <v>18</v>
@@ -9151,17 +9181,17 @@
         <v>356</v>
       </c>
       <c r="D82" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E82" s="140"/>
       <c r="F82" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G82" s="141" t="s">
         <v>243</v>
       </c>
       <c r="H82" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I82" s="141" t="s">
         <v>209</v>
@@ -9173,7 +9203,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B83" s="141" t="n">
         <v>19</v>
@@ -9182,7 +9212,7 @@
         <v>348</v>
       </c>
       <c r="D83" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E83" s="140"/>
       <c r="F83" s="141" t="s">
@@ -9195,25 +9225,25 @@
         <v>231</v>
       </c>
       <c r="I83" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J83" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K83" s="141"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B84" s="141" t="n">
         <v>20</v>
       </c>
       <c r="C84" s="141" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D84" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E84" s="140"/>
       <c r="F84" s="141" t="s">
@@ -9223,10 +9253,10 @@
         <v>221</v>
       </c>
       <c r="H84" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I84" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J84" s="141" t="s">
         <v>233</v>
@@ -9235,20 +9265,20 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B85" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="141" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D85" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E85" s="140"/>
       <c r="F85" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G85" s="141" t="s">
         <v>225</v>
@@ -9266,20 +9296,20 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B86" s="143" t="n">
         <v>22</v>
       </c>
       <c r="C86" s="143" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D86" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E86" s="142"/>
       <c r="F86" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G86" s="143" t="s">
         <v>243</v>
@@ -9288,27 +9318,27 @@
         <v>233</v>
       </c>
       <c r="I86" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J86" s="143"/>
       <c r="K86" s="143"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B87" s="143" t="n">
         <v>23</v>
       </c>
       <c r="C87" s="143" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D87" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E87" s="142"/>
       <c r="F87" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G87" s="143" t="s">
         <v>225</v>
@@ -9326,20 +9356,20 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B88" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C88" s="141" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D88" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E88" s="140"/>
       <c r="F88" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G88" s="141" t="s">
         <v>229</v>
@@ -9348,25 +9378,25 @@
         <v>237</v>
       </c>
       <c r="I88" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J88" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K88" s="141"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B89" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C89" s="141" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D89" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E89" s="140"/>
       <c r="F89" s="141" t="s">
@@ -9376,7 +9406,7 @@
         <v>212</v>
       </c>
       <c r="H89" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I89" s="141" t="s">
         <v>233</v>
@@ -9388,16 +9418,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B90" s="141" t="n">
         <v>26</v>
       </c>
       <c r="C90" s="141" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D90" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E90" s="140"/>
       <c r="F90" s="141" t="s">
@@ -9407,41 +9437,41 @@
         <v>225</v>
       </c>
       <c r="H90" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I90" s="141" t="s">
         <v>221</v>
       </c>
       <c r="J90" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K90" s="141"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B91" s="141" t="n">
         <v>27</v>
       </c>
       <c r="C91" s="141" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D91" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E91" s="140"/>
       <c r="F91" s="141" t="s">
         <v>235</v>
       </c>
       <c r="G91" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H91" s="141" t="s">
         <v>231</v>
       </c>
       <c r="I91" s="141" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J91" s="141" t="s">
         <v>217</v>
@@ -9450,16 +9480,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B92" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C92" s="141" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D92" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E92" s="140"/>
       <c r="F92" s="141" t="s">
@@ -9472,25 +9502,25 @@
         <v>237</v>
       </c>
       <c r="I92" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J92" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K92" s="141"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B93" s="143" t="n">
         <v>29</v>
       </c>
       <c r="C93" s="143" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D93" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E93" s="142"/>
       <c r="F93" s="143" t="s">
@@ -9500,61 +9530,61 @@
         <v>221</v>
       </c>
       <c r="H93" s="143" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I93" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J93" s="143"/>
       <c r="K93" s="143"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="142" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B94" s="143" t="n">
         <v>30</v>
       </c>
       <c r="C94" s="143" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D94" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E94" s="142"/>
       <c r="F94" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G94" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H94" s="143" t="s">
         <v>237</v>
       </c>
       <c r="I94" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J94" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K94" s="143"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="140" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B95" s="141" t="n">
         <v>31</v>
       </c>
       <c r="C95" s="141" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D95" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E95" s="140"/>
       <c r="F95" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G95" s="141" t="s">
         <v>243</v>
@@ -9572,23 +9602,23 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B96" s="141" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="141" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D96" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E96" s="140"/>
       <c r="F96" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G96" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H96" s="141" t="s">
         <v>233</v>
@@ -9603,23 +9633,23 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B97" s="141" t="n">
         <v>2</v>
       </c>
       <c r="C97" s="141" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D97" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E97" s="140"/>
       <c r="F97" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G97" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H97" s="141" t="s">
         <v>237</v>
@@ -9634,16 +9664,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B98" s="141" t="n">
         <v>3</v>
       </c>
       <c r="C98" s="141" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D98" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E98" s="140"/>
       <c r="F98" s="141" t="s">
@@ -9653,10 +9683,10 @@
         <v>217</v>
       </c>
       <c r="H98" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I98" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J98" s="141" t="s">
         <v>191</v>
@@ -9665,16 +9695,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B99" s="141" t="n">
         <v>4</v>
       </c>
       <c r="C99" s="141" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D99" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E99" s="140"/>
       <c r="F99" s="141" t="s">
@@ -9687,7 +9717,7 @@
         <v>229</v>
       </c>
       <c r="I99" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J99" s="141" t="s">
         <v>194</v>
@@ -9696,20 +9726,20 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B100" s="143" t="n">
         <v>5</v>
       </c>
       <c r="C100" s="143" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D100" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E100" s="142"/>
       <c r="F100" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G100" s="143" t="s">
         <v>221</v>
@@ -9727,16 +9757,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B101" s="143" t="n">
         <v>6</v>
       </c>
       <c r="C101" s="143" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D101" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E101" s="142"/>
       <c r="F101" s="143" t="s">
@@ -9749,7 +9779,7 @@
         <v>229</v>
       </c>
       <c r="I101" s="143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J101" s="143" t="s">
         <v>194</v>
@@ -9758,20 +9788,20 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B102" s="141" t="n">
         <v>7</v>
       </c>
       <c r="C102" s="141" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D102" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E102" s="140"/>
       <c r="F102" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G102" s="141" t="s">
         <v>212</v>
@@ -9789,29 +9819,29 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B103" s="141" t="n">
         <v>8</v>
       </c>
       <c r="C103" s="141" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D103" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E103" s="140"/>
       <c r="F103" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G103" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H103" s="141" t="s">
         <v>237</v>
       </c>
       <c r="I103" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J103" s="141" t="s">
         <v>217</v>
@@ -9820,20 +9850,20 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B104" s="141" t="n">
         <v>9</v>
       </c>
       <c r="C104" s="141" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D104" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E104" s="140"/>
       <c r="F104" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G104" s="141" t="s">
         <v>209</v>
@@ -9842,7 +9872,7 @@
         <v>243</v>
       </c>
       <c r="I104" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J104" s="141" t="s">
         <v>219</v>
@@ -9851,26 +9881,26 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B105" s="141" t="n">
         <v>10</v>
       </c>
       <c r="C105" s="141" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D105" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G105" s="141" t="s">
         <v>225</v>
       </c>
       <c r="H105" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I105" s="141" t="s">
         <v>212</v>
@@ -9882,20 +9912,20 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B106" s="141" t="n">
         <v>11</v>
       </c>
       <c r="C106" s="141" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D106" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E106" s="140"/>
       <c r="F106" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G106" s="141" t="s">
         <v>231</v>
@@ -9904,7 +9934,7 @@
         <v>233</v>
       </c>
       <c r="I106" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J106" s="141" t="s">
         <v>207</v>
@@ -9913,20 +9943,20 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B107" s="143" t="n">
         <v>12</v>
       </c>
       <c r="C107" s="143" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D107" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E107" s="142"/>
       <c r="F107" s="143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G107" s="143" t="s">
         <v>212</v>
@@ -9944,20 +9974,20 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B108" s="143" t="n">
         <v>13</v>
       </c>
       <c r="C108" s="143" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D108" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E108" s="142"/>
       <c r="F108" s="143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G108" s="143" t="s">
         <v>231</v>
@@ -9966,7 +9996,7 @@
         <v>233</v>
       </c>
       <c r="I108" s="143" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J108" s="143" t="s">
         <v>207</v>
@@ -9975,23 +10005,23 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B109" s="141" t="n">
         <v>14</v>
       </c>
       <c r="C109" s="141" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D109" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E109" s="140"/>
       <c r="F109" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G109" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H109" s="141" t="s">
         <v>229</v>
@@ -10006,16 +10036,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B110" s="141" t="n">
         <v>15</v>
       </c>
       <c r="C110" s="141" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D110" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E110" s="140"/>
       <c r="F110" s="141" t="s">
@@ -10028,7 +10058,7 @@
         <v>237</v>
       </c>
       <c r="I110" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J110" s="141" t="s">
         <v>225</v>
@@ -10037,26 +10067,26 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B111" s="141" t="n">
         <v>16</v>
       </c>
       <c r="C111" s="141" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D111" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E111" s="140"/>
       <c r="F111" s="141" t="s">
         <v>243</v>
       </c>
       <c r="G111" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H111" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I111" s="141" t="s">
         <v>212</v>
@@ -10068,16 +10098,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B112" s="141" t="n">
         <v>17</v>
       </c>
       <c r="C112" s="141" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D112" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E112" s="140"/>
       <c r="F112" s="141" t="s">
@@ -10087,7 +10117,7 @@
         <v>231</v>
       </c>
       <c r="H112" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I112" s="141" t="s">
         <v>217</v>
@@ -10099,23 +10129,23 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B113" s="141" t="n">
         <v>18</v>
       </c>
       <c r="C113" s="141" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D113" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E113" s="140"/>
       <c r="F113" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G113" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H113" s="141" t="s">
         <v>229</v>
@@ -10124,26 +10154,26 @@
         <v>221</v>
       </c>
       <c r="J113" s="141" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K113" s="141"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B114" s="143" t="n">
         <v>19</v>
       </c>
       <c r="C114" s="143" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D114" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E114" s="142"/>
       <c r="F114" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G114" s="143" t="s">
         <v>209</v>
@@ -10161,23 +10191,23 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B115" s="143" t="n">
         <v>20</v>
       </c>
       <c r="C115" s="143" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D115" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E115" s="142"/>
       <c r="F115" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G115" s="143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H115" s="143" t="s">
         <v>229</v>
@@ -10186,22 +10216,22 @@
         <v>221</v>
       </c>
       <c r="J115" s="143" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K115" s="143"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B116" s="141" t="n">
         <v>21</v>
       </c>
       <c r="C116" s="141" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D116" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E116" s="140"/>
       <c r="F116" s="141" t="s">
@@ -10223,20 +10253,20 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B117" s="141" t="n">
         <v>22</v>
       </c>
       <c r="C117" s="141" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D117" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E117" s="140"/>
       <c r="F117" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G117" s="141" t="s">
         <v>209</v>
@@ -10254,29 +10284,29 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B118" s="141" t="n">
         <v>23</v>
       </c>
       <c r="C118" s="141" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D118" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E118" s="140"/>
       <c r="F118" s="141" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G118" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H118" s="141" t="s">
         <v>243</v>
       </c>
       <c r="I118" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J118" s="141" t="s">
         <v>196</v>
@@ -10285,16 +10315,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B119" s="141" t="n">
         <v>24</v>
       </c>
       <c r="C119" s="141" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D119" s="141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E119" s="140"/>
       <c r="F119" s="141" t="s">
@@ -10307,7 +10337,7 @@
         <v>233</v>
       </c>
       <c r="I119" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J119" s="141" t="s">
         <v>203</v>
@@ -10316,16 +10346,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B120" s="141" t="n">
         <v>25</v>
       </c>
       <c r="C120" s="141" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D120" s="141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E120" s="140"/>
       <c r="F120" s="141" t="s">
@@ -10335,7 +10365,7 @@
         <v>219</v>
       </c>
       <c r="H120" s="141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I120" s="141" t="s">
         <v>205</v>
@@ -10347,16 +10377,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B121" s="143" t="n">
         <v>26</v>
       </c>
       <c r="C121" s="143" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D121" s="143" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E121" s="142"/>
       <c r="F121" s="143" t="s">
@@ -10366,7 +10396,7 @@
         <v>231</v>
       </c>
       <c r="H121" s="143" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I121" s="143" t="s">
         <v>212</v>
@@ -10378,16 +10408,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="142" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B122" s="143" t="n">
         <v>27</v>
       </c>
       <c r="C122" s="143" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D122" s="143" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E122" s="142"/>
       <c r="F122" s="143" t="s">
@@ -10397,7 +10427,7 @@
         <v>219</v>
       </c>
       <c r="H122" s="143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I122" s="143" t="s">
         <v>205</v>
@@ -10409,29 +10439,29 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B123" s="141" t="n">
         <v>28</v>
       </c>
       <c r="C123" s="141" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D123" s="141" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E123" s="140"/>
       <c r="F123" s="141" t="s">
         <v>237</v>
       </c>
       <c r="G123" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H123" s="141" t="s">
         <v>229</v>
       </c>
       <c r="I123" s="141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J123" s="141" t="s">
         <v>221</v>
@@ -10440,16 +10470,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B124" s="141" t="n">
         <v>29</v>
       </c>
       <c r="C124" s="141" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D124" s="141" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E124" s="140"/>
       <c r="F124" s="141" t="s">
@@ -10459,7 +10489,7 @@
         <v>209</v>
       </c>
       <c r="H124" s="141" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I124" s="141" t="s">
         <v>225</v>
@@ -10471,16 +10501,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="140" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B125" s="141" t="n">
         <v>30</v>
       </c>
       <c r="C125" s="141" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D125" s="141" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E125" s="140"/>
       <c r="F125" s="141" t="s">
@@ -10493,16 +10523,16 @@
         <v>243</v>
       </c>
       <c r="I125" s="141" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J125" s="141" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K125" s="141"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="131" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B504" s="131"/>
       <c r="C504" s="131"/>
@@ -10518,37 +10548,37 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="131" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B505" s="131" t="s">
         <v>176</v>
       </c>
       <c r="C505" s="131" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D505" s="131" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E505" s="131" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F505" s="131" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G505" s="131" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H505" s="131" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I505" s="131" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="J505" s="131" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K505" s="131" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10559,7 +10589,7 @@
         <v>192</v>
       </c>
       <c r="C506" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D506" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Rosario")+($G$5:$G$500="Rosario")+($H$5:$H$500="Rosario")+($I$5:$I$500="Rosario")+($J$5:$J$500="Rosario")+($K$5:$K$500="Rosario")))</f>
@@ -10602,7 +10632,7 @@
         <v>195</v>
       </c>
       <c r="C507" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D507" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Cristina")+($G$5:$G$500="Cristina")+($H$5:$H$500="Cristina")+($I$5:$I$500="Cristina")+($J$5:$J$500="Cristina")+($K$5:$K$500="Cristina")))</f>
@@ -10645,7 +10675,7 @@
         <v>197</v>
       </c>
       <c r="C508" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D508" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Miriam")+($G$5:$G$500="Miriam")+($H$5:$H$500="Miriam")+($I$5:$I$500="Miriam")+($J$5:$J$500="Miriam")+($K$5:$K$500="Miriam")))</f>
@@ -10688,7 +10718,7 @@
         <v>200</v>
       </c>
       <c r="C509" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D509" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="David")+($G$5:$G$500="David")+($H$5:$H$500="David")+($I$5:$I$500="David")+($J$5:$J$500="David")+($K$5:$K$500="David")))</f>
@@ -10731,7 +10761,7 @@
         <v>202</v>
       </c>
       <c r="C510" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D510" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Mercedes")+($G$5:$G$500="Mercedes")+($H$5:$H$500="Mercedes")+($I$5:$I$500="Mercedes")+($J$5:$J$500="Mercedes")+($K$5:$K$500="Mercedes")))</f>
@@ -10774,7 +10804,7 @@
         <v>204</v>
       </c>
       <c r="C511" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D511" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Arturo")+($G$5:$G$500="Arturo")+($H$5:$H$500="Arturo")+($I$5:$I$500="Arturo")+($J$5:$J$500="Arturo")+($K$5:$K$500="Arturo")))</f>
@@ -10817,7 +10847,7 @@
         <v>206</v>
       </c>
       <c r="C512" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D512" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Aitor")+($G$5:$G$500="Aitor")+($H$5:$H$500="Aitor")+($I$5:$I$500="Aitor")+($J$5:$J$500="Aitor")+($K$5:$K$500="Aitor")))</f>
@@ -10854,13 +10884,13 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="133" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B513" s="134" t="s">
         <v>208</v>
       </c>
       <c r="C513" s="134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D513" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fatima")+($G$5:$G$500="Fatima")+($H$5:$H$500="Fatima")+($I$5:$I$500="Fatima")+($J$5:$J$500="Fatima")+($K$5:$K$500="Fatima")))</f>
@@ -10903,7 +10933,7 @@
         <v>210</v>
       </c>
       <c r="C514" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D514" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tania")+($G$5:$G$500="Tania")+($H$5:$H$500="Tania")+($I$5:$I$500="Tania")+($J$5:$J$500="Tania")+($K$5:$K$500="Tania")))</f>
@@ -10940,13 +10970,13 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="133" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B515" s="134" t="s">
         <v>213</v>
       </c>
       <c r="C515" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D515" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Asis")+($G$5:$G$500="Asis")+($H$5:$H$500="Asis")+($I$5:$I$500="Asis")+($J$5:$J$500="Asis")+($K$5:$K$500="Asis")))</f>
@@ -10983,13 +11013,13 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="133" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B516" s="134" t="s">
         <v>216</v>
       </c>
       <c r="C516" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D516" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR2")+($G$5:$G$500="PatriciaR2")+($H$5:$H$500="PatriciaR2")+($I$5:$I$500="PatriciaR2")+($J$5:$J$500="PatriciaR2")+($K$5:$K$500="PatriciaR2")))</f>
@@ -11032,7 +11062,7 @@
         <v>218</v>
       </c>
       <c r="C517" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D517" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Eva")+($G$5:$G$500="Eva")+($H$5:$H$500="Eva")+($I$5:$I$500="Eva")+($J$5:$J$500="Eva")+($K$5:$K$500="Eva")))</f>
@@ -11075,7 +11105,7 @@
         <v>220</v>
       </c>
       <c r="C518" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D518" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Emilio")+($G$5:$G$500="Emilio")+($H$5:$H$500="Emilio")+($I$5:$I$500="Emilio")+($J$5:$J$500="Emilio")+($K$5:$K$500="Emilio")))</f>
@@ -11118,7 +11148,7 @@
         <v>222</v>
       </c>
       <c r="C519" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D519" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Antonio")+($G$5:$G$500="Antonio")+($H$5:$H$500="Antonio")+($I$5:$I$500="Antonio")+($J$5:$J$500="Antonio")+($K$5:$K$500="Antonio")))</f>
@@ -11155,13 +11185,13 @@
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="133" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B520" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C520" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D520" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR2")+($G$5:$G$500="AnaR2")+($H$5:$H$500="AnaR2")+($I$5:$I$500="AnaR2")+($J$5:$J$500="AnaR2")+($K$5:$K$500="AnaR2")))</f>
@@ -11204,7 +11234,7 @@
         <v>226</v>
       </c>
       <c r="C521" s="134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D521" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Marc")+($G$5:$G$500="Marc")+($H$5:$H$500="Marc")+($I$5:$I$500="Marc")+($J$5:$J$500="Marc")+($K$5:$K$500="Marc")))</f>
@@ -11241,13 +11271,13 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="133" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B522" s="134" t="s">
         <v>228</v>
       </c>
       <c r="C522" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D522" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="PatriciaR3")+($G$5:$G$500="PatriciaR3")+($H$5:$H$500="PatriciaR3")+($I$5:$I$500="PatriciaR3")+($J$5:$J$500="PatriciaR3")+($K$5:$K$500="PatriciaR3")))</f>
@@ -11290,7 +11320,7 @@
         <v>230</v>
       </c>
       <c r="C523" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D523" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Candela")+($G$5:$G$500="Candela")+($H$5:$H$500="Candela")+($I$5:$I$500="Candela")+($J$5:$J$500="Candela")+($K$5:$K$500="Candela")))</f>
@@ -11327,13 +11357,13 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="133" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B524" s="134" t="s">
         <v>232</v>
       </c>
       <c r="C524" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D524" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Fabian")+($G$5:$G$500="Fabian")+($H$5:$H$500="Fabian")+($I$5:$I$500="Fabian")+($J$5:$J$500="Fabian")+($K$5:$K$500="Fabian")))</f>
@@ -11376,7 +11406,7 @@
         <v>234</v>
       </c>
       <c r="C525" s="134" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D525" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Tony")+($G$5:$G$500="Tony")+($H$5:$H$500="Tony")+($I$5:$I$500="Tony")+($J$5:$J$500="Tony")+($K$5:$K$500="Tony")))</f>
@@ -11419,7 +11449,7 @@
         <v>236</v>
       </c>
       <c r="C526" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D526" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Carlota")+($G$5:$G$500="Carlota")+($H$5:$H$500="Carlota")+($I$5:$I$500="Carlota")+($J$5:$J$500="Carlota")+($K$5:$K$500="Carlota")))</f>
@@ -11462,7 +11492,7 @@
         <v>238</v>
       </c>
       <c r="C527" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D527" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Almudena")+($G$5:$G$500="Almudena")+($H$5:$H$500="Almudena")+($I$5:$I$500="Almudena")+($J$5:$J$500="Almudena")+($K$5:$K$500="Almudena")))</f>
@@ -11499,13 +11529,13 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="133" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B528" s="134" t="s">
         <v>240</v>
       </c>
       <c r="C528" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D528" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="AnaR4")+($G$5:$G$500="AnaR4")+($H$5:$H$500="AnaR4")+($I$5:$I$500="AnaR4")+($J$5:$J$500="AnaR4")+($K$5:$K$500="AnaR4")))</f>
@@ -11548,7 +11578,7 @@
         <v>242</v>
       </c>
       <c r="C529" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D529" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Sandra")+($G$5:$G$500="Sandra")+($H$5:$H$500="Sandra")+($I$5:$I$500="Sandra")+($J$5:$J$500="Sandra")+($K$5:$K$500="Sandra")))</f>
@@ -11591,7 +11621,7 @@
         <v>244</v>
       </c>
       <c r="C530" s="134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D530" s="134" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Isa")+($G$5:$G$500="Isa")+($H$5:$H$500="Isa")+($I$5:$I$500="Isa")+($J$5:$J$500="Isa")+($K$5:$K$500="Isa")))</f>
@@ -11628,13 +11658,13 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="137" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B531" s="138" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C531" s="138" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D531" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Maria")+($G$5:$G$500="Maria")+($H$5:$H$500="Maria")+($I$5:$I$500="Maria")+($J$5:$J$500="Maria")+($K$5:$K$500="Maria")))</f>
@@ -11671,13 +11701,13 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="137" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B532" s="138" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C532" s="138" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D532" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="Gerard")+($G$5:$G$500="Gerard")+($H$5:$H$500="Gerard")+($I$5:$I$500="Gerard")+($J$5:$J$500="Gerard")+($K$5:$K$500="Gerard")))</f>
@@ -11714,13 +11744,13 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="137" t="s">
+        <v>506</v>
+      </c>
+      <c r="B533" s="138" t="s">
         <v>504</v>
       </c>
-      <c r="B533" s="138" t="s">
-        <v>502</v>
-      </c>
       <c r="C533" s="138" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D533" s="138" t="n">
         <f aca="false">SUMPRODUCT(($D$5:$D$500="Viernes")*(($F$5:$F$500="DavidR3")+($G$5:$G$500="DavidR3")+($H$5:$H$500="DavidR3")+($I$5:$I$500="DavidR3")+($J$5:$J$500="DavidR3")+($K$5:$K$500="DavidR3")))</f>
@@ -12808,7 +12838,7 @@
         <v>23</v>
       </c>
       <c r="L36" s="29" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="M36" s="28" t="s">
         <v>23</v>
@@ -13060,7 +13090,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C45" s="28" t="s">
         <v>23</v>
@@ -17510,7 +17540,7 @@
       </c>
       <c r="M23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Carlota")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Carlota")</f>
@@ -17530,7 +17560,7 @@
       </c>
       <c r="R23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Carlota")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Carlota")</f>
@@ -17723,7 +17753,7 @@
       </c>
       <c r="M26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Sandra")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Sandra")</f>
@@ -17743,7 +17773,7 @@
       </c>
       <c r="R26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Sandra")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" s="60" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Sandra")</f>
@@ -19634,7 +19664,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -20198,6 +20228,20 @@
       </c>
       <c r="D47" s="1" t="s">
         <v>359</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C48" s="103" t="s">
+        <v>361</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -20238,7 +20282,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20251,7 +20295,7 @@
         <v>176</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20262,7 +20306,7 @@
         <v>192</v>
       </c>
       <c r="C3" s="113" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20273,7 +20317,7 @@
         <v>195</v>
       </c>
       <c r="C4" s="114" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20284,7 +20328,7 @@
         <v>197</v>
       </c>
       <c r="C5" s="113" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20295,7 +20339,7 @@
         <v>200</v>
       </c>
       <c r="C6" s="114" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20306,7 +20350,7 @@
         <v>202</v>
       </c>
       <c r="C7" s="113" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20317,7 +20361,7 @@
         <v>204</v>
       </c>
       <c r="C8" s="114" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20328,7 +20372,7 @@
         <v>206</v>
       </c>
       <c r="C9" s="113" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20339,7 +20383,7 @@
         <v>208</v>
       </c>
       <c r="C10" s="114" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20361,7 +20405,7 @@
         <v>213</v>
       </c>
       <c r="C12" s="114" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20372,7 +20416,7 @@
         <v>216</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20383,7 +20427,7 @@
         <v>218</v>
       </c>
       <c r="C14" s="114" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20394,7 +20438,7 @@
         <v>220</v>
       </c>
       <c r="C15" s="113" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20405,7 +20449,7 @@
         <v>222</v>
       </c>
       <c r="C16" s="114" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20416,7 +20460,7 @@
         <v>224</v>
       </c>
       <c r="C17" s="113" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20427,7 +20471,7 @@
         <v>226</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20438,7 +20482,7 @@
         <v>228</v>
       </c>
       <c r="C19" s="113" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20449,7 +20493,7 @@
         <v>230</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20460,7 +20504,7 @@
         <v>232</v>
       </c>
       <c r="C21" s="113" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20471,7 +20515,7 @@
         <v>234</v>
       </c>
       <c r="C22" s="114" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20482,7 +20526,7 @@
         <v>236</v>
       </c>
       <c r="C23" s="113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20493,7 +20537,7 @@
         <v>238</v>
       </c>
       <c r="C24" s="114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20504,7 +20548,7 @@
         <v>240</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20515,7 +20559,7 @@
         <v>242</v>
       </c>
       <c r="C26" s="114" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20526,124 +20570,124 @@
         <v>244</v>
       </c>
       <c r="C27" s="113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="106" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B29" s="106"/>
       <c r="C29" s="106"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B30" s="78" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="115" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B31" s="115" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C31" s="115" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="115" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B32" s="115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C32" s="115" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="115" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B33" s="115" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C33" s="115" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="115" t="s">
+        <v>394</v>
+      </c>
+      <c r="B34" s="115" t="s">
+        <v>391</v>
+      </c>
+      <c r="C34" s="115" t="s">
         <v>392</v>
-      </c>
-      <c r="B34" s="115" t="s">
-        <v>389</v>
-      </c>
-      <c r="C34" s="115" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="115" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B35" s="115" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C35" s="115" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="115" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C36" s="115" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="115" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C37" s="115" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="115" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C38" s="115" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="115" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C39" s="115" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -20677,7 +20721,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20688,181 +20732,181 @@
         <v>176</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="96" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B3" s="116" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="100" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="96" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C5" s="119" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="100" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B6" s="118" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="96" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B7" s="116" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C7" s="119" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D7" s="116" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="100" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="96" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B9" s="116" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D9" s="116" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="100" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B10" s="118" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D10" s="118" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="96" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B11" s="116" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D11" s="116" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="100" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B12" s="118" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="96" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B13" s="116" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D13" s="116" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="100" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B14" s="118" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D14" s="118" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -20896,7 +20940,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="112" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -20909,19 +20953,19 @@
         <v>176</v>
       </c>
       <c r="B2" s="121" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D2" s="121" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E2" s="121" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F2" s="121" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G2" s="121" t="s">
         <v>19</v>
@@ -20935,12 +20979,12 @@
         <v>191</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122"/>
       <c r="F3" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G3" s="122"/>
     </row>
@@ -20952,12 +20996,12 @@
         <v>194</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D4" s="123"/>
       <c r="E4" s="123"/>
       <c r="F4" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G4" s="123"/>
     </row>
@@ -20969,12 +21013,12 @@
         <v>196</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G5" s="122"/>
     </row>
@@ -20986,12 +21030,12 @@
         <v>199</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D6" s="123"/>
       <c r="E6" s="123"/>
       <c r="F6" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G6" s="123"/>
     </row>
@@ -21003,12 +21047,12 @@
         <v>201</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D7" s="122"/>
       <c r="E7" s="122"/>
       <c r="F7" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G7" s="122"/>
     </row>
@@ -21020,12 +21064,12 @@
         <v>203</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D8" s="123"/>
       <c r="E8" s="123"/>
       <c r="F8" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G8" s="123"/>
     </row>
@@ -21037,12 +21081,12 @@
         <v>205</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D9" s="122"/>
       <c r="E9" s="122"/>
       <c r="F9" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G9" s="122"/>
     </row>
@@ -21054,12 +21098,12 @@
         <v>207</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D10" s="123"/>
       <c r="E10" s="123"/>
       <c r="F10" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G10" s="123"/>
     </row>
@@ -21071,11 +21115,11 @@
         <v>209</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D11" s="122"/>
       <c r="E11" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F11" s="122"/>
       <c r="G11" s="122"/>
@@ -21088,14 +21132,14 @@
         <v>212</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D12" s="123"/>
       <c r="E12" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F12" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G12" s="123"/>
     </row>
@@ -21107,11 +21151,11 @@
         <v>215</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D13" s="122"/>
       <c r="E13" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F13" s="122"/>
       <c r="G13" s="122"/>
@@ -21124,14 +21168,14 @@
         <v>217</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D14" s="123"/>
       <c r="E14" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F14" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G14" s="123"/>
     </row>
@@ -21143,14 +21187,14 @@
         <v>219</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D15" s="122"/>
       <c r="E15" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F15" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G15" s="122"/>
     </row>
@@ -21162,14 +21206,14 @@
         <v>221</v>
       </c>
       <c r="C16" s="63" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D16" s="123"/>
       <c r="E16" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F16" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G16" s="123"/>
     </row>
@@ -21181,14 +21225,14 @@
         <v>223</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D17" s="122"/>
       <c r="E17" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F17" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G17" s="122"/>
     </row>
@@ -21200,14 +21244,14 @@
         <v>225</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D18" s="123"/>
       <c r="E18" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F18" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G18" s="123"/>
     </row>
@@ -21219,10 +21263,10 @@
         <v>227</v>
       </c>
       <c r="C19" s="57" t="s">
+        <v>454</v>
+      </c>
+      <c r="D19" s="122" t="s">
         <v>452</v>
-      </c>
-      <c r="D19" s="122" t="s">
-        <v>450</v>
       </c>
       <c r="E19" s="122"/>
       <c r="F19" s="122"/>
@@ -21236,10 +21280,10 @@
         <v>229</v>
       </c>
       <c r="C20" s="63" t="s">
+        <v>454</v>
+      </c>
+      <c r="D20" s="123" t="s">
         <v>452</v>
-      </c>
-      <c r="D20" s="123" t="s">
-        <v>450</v>
       </c>
       <c r="E20" s="123"/>
       <c r="F20" s="123"/>
@@ -21253,11 +21297,11 @@
         <v>231</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D21" s="122"/>
       <c r="E21" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F21" s="122"/>
       <c r="G21" s="122"/>
@@ -21270,11 +21314,11 @@
         <v>233</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D22" s="123"/>
       <c r="E22" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F22" s="123"/>
       <c r="G22" s="123"/>
@@ -21287,15 +21331,15 @@
         <v>235</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D23" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E23" s="122"/>
       <c r="F23" s="122"/>
       <c r="G23" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21306,15 +21350,15 @@
         <v>237</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D24" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E24" s="123"/>
       <c r="F24" s="123"/>
       <c r="G24" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21325,15 +21369,15 @@
         <v>239</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D25" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E25" s="122"/>
       <c r="F25" s="122"/>
       <c r="G25" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21344,15 +21388,15 @@
         <v>241</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D26" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E26" s="123"/>
       <c r="F26" s="123"/>
       <c r="G26" s="123" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21363,20 +21407,20 @@
         <v>243</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D27" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E27" s="122"/>
       <c r="F27" s="122"/>
       <c r="G27" s="122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="124" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B28" s="124"/>
       <c r="C28" s="124"/>
@@ -21387,121 +21431,121 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="125" t="s">
+        <v>457</v>
+      </c>
+      <c r="B29" s="126" t="s">
+        <v>458</v>
+      </c>
+      <c r="C29" s="125" t="s">
         <v>455</v>
       </c>
-      <c r="B29" s="126" t="s">
-        <v>456</v>
-      </c>
-      <c r="C29" s="125" t="s">
-        <v>453</v>
-      </c>
       <c r="D29" s="125" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
       <c r="G29" s="125" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="125" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B30" s="126" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C30" s="125" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D30" s="125" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
       <c r="G30" s="125" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="125" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B31" s="126" t="s">
         <v>199</v>
       </c>
       <c r="C31" s="125" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D31" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E31" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F31" s="125"/>
       <c r="G31" s="125"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="125" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B32" s="126" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="125" t="s">
+        <v>454</v>
+      </c>
+      <c r="D32" s="127" t="s">
         <v>462</v>
       </c>
-      <c r="C32" s="125" t="s">
-        <v>452</v>
-      </c>
-      <c r="D32" s="127" t="s">
-        <v>460</v>
-      </c>
       <c r="E32" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F32" s="125"/>
       <c r="G32" s="125"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="125" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B33" s="126" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C33" s="125" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D33" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E33" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F33" s="125"/>
       <c r="G33" s="125"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="125" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B34" s="126" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C34" s="125" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D34" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E34" s="127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F34" s="125"/>
       <c r="G34" s="125"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="128" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B37" s="128"/>
       <c r="C37" s="128"/>
@@ -21512,7 +21556,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="129" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B38" s="129"/>
       <c r="C38" s="129"/>

--- a/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
+++ b/guardias-anestesia/cuadrantes/CUADRANTEOCT2026_plantilla.xlsx
@@ -1295,7 +1295,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Base FIJA del calendario que paso Pablo (Mayor / UCQ de fin de semana / TX). No se ha modificado.</t>
+          <t xml:space="preserve">CAMBIO autorizado por Pablo (2026-08-19): antes Patricia R2, ahora Asis.
+Motivo: era la unica forma de cubrir el 2o PEQ del sabado 24 sin dejar a nadie con 3 fines de semana y sin interrumpir vacaciones. Patricia R2 mueve su sabado de UCQ del 17 al 24, Asis coge el 17, y asi Marc queda libre para el PEQ del 24.</t>
         </r>
       </text>
     </comment>
@@ -1331,7 +1332,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Base FIJA del calendario que paso Pablo (Mayor / UCQ de fin de semana / TX). No se ha modificado.</t>
+          <t xml:space="preserve">CAMBIO autorizado por Pablo (2026-08-19): antes Marc, ahora Patricia R2.
+Motivo: era la unica forma de cubrir el 2o PEQ del sabado 24 sin dejar a nadie con 3 fines de semana y sin interrumpir vacaciones. Patricia R2 mueve su sabado de UCQ del 17 al 24, Asis coge el 17, y asi Marc queda libre para el PEQ del 24.</t>
         </r>
       </text>
     </comment>
@@ -1344,18 +1346,6 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Base FIJA del calendario que paso Pablo (Mayor / UCQ de fin de semana / TX). No se ha modificado.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L38" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">SIN CUBRIR (unico hueco del mes). Sabado 24: los 8 R1 estan de congreso (H-18) y Asis y Ana R2 de vacaciones. Solo quedan Eva, Emilio y Antonio para PEQ, y Marc no puede porque ya tiene UCQ ese dia. H-05 obliga a que los 2 del viernes 23 sean los mismos del domingo 25, y H-04 obliga a que los del sabado 24 libren el 25: hacen falta 4 personas distintas y solo hay 3.</t>
         </r>
       </text>
     </comment>
@@ -1843,7 +1833,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="667">
   <si>
     <t xml:space="preserve">Cuadrante de Guardias — Servicio de Anestesiología y Reanimación</t>
   </si>
@@ -1965,217 +1955,217 @@
     <t xml:space="preserve">TX-Sandra</t>
   </si>
   <si>
+    <t xml:space="preserve">UCQ-Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Tania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-PatriciaR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Candela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Cristina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Miriam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Arturo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Fatima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4, Emi, Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, Carlota, Cris, Eva, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, Carlota, Cris, Eva, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, AnaR4, Carlota, Cris, Eva, Isa, Merce, Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-Almudena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-Carlota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-PatriciaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Emilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Almudena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Sandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAY-Carlota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Aitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Rosario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Emilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Asis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEQ-AnaR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4, Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Asís, Cande, Eva, PatR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Asís, Cande, Fati, Miri, PatR3, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, AnaR4, Fati, Miri, PatR3, Tania, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Carlota, Fati, Miri, PatR3, Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
     <t xml:space="preserve">UCQ-Marc</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Tania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-PatriciaR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Candela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Fatima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Miriam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-AnaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Arturo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Asis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4, Emi, Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, Carlota, Cris, Eva, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, Carlota, Cris, Eva, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Aitor, Almu, AnaR2, AnaR4, Carlota, Cris, Eva, Isa, Merce, Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-AnaR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-Almudena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-Carlota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-PatriciaR2</t>
-  </si>
-  <si>
     <t xml:space="preserve">UCQ-Asis</t>
   </si>
   <si>
-    <t xml:space="preserve">UCQ-Fabian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-Emilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Almudena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Sandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAY-Carlota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Aitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Rosario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Marc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4, Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Asís, Cande, Eva, PatR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Asís, Cande, Fati, Miri, PatR3, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, AnaR4, Fati, Miri, PatR3, Tania, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Carlota, Fati, Miri, PatR3, Tony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★ 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAY-AnaR4</t>
   </si>
   <si>
     <t xml:space="preserve">PEQ-Mercedes</t>
   </si>
   <si>
-    <t xml:space="preserve">PEQ-Cristina</t>
+    <t xml:space="preserve">⛔ PatR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ AnaR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, Anto, Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛔ Almu, AnaR4, Anto, Isa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCQ-AnaR2</t>
   </si>
   <si>
     <t xml:space="preserve">PEQ-Eva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ PatR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ AnaR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, Anto, Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⛔ Almu, AnaR4, Anto, Isa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCQ-AnaR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEQ-Emilio</t>
   </si>
   <si>
     <t xml:space="preserve">⛔ Almu</t>
@@ -2654,48 +2644,48 @@
     <t xml:space="preserve">Cobertura completa: cada día tiene exactamente 1 TX, 1 UCQ, 1 MAY y 2 PEQ.</t>
   </si>
   <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobertura COMPLETA los 33 dias: 1 TX, 1 UCQ, 1 MAY y 2 PEQ. El hueco que habia en el 2o PEQ del sabado 24 quedo resuelto el 2026-08-19 moviendo el sabado de UCQ de Patricia R2 del 17 al 24 (Asis coge el 17), lo que libera a Marc para el PEQ del 24.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadie ocupa más de un puesto el mismo día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 violaciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saliente de guardia libra 24h (D+1 vacío).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardia en sábado (no puente) ⇒ libra domingo y lunes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pareja viernes-domingo: misma persona, mismo puesto, bloque indivisible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclusión de puentes: quien cubre Pilar (10-12 oct) no cubre Santos (31 oct-2 nov) y viceversa.</t>
+  </si>
+  <si>
     <t xml:space="preserve">⚠️</t>
   </si>
   <si>
-    <t xml:space="preserve">1 hueco: falta 1 de los 2 PEQ del sabado 24. Los 8 R1 estan de congreso (H-18) y Asis y Ana R2 de vacaciones; solo quedan Eva, Emilio y Antonio, y Marc no puede porque ya tiene UCQ ese dia. H-05 obliga a que los 2 del viernes 23 sean los mismos del domingo 25 y H-04 obliga a que los del sabado 24 libren el 25: hacen falta 4 personas distintas y solo hay 3. Resto del mes: cobertura completa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadie ocupa más de un puesto el mismo día.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 violaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saliente de guardia libra 24h (D+1 vacío).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardia en sábado (no puente) ⇒ libra domingo y lunes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pareja viernes-domingo: misma persona, mismo puesto, bloque indivisible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclusión de puentes: quien cubre Pilar (10-12 oct) no cubre Santos (31 oct-2 nov) y viceversa.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 casos, ambos de la base fija: Almudena (TX el 12, del Pilar, y TX el 31, 1 y 2 nov, de los Santos) y Ana G (TX el 11, del Pilar, y MAY el 1 nov, de los Santos). Viene de la BASE FIJA del calendario que paso Pablo (Mayor/UCQ de finde/TX). No se ha tocado por indicacion expresa suya.</t>
   </si>
   <si>
@@ -2834,7 +2824,7 @@
     <t xml:space="preserve">VEREDICTO GLOBAL: </t>
   </si>
   <si>
-    <t xml:space="preserve">Reparto reconstruido el 2026-08-19 sobre la BASE FIJA del calendario que paso Pablo (Mayor + UCQ de fin de semana + TX intactos). Lo generado son los 16 UCQ de diario y los 66 PEQ. VEREDICTO: el relleno no introduce NI UNA violacion — las 6 incidencias (H-06, H-09, H-10, H-11, H-15, H-16) estan todas en celdas de la base fija, y S-06 esta relajada por decision de Pablo. Unico hueco del mes: 1 PEQ del sabado 24, estructuralmente imposible de cubrir (ver H-01).</t>
+    <t xml:space="preserve">Reparto sobre la BASE FIJA del calendario de Pablo. Mayor y TX intactos; del UCQ de fin de semana solo se movieron 2 casillas, autorizadas por Pablo (sabados 17 y 24). COBERTURA COMPLETA, 0 huecos. Ningun R2 pasa de 2 fines de semana. R1 todos a 5, R2 todos a 6. Las 6 incidencias restantes (H-06, H-09, H-10, H-11, H-15, H-16) estan todas en celdas de la base fija, verificado celda a celda; S-06 esta relajada por decision de Pablo (10 dias).</t>
   </si>
   <si>
     <t xml:space="preserve">Puntuación de reglas blandas S-01 a S-07 (0-41, ver fuente de la verdad §7 para el detalle de cada métrica)</t>
@@ -2909,19 +2899,19 @@
     <t xml:space="preserve">19/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">H-01 (1 PEQ del sabado 24 sin cubrir)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congreso R1 (H-18) + vacaciones de Asis y Ana R2 dejan solo a Eva, Emilio y Antonio; Marc ya tiene UCQ ese dia. H-05 + H-04 exigen 4 personas distintas entre el 23/25 y el 24. Minimo estructural comprobado con el solver: 1 hueco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructural (base fija)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-06, H-09, H-10, H-15, H-16 (base fija)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todas estas incidencias estan en celdas del calendario que paso Pablo (Mayor / UCQ de finde / TX), verificado celda a celda. Se respetan sin modificar por indicacion expresa suya.</t>
+    <t xml:space="preserve">Cambio de 2 casillas de la base (UCQ sabados 17 y 24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para cubrir el 2o PEQ del sabado 24: Patricia R2 pasa su sabado de UCQ del 17 al 24 y Asis coge el 17. Asi Marc queda libre para el PEQ del 24. Demostrado que sin mover alguna casilla de la base es IMPOSIBLE (el solver da INFEASIBLE), y que esta es la unica via de 2 celdas que respeta H-16 y el tope de 2 findes. Nadie gana un fin de semana: Asis cambia el suyo del 3-4 al 16-18.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo (2026-08-19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-06, H-09, H-10, H-15, H-16-Fabian (base fija)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incidencias en celdas del calendario que paso Pablo, verificadas celda a celda. Se respetan sin modificar.</t>
   </si>
   <si>
     <t xml:space="preserve">Pablo (calendario base)</t>
@@ -2930,19 +2920,16 @@
     <t xml:space="preserve">H-20 solo para Fabian (7 en vez de 6)</t>
   </si>
   <si>
-    <t xml:space="preserve">La base le da 2 dias de MAY (31 oct y 2 nov por H-07). Con el tope de 6 sus UCQ bajarian a 4 y no quedarian plazas de PEQ suficientes para que los 8 R1 llegasen a su minimo de 4 guardias.</t>
+    <t xml:space="preserve">La base le da 2 dias de MAY (31 oct y 2 nov por H-07). Con el tope de 6, sus UCQ bajarian a 4 y no quedarian plazas de PEQ para que los 8 R1 llegasen a su minimo de 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Aritmetica forzada</t>
   </si>
   <si>
-    <t xml:space="preserve">S-06 (2 R1 juntos en PEQ): 9 dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relajada por decision expresa de Pablo ('cumpliendo todas las normas menos la norma de r1 juntos'). Dias: 2, 4, 8, 9, 11, 16, 18, 30, 32.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pablo (2026-08-19)</t>
+    <t xml:space="preserve">S-06 (2 R1 juntos en PEQ): 10 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relajada por decision expresa de Pablo. Dias: 2, 3, 4, 16, 17, 18, 30, 31, 1 y 2 nov.</t>
   </si>
   <si>
     <t xml:space="preserve">Bloqueos y vacaciones declarados — octubre 2026 (32 = 1 nov, 33 = 2 nov)</t>
@@ -2966,19 +2953,22 @@
     <t xml:space="preserve">8-9, 23-25</t>
   </si>
   <si>
+    <t xml:space="preserve">— (ninguno). NOTA: su sabado de UCQ se movio del 17 al 24 (autorizado por Pablo, 19/08).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 26, 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-4, 23-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">— (ninguno)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 26, 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-4, 23-25</t>
   </si>
   <si>
     <t xml:space="preserve">8-12</t>
@@ -3860,7 +3850,7 @@
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="67">
+  <fonts count="68">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4047,6 +4037,14 @@
       <color rgb="FFC0392B"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -4478,6 +4476,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEDF7ED"/>
         <bgColor rgb="FFF4F7F4"/>
       </patternFill>
@@ -4498,12 +4502,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F9FC"/>
         <bgColor rgb="FFF8F9FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -4832,7 +4830,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4844,19 +4842,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4868,43 +4866,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="31" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="34" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4912,19 +4910,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="39" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4932,39 +4930,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="43" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="44" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="45" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4972,23 +4970,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="43" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4996,7 +4994,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5012,7 +5010,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5024,23 +5022,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="48" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5048,71 +5046,71 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="49" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5120,11 +5118,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5132,7 +5130,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5140,19 +5138,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="24" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="23" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5160,11 +5158,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5172,19 +5170,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="56" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="57" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5192,35 +5190,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="58" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="59" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="59" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="59" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="60" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="60" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="61" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5228,7 +5226,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="63" fillId="32" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="64" fillId="32" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5236,27 +5234,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="65" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="65" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="65" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="65" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="66" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5264,27 +5254,35 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="66" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="33" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5326,7 +5324,7 @@
       <rgbColor rgb="FF375623"/>
       <rgbColor rgb="FF1E5B2A"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF7F6000"/>
       <rgbColor rgb="FF4B5563"/>
       <rgbColor rgb="FF047857"/>
       <rgbColor rgb="FFCCCCCC"/>
@@ -5339,11 +5337,11 @@
       <rgbColor rgb="FFE06666"/>
       <rgbColor rgb="FF1D4ED8"/>
       <rgbColor rgb="FFCBD5E1"/>
-      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF44546A"/>
       <rgbColor rgb="FFF4F7F4"/>
       <rgbColor rgb="FFFFF3CD"/>
       <rgbColor rgb="FFE5E9EF"/>
-      <rgbColor rgb="FF44546A"/>
+      <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF7C5CBF"/>
       <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FFF8F9FA"/>
@@ -5705,34 +5703,34 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="113" t="s">
         <v>274</v>
-      </c>
-      <c r="B6" s="113" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="115" t="s">
         <v>276</v>
-      </c>
-      <c r="B7" s="115" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="113" t="s">
         <v>278</v>
-      </c>
-      <c r="B8" s="113" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="115" t="s">
         <v>280</v>
-      </c>
-      <c r="B9" s="115" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5930,13 +5928,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>66</v>
@@ -5944,13 +5942,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>64</v>
@@ -5958,7 +5956,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
@@ -5972,13 +5970,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>39</v>
@@ -5992,7 +5990,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -6003,10 +6001,10 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6014,18 +6012,18 @@
         <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6038,10 +6036,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6051,12 +6049,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6066,12 +6064,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -6196,15 +6194,15 @@
       </c>
       <c r="E5" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$506+'Histórico de guardias'!$E$506+'Histórico de guardias'!$F$506)+('Resumen de guardias'!$Q$3+'Resumen de guardias'!$R$3+'Resumen de guardias'!$S$3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G5" s="133" t="n">
         <f aca="false">E5-F5</f>
-        <v>-0.875</v>
+        <v>0</v>
       </c>
       <c r="H5" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$506+'Resumen de guardias'!$T$3</f>
@@ -6212,11 +6210,11 @@
       </c>
       <c r="I5" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J5" s="133" t="n">
         <f aca="false">H5-I5</f>
-        <v>-0.5</v>
+        <v>-0.625</v>
       </c>
       <c r="K5" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$506+'Resumen de guardias'!$I$3</f>
@@ -6228,7 +6226,7 @@
       </c>
       <c r="M5" s="133" t="n">
         <f aca="false">L5-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C5,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6246,15 +6244,15 @@
       </c>
       <c r="E6" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$507+'Histórico de guardias'!$E$507+'Histórico de guardias'!$F$507)+('Resumen de guardias'!$Q$4+'Resumen de guardias'!$R$4+'Resumen de guardias'!$S$4)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G6" s="133" t="n">
         <f aca="false">E6-F6</f>
-        <v>2.125</v>
+        <v>1</v>
       </c>
       <c r="H6" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$507+'Resumen de guardias'!$T$4</f>
@@ -6262,11 +6260,11 @@
       </c>
       <c r="I6" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J6" s="133" t="n">
         <f aca="false">H6-I6</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K6" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$507+'Resumen de guardias'!$I$4</f>
@@ -6278,7 +6276,7 @@
       </c>
       <c r="M6" s="133" t="n">
         <f aca="false">L6-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C6,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6300,23 +6298,23 @@
       </c>
       <c r="F7" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G7" s="133" t="n">
         <f aca="false">E7-F7</f>
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="H7" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$508+'Resumen de guardias'!$T$5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J7" s="133" t="n">
         <f aca="false">H7-I7</f>
-        <v>-0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K7" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$508+'Resumen de guardias'!$I$5</f>
@@ -6328,7 +6326,7 @@
       </c>
       <c r="M7" s="133" t="n">
         <f aca="false">L7-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C7,$D$5:$D$32,"Sí"))</f>
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6350,23 +6348,23 @@
       </c>
       <c r="F8" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C8,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G8" s="133" t="n">
         <f aca="false">E8-F8</f>
-        <v>-0.875</v>
+        <v>-1</v>
       </c>
       <c r="H8" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$509+'Resumen de guardias'!$T$6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C8,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J8" s="133" t="n">
         <f aca="false">H8-I8</f>
-        <v>0.5</v>
+        <v>-0.625</v>
       </c>
       <c r="K8" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$509+'Resumen de guardias'!$I$6</f>
@@ -6378,7 +6376,7 @@
       </c>
       <c r="M8" s="133" t="n">
         <f aca="false">L8-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C8,$D$5:$D$32,"Sí"))</f>
-        <v>-2.625</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6396,27 +6394,27 @@
       </c>
       <c r="E9" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$510+'Histórico de guardias'!$E$510+'Histórico de guardias'!$F$510)+('Resumen de guardias'!$Q$7+'Resumen de guardias'!$R$7+'Resumen de guardias'!$S$7)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C9,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G9" s="133" t="n">
         <f aca="false">E9-F9</f>
-        <v>0.125</v>
+        <v>2</v>
       </c>
       <c r="H9" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$510+'Resumen de guardias'!$T$7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C9,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J9" s="133" t="n">
         <f aca="false">H9-I9</f>
-        <v>-0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K9" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$510+'Resumen de guardias'!$I$7</f>
@@ -6424,11 +6422,11 @@
       </c>
       <c r="L9" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$K$510+'Resumen de guardias'!$L$7</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M9" s="133" t="n">
         <f aca="false">L9-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C9,$D$5:$D$32,"Sí"))</f>
-        <v>-0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6446,15 +6444,15 @@
       </c>
       <c r="E10" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$511+'Histórico de guardias'!$E$511+'Histórico de guardias'!$F$511)+('Resumen de guardias'!$Q$8+'Resumen de guardias'!$R$8+'Resumen de guardias'!$S$8)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C10,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G10" s="133" t="n">
         <f aca="false">E10-F10</f>
-        <v>1.125</v>
+        <v>-2</v>
       </c>
       <c r="H10" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$511+'Resumen de guardias'!$T$8</f>
@@ -6462,11 +6460,11 @@
       </c>
       <c r="I10" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C10,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J10" s="133" t="n">
         <f aca="false">H10-I10</f>
-        <v>-0.5</v>
+        <v>-0.625</v>
       </c>
       <c r="K10" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$511+'Resumen de guardias'!$I$8</f>
@@ -6478,7 +6476,7 @@
       </c>
       <c r="M10" s="133" t="n">
         <f aca="false">L10-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C10,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6496,15 +6494,15 @@
       </c>
       <c r="E11" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$512+'Histórico de guardias'!$E$512+'Histórico de guardias'!$F$512)+('Resumen de guardias'!$Q$9+'Resumen de guardias'!$R$9+'Resumen de guardias'!$S$9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C11,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G11" s="133" t="n">
         <f aca="false">E11-F11</f>
-        <v>-0.875</v>
+        <v>0</v>
       </c>
       <c r="H11" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$512+'Resumen de guardias'!$T$9</f>
@@ -6512,11 +6510,11 @@
       </c>
       <c r="I11" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C11,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J11" s="133" t="n">
         <f aca="false">H11-I11</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K11" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$512+'Resumen de guardias'!$I$9</f>
@@ -6528,7 +6526,7 @@
       </c>
       <c r="M11" s="133" t="n">
         <f aca="false">L11-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C11,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6546,15 +6544,15 @@
       </c>
       <c r="E12" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$513+'Histórico de guardias'!$E$513+'Histórico de guardias'!$F$513)+('Resumen de guardias'!$Q$10+'Resumen de guardias'!$R$10+'Resumen de guardias'!$S$10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí")</f>
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="G12" s="133" t="n">
         <f aca="false">E12-F12</f>
-        <v>-0.875</v>
+        <v>0</v>
       </c>
       <c r="H12" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$513+'Resumen de guardias'!$T$10</f>
@@ -6562,11 +6560,11 @@
       </c>
       <c r="I12" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí")</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J12" s="133" t="n">
         <f aca="false">H12-I12</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K12" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$513+'Resumen de guardias'!$I$10</f>
@@ -6578,7 +6576,7 @@
       </c>
       <c r="M12" s="133" t="n">
         <f aca="false">L12-(AVERAGEIFS($L$5:$L$32,$C$5:$C$32,$C12,$D$5:$D$32,"Sí"))</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6612,11 +6610,11 @@
       </c>
       <c r="I13" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C13,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J13" s="133" t="n">
         <f aca="false">H13-I13</f>
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K13" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$514+'Resumen de guardias'!$I$11</f>
@@ -6662,11 +6660,11 @@
       </c>
       <c r="I14" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C14,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J14" s="133" t="n">
         <f aca="false">H14-I14</f>
-        <v>-0.75</v>
+        <v>-0.625</v>
       </c>
       <c r="K14" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$515+'Resumen de guardias'!$I$12</f>
@@ -6712,11 +6710,11 @@
       </c>
       <c r="I15" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C15,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J15" s="133" t="n">
         <f aca="false">H15-I15</f>
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K15" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$516+'Resumen de guardias'!$I$13</f>
@@ -6746,7 +6744,7 @@
       </c>
       <c r="E16" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$517+'Histórico de guardias'!$E$517+'Histórico de guardias'!$F$517)+('Resumen de guardias'!$Q$14+'Resumen de guardias'!$R$14+'Resumen de guardias'!$S$14)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C16,$D$5:$D$32,"Sí")</f>
@@ -6754,7 +6752,7 @@
       </c>
       <c r="G16" s="133" t="n">
         <f aca="false">E16-F16</f>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="H16" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$517+'Resumen de guardias'!$T$14</f>
@@ -6762,11 +6760,11 @@
       </c>
       <c r="I16" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C16,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J16" s="133" t="n">
         <f aca="false">H16-I16</f>
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K16" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$517+'Resumen de guardias'!$I$14</f>
@@ -6796,7 +6794,7 @@
       </c>
       <c r="E17" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$518+'Histórico de guardias'!$E$518+'Histórico de guardias'!$F$518)+('Resumen de guardias'!$Q$15+'Resumen de guardias'!$R$15+'Resumen de guardias'!$S$15)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C17,$D$5:$D$32,"Sí")</f>
@@ -6804,7 +6802,7 @@
       </c>
       <c r="G17" s="133" t="n">
         <f aca="false">E17-F17</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$518+'Resumen de guardias'!$T$15</f>
@@ -6812,11 +6810,11 @@
       </c>
       <c r="I17" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C17,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J17" s="133" t="n">
         <f aca="false">H17-I17</f>
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K17" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$518+'Resumen de guardias'!$I$15</f>
@@ -6846,7 +6844,7 @@
       </c>
       <c r="E18" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$519+'Histórico de guardias'!$E$519+'Histórico de guardias'!$F$519)+('Resumen de guardias'!$Q$16+'Resumen de guardias'!$R$16+'Resumen de guardias'!$S$16)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C18,$D$5:$D$32,"Sí")</f>
@@ -6854,19 +6852,19 @@
       </c>
       <c r="G18" s="133" t="n">
         <f aca="false">E18-F18</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$519+'Resumen de guardias'!$T$16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C18,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J18" s="133" t="n">
         <f aca="false">H18-I18</f>
-        <v>0.25</v>
+        <v>-0.625</v>
       </c>
       <c r="K18" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$519+'Resumen de guardias'!$I$16</f>
@@ -6908,15 +6906,15 @@
       </c>
       <c r="H19" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$520+'Resumen de guardias'!$T$17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C19,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J19" s="133" t="n">
         <f aca="false">H19-I19</f>
-        <v>-0.75</v>
+        <v>0.375</v>
       </c>
       <c r="K19" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$520+'Resumen de guardias'!$I$17</f>
@@ -6946,7 +6944,7 @@
       </c>
       <c r="E20" s="131" t="n">
         <f aca="false">('Histórico de guardias'!$D$521+'Histórico de guardias'!$E$521+'Histórico de guardias'!$F$521)+('Resumen de guardias'!$Q$18+'Resumen de guardias'!$R$18+'Resumen de guardias'!$S$18)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="131" t="n">
         <f aca="false">AVERAGEIFS($E$5:$E$32,$C$5:$C$32,$C20,$D$5:$D$32,"Sí")</f>
@@ -6954,19 +6952,19 @@
       </c>
       <c r="G20" s="133" t="n">
         <f aca="false">E20-F20</f>
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H20" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$J$521+'Resumen de guardias'!$T$18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="131" t="n">
         <f aca="false">AVERAGEIFS($H$5:$H$32,$C$5:$C$32,$C20,$D$5:$D$32,"Sí")</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="J20" s="133" t="n">
         <f aca="false">H20-I20</f>
-        <v>0.25</v>
+        <v>-0.625</v>
       </c>
       <c r="K20" s="131" t="n">
         <f aca="false">'Histórico de guardias'!$G$521+'Resumen de guardias'!$I$18</f>
@@ -13131,31 +13129,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="I17" s="25" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M17" s="25" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13163,25 +13161,25 @@
         <v>23</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" s="27" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I18" s="27" t="s">
         <v>23</v>
@@ -13193,7 +13191,7 @@
         <v>23</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M18" s="27" t="s">
         <v>23</v>
@@ -13207,43 +13205,43 @@
         <v>25</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L19" s="29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M19" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N19" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13251,103 +13249,103 @@
         <v>25</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="29" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N20" s="29" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="30"/>
       <c r="G21" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="30"/>
       <c r="I21" s="30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J21" s="30"/>
       <c r="K21" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L21" s="30"/>
       <c r="M21" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N21" s="30"/>
     </row>
     <row r="22" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N23" s="22"/>
     </row>
@@ -13401,43 +13399,43 @@
         <v>21</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="I26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="24" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="K26" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>67</v>
+      <c r="L26" s="32" t="s">
+        <v>94</v>
       </c>
       <c r="M26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="N26" s="24" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13445,25 +13443,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="27" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I27" s="27" t="s">
         <v>23</v>
@@ -13489,43 +13487,43 @@
         <v>25</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="E28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="I28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J28" s="29" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="K28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="M28" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N28" s="29" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13533,103 +13531,103 @@
         <v>25</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="G29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J29" s="29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L29" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M29" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D30" s="30"/>
       <c r="E30" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F30" s="30"/>
       <c r="G30" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="30"/>
       <c r="I30" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J30" s="30"/>
       <c r="K30" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L30" s="30"/>
       <c r="M30" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L32" s="22"/>
       <c r="M32" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N32" s="22"/>
     </row>
@@ -13683,19 +13681,19 @@
         <v>21</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>21</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="G35" s="25" t="s">
         <v>21</v>
@@ -13712,8 +13710,8 @@
       <c r="K35" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="L35" s="24" t="s">
-        <v>40</v>
+      <c r="L35" s="32" t="s">
+        <v>67</v>
       </c>
       <c r="M35" s="25" t="s">
         <v>21</v>
@@ -13733,7 +13731,7 @@
         <v>23</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>23</v>
@@ -13745,25 +13743,25 @@
         <v>23</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I36" s="27" t="s">
         <v>23</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K36" s="27" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M36" s="27" t="s">
         <v>23</v>
       </c>
       <c r="N36" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13771,7 +13769,7 @@
         <v>25</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C37" s="28" t="s">
         <v>25</v>
@@ -13783,13 +13781,13 @@
         <v>25</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G37" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="I37" s="28" t="s">
         <v>25</v>
@@ -13801,7 +13799,7 @@
         <v>25</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="M37" s="28" t="s">
         <v>25</v>
@@ -13815,7 +13813,7 @@
         <v>25</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>25</v>
@@ -13827,13 +13825,13 @@
         <v>25</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G38" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="I38" s="28" t="s">
         <v>25</v>
@@ -13844,7 +13842,9 @@
       <c r="K38" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="32"/>
+      <c r="L38" s="29" t="s">
+        <v>49</v>
+      </c>
       <c r="M38" s="28" t="s">
         <v>25</v>
       </c>
@@ -13963,19 +13963,19 @@
         <v>21</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C44" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>21</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G44" s="25" t="s">
         <v>21</v>
@@ -14007,7 +14007,7 @@
         <v>23</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="27" t="s">
         <v>23</v>
@@ -14025,13 +14025,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I45" s="27" t="s">
         <v>23</v>
       </c>
       <c r="J45" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K45" s="27" t="s">
         <v>23</v>
@@ -14043,7 +14043,7 @@
         <v>23</v>
       </c>
       <c r="N45" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14051,43 +14051,43 @@
         <v>25</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="I46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M46" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N46" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14095,19 +14095,19 @@
         <v>25</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C47" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E47" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G47" s="28" t="s">
         <v>25</v>
@@ -14119,19 +14119,19 @@
         <v>25</v>
       </c>
       <c r="J47" s="29" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K47" s="28" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="29" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="M47" s="28" t="s">
         <v>25</v>
       </c>
       <c r="N47" s="29" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="D48" s="33"/>
       <c r="E48" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F48" s="30"/>
       <c r="G48" s="30" t="s">
@@ -14262,7 +14262,7 @@
         <v>25</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
@@ -14282,7 +14282,7 @@
         <v>25</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="B16" s="42" t="n">
         <f aca="false">SUM(C16:AI16)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="43" t="n">
         <f aca="false">IF('Calendario Octubre 2026'!$H$10&lt;&gt;"",1,0)+IF('Calendario Octubre 2026'!$H$11&lt;&gt;"",1,0)</f>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="Z16" s="44" t="n">
         <f aca="false">IF('Calendario Octubre 2026'!$L$37&lt;&gt;"",1,0)+IF('Calendario Octubre 2026'!$L$38&lt;&gt;"",1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16" s="44" t="n">
         <f aca="false">IF('Calendario Octubre 2026'!$N$37&lt;&gt;"",1,0)+IF('Calendario Octubre 2026'!$N$38&lt;&gt;"",1,0)</f>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">SUM(C17:AI17)</f>
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">SUM(C13:C16)</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="Z17" s="50" t="n">
         <f aca="false">SUM(Z13:Z16)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA17" s="50" t="n">
         <f aca="false">SUM(AA13:AA16)</f>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="B24" s="42" t="n">
         <f aca="false">SUM(C24:AI24)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="43" t="n">
         <f aca="false">C8-C16</f>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="Z24" s="44" t="n">
         <f aca="false">Z8-Z16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="44" t="n">
         <f aca="false">AA8-AA16</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">SUM(C25:AI25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="Z25" s="50" t="n">
         <f aca="false">SUM(Z21:Z24)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="50" t="n">
         <f aca="false">SUM(AA21:AA24)</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="M3" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Rosario")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Rosario")</f>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="R3" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Rosario")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Rosario")</f>
@@ -17148,11 +17148,11 @@
       </c>
       <c r="M4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Cristina")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Cristina")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Cristina")</f>
@@ -17160,19 +17160,19 @@
       </c>
       <c r="P4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Cristina")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Cristina")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Cristina")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Cristina")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Cristina")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Cristina")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Cristina")</f>
@@ -17215,7 +17215,7 @@
       </c>
       <c r="M5" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Miriam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Miriam")</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="P5" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Miriam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Miriam")</f>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="T5" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Miriam")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Miriam")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Miriam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="N6" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-David")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-David")</f>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="P6" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-David")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-David")</f>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="T6" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-David")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-David")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-David")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17341,11 +17341,11 @@
       </c>
       <c r="K7" s="58" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$A$5:$N$58,"PEQ-Mercedes")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="59" t="n">
         <f aca="false">SUM(H7:K7)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Mercedes")</f>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="N7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Mercedes")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Mercedes")</f>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="Q7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Mercedes")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Mercedes")</f>
@@ -17373,11 +17373,11 @@
       </c>
       <c r="S7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Mercedes")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Mercedes")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Mercedes")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Mercedes")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17416,31 +17416,31 @@
       </c>
       <c r="M8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Arturo")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Arturo")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Arturo")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Arturo")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Arturo")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Arturo")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Arturo")</f>
@@ -17487,27 +17487,27 @@
       </c>
       <c r="N9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Aitor")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Aitor")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Aitor")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Aitor")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Aitor")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Aitor")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Aitor")</f>
@@ -17550,11 +17550,11 @@
       </c>
       <c r="M10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Fatima")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Fatima")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Fatima")</f>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="P10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Fatima")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Fatima")</f>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="R10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Fatima")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Fatima")</f>
@@ -17621,19 +17621,19 @@
       </c>
       <c r="M11" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Tania")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Tania")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Tania")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Tania")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Tania")</f>
@@ -17690,15 +17690,15 @@
       </c>
       <c r="M12" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Asis")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Asis")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Asis")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Asis")</f>
@@ -17765,11 +17765,11 @@
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-PatriciaR2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-PatriciaR2")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-PatriciaR2")</f>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="N14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Eva")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Eva")</f>
@@ -17846,15 +17846,15 @@
       </c>
       <c r="Q14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Eva")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Eva")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Eva")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Eva")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Eva")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Eva")</f>
@@ -17899,31 +17899,31 @@
       </c>
       <c r="M15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Emilio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Emilio")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Emilio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Emilio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Emilio")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Emilio")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Emilio")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Emilio")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Emilio")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Emilio")</f>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="N16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Antonio")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Antonio")</f>
@@ -17984,19 +17984,19 @@
       </c>
       <c r="Q16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Antonio")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Antonio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Antonio")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Antonio")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Antonio")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Antonio")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18037,19 +18037,19 @@
       </c>
       <c r="M17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-AnaR2")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-AnaR2")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-AnaR2")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-AnaR2")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-AnaR2")</f>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="T17" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-AnaR2")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-AnaR2")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-AnaR2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="M18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Marc")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Marc")</f>
@@ -18116,11 +18116,11 @@
       </c>
       <c r="O18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Marc")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Marc")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Marc")</f>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="R18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$L$5:$L$58,"*-Marc")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$N$5:$N$58,"*-Marc")</f>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="T18" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$25:$B$29,"*-Marc")+COUNTIF('Calendario Octubre 2026'!$N$43:$N$47,"*-Marc")+COUNTIF('Calendario Octubre 2026'!$B$52:$B$56,"*-Marc")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="M21" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$B$5:$B$58,"*-Fabian")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$D$5:$D$58,"*-Fabian")</f>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="O21" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Fabian")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Fabian")</f>
@@ -18394,11 +18394,11 @@
       </c>
       <c r="O22" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$F$5:$F$58,"*-Tony")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$H$5:$H$58,"*-Tony")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="57" t="n">
         <f aca="false">COUNTIF('Calendario Octubre 2026'!$J$5:$J$58,"*-Tony")</f>
@@ -18790,11 +18790,11 @@
       </c>
       <c r="K28" s="68" t="n">
         <f aca="false">SUM(K3:K27)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L28" s="68" t="n">
         <f aca="false">SUM(L3:L27)</f>
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M28" s="68" t="n">
         <f aca="false">SUM(M3:M27)</f>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="R28" s="68" t="n">
         <f aca="false">SUM(R3:R27)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S28" s="68" t="n">
         <f aca="false">SUM(S3:S27)</f>
@@ -19109,43 +19109,43 @@
         <v>255</v>
       </c>
       <c r="O4" s="77" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P4" s="77" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q4" s="77" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R4" s="77" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S4" s="78" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T4" s="78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U4" s="77" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V4" s="77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W4" s="77" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X4" s="77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y4" s="77" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Z4" s="78" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AA4" s="78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AB4" s="77" t="s">
         <v>117</v>
@@ -20634,63 +20634,63 @@
         <v>271</v>
       </c>
       <c r="C5" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="99" t="s">
         <v>272</v>
-      </c>
-      <c r="D5" s="99" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="94" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="94" t="s">
-        <v>275</v>
-      </c>
       <c r="C6" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="96" t="s">
         <v>272</v>
-      </c>
-      <c r="D6" s="96" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="98" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="98" t="s">
-        <v>277</v>
-      </c>
       <c r="C7" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="99" t="s">
         <v>272</v>
-      </c>
-      <c r="D7" s="99" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="94" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="94" t="s">
-        <v>279</v>
-      </c>
       <c r="C8" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="96" t="s">
         <v>272</v>
-      </c>
-      <c r="D8" s="96" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="98" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="C9" s="95" t="s">
         <v>281</v>
-      </c>
-      <c r="C9" s="95" t="s">
-        <v>268</v>
       </c>
       <c r="D9" s="99" t="s">
         <v>282</v>
@@ -20704,10 +20704,10 @@
         <v>284</v>
       </c>
       <c r="C10" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="96" t="s">
         <v>272</v>
-      </c>
-      <c r="D10" s="96" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20718,10 +20718,10 @@
         <v>286</v>
       </c>
       <c r="C11" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="99" t="s">
         <v>272</v>
-      </c>
-      <c r="D11" s="99" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20732,7 +20732,7 @@
         <v>288</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D12" s="96" t="s">
         <v>289</v>
@@ -20746,7 +20746,7 @@
         <v>291</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D13" s="99" t="s">
         <v>292</v>
@@ -20763,7 +20763,7 @@
         <v>295</v>
       </c>
       <c r="C14" s="95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D14" s="96" t="s">
         <v>296</v>
@@ -20777,7 +20777,7 @@
         <v>298</v>
       </c>
       <c r="C15" s="95" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D15" s="99" t="s">
         <v>299</v>
@@ -20791,7 +20791,7 @@
         <v>301</v>
       </c>
       <c r="C16" s="95" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D16" s="96" t="s">
         <v>302</v>
@@ -20805,10 +20805,10 @@
         <v>304</v>
       </c>
       <c r="C17" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="99" t="s">
         <v>272</v>
-      </c>
-      <c r="D17" s="99" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20819,7 +20819,7 @@
         <v>306</v>
       </c>
       <c r="C18" s="95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D18" s="96" t="s">
         <v>307</v>
@@ -20833,7 +20833,7 @@
         <v>309</v>
       </c>
       <c r="C19" s="95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D19" s="99" t="s">
         <v>310</v>
@@ -20850,10 +20850,10 @@
         <v>313</v>
       </c>
       <c r="C20" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" s="96" t="s">
         <v>272</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>273</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>314</v>
@@ -20867,7 +20867,7 @@
         <v>316</v>
       </c>
       <c r="C21" s="95" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D21" s="99" t="s">
         <v>317</v>
@@ -20884,10 +20884,10 @@
         <v>320</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="100" t="s">
         <v>272</v>
-      </c>
-      <c r="D22" s="100" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20898,7 +20898,7 @@
         <v>322</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D23" s="100" t="s">
         <v>323</v>
@@ -20912,7 +20912,7 @@
         <v>325</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D24" s="100" t="s">
         <v>326</v>
@@ -21146,7 +21146,7 @@
         <v>363</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="404.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21190,7 +21190,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="109" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B1" s="109"/>
       <c r="C1" s="109"/>
@@ -21203,7 +21203,7 @@
         <v>178</v>
       </c>
       <c r="C2" s="75" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21214,7 +21214,7 @@
         <v>194</v>
       </c>
       <c r="C3" s="110" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21225,7 +21225,7 @@
         <v>197</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21236,7 +21236,7 @@
         <v>199</v>
       </c>
       <c r="C5" s="110" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21247,7 +21247,7 @@
         <v>202</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21258,7 +21258,7 @@
         <v>204</v>
       </c>
       <c r="C7" s="110" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21269,7 +21269,7 @@
         <v>206</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21280,7 +21280,7 @@
         <v>208</v>
       </c>
       <c r="C9" s="110" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21291,7 +21291,7 @@
         <v>210</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21313,7 +21313,7 @@
         <v>215</v>
       </c>
       <c r="C12" s="111" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21324,7 +21324,7 @@
         <v>218</v>
       </c>
       <c r="C13" s="110" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21335,7 +21335,7 @@
         <v>220</v>
       </c>
       <c r="C14" s="111" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21346,7 +21346,7 @@
         <v>222</v>
       </c>
       <c r="C15" s="110" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21357,7 +21357,7 @@
         <v>224</v>
       </c>
       <c r="C16" s="111" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21368,7 +21368,7 @@
         <v>226</v>
       </c>
       <c r="C17" s="110" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21379,7 +21379,7 @@
         <v>228</v>
       </c>
       <c r="C18" s="111" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
